--- a/resources/si/_SI_差分總表.xlsx
+++ b/resources/si/_SI_差分總表.xlsx
@@ -10668,92 +10668,102 @@
       </c>
     </row>
     <row r="3" ht="111" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Rennasorana</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>索菈娜</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>rennasorana_si_annoyedc.webp</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>rennaannoyc</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>與索拉娜同框</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>1535</v>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>1221×1536</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="L3" s="6" t="inlineStr">
         <is>
           <t>resources/si/rennasorana_si_annoyedc.webp</t>
         </is>
       </c>
     </row>
     <row r="4" ht="111" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Rennasorana</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>索菈娜</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>rennasorana_si_annoyedd.webp</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>rennaannoy</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>與索拉娜同框</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
-      <c r="J4" s="2" t="n"/>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>1534</v>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>1091×1536</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="L4" s="6" t="inlineStr">
         <is>
           <t>resources/si/rennasorana_si_annoyedd.webp</t>
         </is>
@@ -12373,42 +12383,47 @@
       </c>
     </row>
     <row r="38" ht="111" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>蕾娜</t>
         </is>
       </c>
-      <c r="B38" s="3" t="n"/>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>renna_si_hugangry2.png</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="n"/>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="n"/>
-      <c r="I38" s="2" t="n"/>
-      <c r="J38" s="2" t="n"/>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>hugangry2</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="n"/>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>1528</v>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
         <is>
           <t>1024×1535</t>
         </is>
       </c>
-      <c r="L38" s="4" t="inlineStr">
+      <c r="L38" s="6" t="inlineStr">
         <is>
           <t>resources/si/renna_si_hugangry2.png</t>
         </is>
@@ -12517,84 +12532,94 @@
       </c>
     </row>
     <row r="41" ht="111" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>蕾娜</t>
         </is>
       </c>
-      <c r="B41" s="3" t="n"/>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>renna_si_hugserious.webp</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="n"/>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="n"/>
-      <c r="I41" s="2" t="n"/>
-      <c r="J41" s="2" t="n"/>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L41" s="4" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>hugserious</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="n"/>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>1528</v>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L41" s="6" t="inlineStr">
         <is>
           <t>resources/si/renna_si_hugserious.webp</t>
         </is>
       </c>
     </row>
     <row r="42" ht="111" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>蕾娜</t>
         </is>
       </c>
-      <c r="B42" s="3" t="n"/>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>renna_si_hugshock.webp</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="n"/>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="n"/>
-      <c r="I42" s="2" t="n"/>
-      <c r="J42" s="2" t="n"/>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>hugshock</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="n"/>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>1528</v>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L42" s="6" t="inlineStr">
         <is>
           <t>resources/si/renna_si_hugshock.webp</t>
         </is>
@@ -12648,84 +12673,94 @@
       </c>
     </row>
     <row r="44" ht="111" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>蕾娜</t>
         </is>
       </c>
-      <c r="B44" s="3" t="n"/>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t>renna_si_hugtalk.webp</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="n"/>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="n"/>
-      <c r="I44" s="2" t="n"/>
-      <c r="J44" s="2" t="n"/>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L44" s="4" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>hugtalk</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="n"/>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>1528</v>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L44" s="6" t="inlineStr">
         <is>
           <t>resources/si/renna_si_hugtalk.webp</t>
         </is>
       </c>
     </row>
     <row r="45" ht="111" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>蕾娜</t>
         </is>
       </c>
-      <c r="B45" s="3" t="n"/>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>renna_si_hugtalk2.webp</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="n"/>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="n"/>
-      <c r="I45" s="2" t="n"/>
-      <c r="J45" s="2" t="n"/>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L45" s="4" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>hugtalk2</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="n"/>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>1528</v>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L45" s="6" t="inlineStr">
         <is>
           <t>resources/si/renna_si_hugtalk2.webp</t>
         </is>
@@ -18239,7 +18274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:D94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -18718,12 +18753,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Renna</t>
+          <t>Sorana</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>renna_si_hugangry2.png</t>
+          <t>sorana_si_furious.webp</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -18740,12 +18775,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Renna</t>
+          <t>Sorana</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>renna_si_hugserious.webp</t>
+          <t>sorana_si_q.webp</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -18762,12 +18797,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Renna</t>
+          <t>image - 2026-09-20T150615.066</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>renna_si_hugshock.webp</t>
+          <t>image - 2026-09-20T150615.066.png</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -18784,12 +18819,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Renna</t>
+          <t>image - 2026-09-20T150842.343</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>renna_si_hugtalk.webp</t>
+          <t>image - 2026-09-20T150842.343.png</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -18806,12 +18841,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Renna</t>
+          <t>image - 2026-09-20T151013.881</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>renna_si_hugtalk2.webp</t>
+          <t>image - 2026-09-20T151013.881.png</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -18828,12 +18863,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Rennasorana</t>
+          <t>image - 2026-09-20T151141.942</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>rennasorana_si_annoyedc.webp</t>
+          <t>image - 2026-09-20T151141.942.png</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -18850,12 +18885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Rennasorana</t>
+          <t>Torsten</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>rennasorana_si_annoyedd.webp</t>
+          <t>torsten_si_front.webp</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -18872,12 +18907,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sorana</t>
+          <t>Torsten</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>sorana_si_carrynouvelleshock2.webp</t>
+          <t>torsten_si_q.webp</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -18894,12 +18929,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sorana</t>
+          <t>Xanya</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sorana_si_furious.webp</t>
+          <t>xanya_si_front.webp</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -18911,220 +18946,220 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>美術交了沒接線</t>
+          <t>指到但檔案不在</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sorana</t>
+          <t>sorana / excite</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>sorana_si_q.webp</t>
+          <t>resources/si/sorana_si_excite.webp</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>在 script/speakers.js 的 ART 補一筆 expr，並量 fx／top／bot（§6.5）</t>
+          <t>路徑打錯，或美術還沒交 —— 演到那一句會回退基本立繪</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>美術交了沒接線</t>
+          <t>指到但檔案不在</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T150615.066</t>
+          <t>sorana / furiouscute</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T150615.066.png</t>
+          <t>resources/si/sorana_si_furiouscute.webp</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>在 script/speakers.js 的 ART 補一筆 expr，並量 fx／top／bot（§6.5）</t>
+          <t>路徑打錯，或美術還沒交 —— 演到那一句會回退基本立繪</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>美術交了沒接線</t>
+          <t>同差分的另一個版本</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T150842.343</t>
+          <t>Anya</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T150842.343.png</t>
+          <t>resources/si/anya_si_nod.png</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>在 script/speakers.js 的 ART 補一筆 expr，並量 fx／top／bot（§6.5）</t>
+          <t>線上跑的是 anya_si_nod.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>美術交了沒接線</t>
+          <t>同差分的另一個版本</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T151013.881</t>
+          <t>Npc_grocer</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T151013.881.png</t>
+          <t>resources/si/npc/npc_grocer_si_v2.webp</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>在 script/speakers.js 的 ART 補一筆 expr，並量 fx／top／bot（§6.5）</t>
+          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>美術交了沒接線</t>
+          <t>同差分的另一個版本</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T151141.942</t>
+          <t>Npc_grocer</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T151141.942.png</t>
+          <t>resources/si/npc/npc_grocer_si_v3.webp</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>在 script/speakers.js 的 ART 補一筆 expr，並量 fx／top／bot（§6.5）</t>
+          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>美術交了沒接線</t>
+          <t>同差分的另一個版本</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Torsten</t>
+          <t>Npc_grocer</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>torsten_si_front.webp</t>
+          <t>resources/si/npc/npc_grocer_si_v4.webp</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>在 script/speakers.js 的 ART 補一筆 expr，並量 fx／top／bot（§6.5）</t>
+          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>美術交了沒接線</t>
+          <t>同差分的另一個版本</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Torsten</t>
+          <t>Npc_grocer</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>torsten_si_q.webp</t>
+          <t>resources/si/npc/npc_grocer_si_v5.webp</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>在 script/speakers.js 的 ART 補一筆 expr，並量 fx／top／bot（§6.5）</t>
+          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>美術交了沒接線</t>
+          <t>同差分的另一個版本</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Xanya</t>
+          <t>Npc_guildcounter</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>xanya_si_front.webp</t>
+          <t>resources/si/npc/npc_guildcounter_si_v1.webp</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>在 script/speakers.js 的 ART 補一筆 expr，並量 fx／top／bot（§6.5）</t>
+          <t>線上跑的是 npc_guildcounter_si_v5.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>指到但檔案不在</t>
+          <t>同差分的另一個版本</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>sorana / excite</t>
+          <t>Npc_guildcounter</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_excite.webp</t>
+          <t>resources/si/npc/npc_guildcounter_si_v3.webp</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>路徑打錯，或美術還沒交 —— 演到那一句會回退基本立繪</t>
+          <t>線上跑的是 npc_guildcounter_si_v5.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>指到但檔案不在</t>
+          <t>同差分的另一個版本</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>sorana / furiouscute</t>
+          <t>Npc_guildcounter</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_furiouscute.webp</t>
+          <t>resources/si/npc/npc_guildcounter_si_v4.webp</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>路徑打錯，或美術還沒交 —— 演到那一句會回退基本立繪</t>
+          <t>線上跑的是 npc_guildcounter_si_v5.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19136,17 +19171,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Npc_grocer</t>
+          <t>Npc_gunsmith</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_grocer_si_v2.webp</t>
+          <t>resources/si/npc/npc_gunsmith_si_v2.webp</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19158,17 +19193,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Npc_grocer</t>
+          <t>Npc_gunsmith</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_grocer_si_v3.webp</t>
+          <t>resources/si/npc/npc_gunsmith_si_v3.webp</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19180,17 +19215,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Npc_grocer</t>
+          <t>Npc_gunsmith</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_grocer_si_v4.webp</t>
+          <t>resources/si/npc/npc_gunsmith_si_v4.webp</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19202,17 +19237,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Npc_grocer</t>
+          <t>Npc_gunsmith</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_grocer_si_v5.webp</t>
+          <t>resources/si/npc/npc_gunsmith_si_v5.webp</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19224,17 +19259,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Npc_guildcounter</t>
+          <t>Cecilie</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_guildcounter_si_v1.webp</t>
+          <t>resources/si/old/cecilie_si_front.png</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_guildcounter_si_v5.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_front.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19246,17 +19281,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Npc_guildcounter</t>
+          <t>Cecilie</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_guildcounter_si_v3.webp</t>
+          <t>resources/si/old/cecilie_si_lookaside.png</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_guildcounter_si_v5.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_lookaside.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19268,17 +19303,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Npc_guildcounter</t>
+          <t>Cecilie</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_guildcounter_si_v4.webp</t>
+          <t>resources/si/old/cecilie_si_sadback.png</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_guildcounter_si_v5.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_sadback.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19290,17 +19325,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Npc_gunsmith</t>
+          <t>Cecilie</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_gunsmith_si_v2.webp</t>
+          <t>resources/si/old/cecilie_si_smile.png</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_smile.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19312,17 +19347,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Npc_gunsmith</t>
+          <t>Cecilie</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_gunsmith_si_v3.webp</t>
+          <t>resources/si/old/cecilie_si_tease.png</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_tease.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19334,17 +19369,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Npc_gunsmith</t>
+          <t>Cecilie</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_gunsmith_si_v4.webp</t>
+          <t>resources/si/old/cecilie_si_upset.png</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_upset.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19356,17 +19391,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Npc_gunsmith</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_gunsmith_si_v5.webp</t>
+          <t>resources/si/renna_newhair/renna_si_argue.webp</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_argue.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19378,17 +19413,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_front.png</t>
+          <t>resources/si/renna_newhair/renna_si_arguecute.webp</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_front.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_arguecute.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19400,17 +19435,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_lookaside.png</t>
+          <t>resources/si/renna_newhair/renna_si_ask.webp</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_lookaside.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_ask.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19422,17 +19457,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_sadback.png</t>
+          <t>resources/si/renna_newhair/renna_si_askserious.webp</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_sadback.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_askserious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19444,17 +19479,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_smile.png</t>
+          <t>resources/si/renna_newhair/renna_si_awkwerd.webp</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_smile.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_awkwerd.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19466,17 +19501,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_tease.png</t>
+          <t>resources/si/renna_newhair/renna_si_blush.webp</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_tease.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_blush.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19488,17 +19523,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_upset.png</t>
+          <t>resources/si/renna_newhair/renna_si_bow.webp</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_upset.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_bow.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19515,12 +19550,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_argue.webp</t>
+          <t>resources/si/renna_newhair/renna_si_callangry.webp</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_argue.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_callangry.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19537,12 +19572,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_arguecute.webp</t>
+          <t>resources/si/renna_newhair/renna_si_chase.webp</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_arguecute.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_chase.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19559,12 +19594,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_ask.webp</t>
+          <t>resources/si/renna_newhair/renna_si_chase2.webp</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_ask.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_chase2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19581,12 +19616,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_askserious.webp</t>
+          <t>resources/si/renna_newhair/renna_si_command.webp</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_askserious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_command.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19603,12 +19638,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_awkwerd.webp</t>
+          <t>resources/si/renna_newhair/renna_si_covermouth.webp</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_awkwerd.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_covermouth.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19625,12 +19660,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_blush.webp</t>
+          <t>resources/si/renna_newhair/renna_si_cringe.webp</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_blush.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_cringe.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19647,12 +19682,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_bow.webp</t>
+          <t>resources/si/renna_newhair/renna_si_curious.webp</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_bow.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_curious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19669,12 +19704,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_callangry.webp</t>
+          <t>resources/si/renna_newhair/renna_si_die.webp</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_callangry.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_die.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19691,12 +19726,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_chase.webp</t>
+          <t>resources/si/renna_newhair/renna_si_evaluate.webp</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_chase.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_evaluate.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19713,12 +19748,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_chase2.webp</t>
+          <t>resources/si/renna_newhair/renna_si_front.webp</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_chase2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_front.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19735,12 +19770,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_command.webp</t>
+          <t>resources/si/renna_newhair/renna_si_intense.webp</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_command.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_intense.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19757,12 +19792,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_covermouth.webp</t>
+          <t>resources/si/renna_newhair/renna_si_intense2.webp</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_covermouth.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_intense2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19779,12 +19814,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_cringe.webp</t>
+          <t>resources/si/renna_newhair/renna_si_invite.webp</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_cringe.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_invite.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19801,12 +19836,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_curious.webp</t>
+          <t>resources/si/renna_newhair/renna_si_lookaway.webp</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_curious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_lookaway.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19823,12 +19858,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_die.webp</t>
+          <t>resources/si/renna_newhair/renna_si_lookawaytalk.webp</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_die.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_lookawaytalk.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19845,12 +19880,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_evaluate.webp</t>
+          <t>resources/si/renna_newhair/renna_si_lookdown.webp</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_evaluate.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_lookdown.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19867,12 +19902,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_front.webp</t>
+          <t>resources/si/renna_newhair/renna_si_lookup.webp</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_front.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_lookup.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19889,12 +19924,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_intense.webp</t>
+          <t>resources/si/renna_newhair/renna_si_pause.webp</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_intense.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_pause.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19911,12 +19946,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_intense2.webp</t>
+          <t>resources/si/renna_newhair/renna_si_relief.webp</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_intense2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_relief.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19933,12 +19968,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_invite.webp</t>
+          <t>resources/si/renna_newhair/renna_si_sad.webp</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_invite.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_sad.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19955,12 +19990,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_lookaway.webp</t>
+          <t>resources/si/renna_newhair/renna_si_shout.webp</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_lookaway.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_shout.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19977,12 +20012,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_lookawaytalk.webp</t>
+          <t>resources/si/renna_newhair/renna_si_smile.webp</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_lookawaytalk.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_smile.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19999,12 +20034,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_lookdown.webp</t>
+          <t>resources/si/renna_newhair/renna_si_stare.webp</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_lookdown.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_stare.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -20021,12 +20056,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_lookup.webp</t>
+          <t>resources/si/renna_newhair/renna_si_surprise.webp</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_lookup.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_surprise.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -20043,12 +20078,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_pause.webp</t>
+          <t>resources/si/renna_newhair/renna_si_talkserious.webp</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_pause.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_talkserious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -20065,12 +20100,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_relief.webp</t>
+          <t>resources/si/renna_newhair/renna_si_talkwork.webp</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_relief.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_talkwork.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -20087,12 +20122,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_sad.webp</t>
+          <t>resources/si/renna_newhair/renna_si_think.webp</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_sad.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_think.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -20109,12 +20144,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_shout.webp</t>
+          <t>resources/si/renna_newhair/renna_si_tire.webp</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_shout.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_tire.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -20131,12 +20166,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_smile.webp</t>
+          <t>resources/si/renna_newhair/renna_si_upset.webp</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_smile.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_upset.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -20153,12 +20188,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_stare.webp</t>
+          <t>resources/si/renna_newhair/renna_si_upsetstare.webp</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_stare.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_upsetstare.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -20175,12 +20210,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_surprise.webp</t>
+          <t>resources/si/renna_newhair/renna_si_wake.webp</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_surprise.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_wake.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -20197,12 +20232,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_talkserious.webp</t>
+          <t>resources/si/renna_newhair/renna_si_watch.webp</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_talkserious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_watch.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -20219,12 +20254,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_talkwork.webp</t>
+          <t>resources/si/renna_newhair/renna_si_worry.webp</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_talkwork.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_worry.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -20241,12 +20276,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_think.webp</t>
+          <t>resources/si/renna_newhair/renna_si_write.webp</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_think.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_write.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -20263,12 +20298,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_tire.webp</t>
+          <t>resources/si/renna_si_hug.png</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_tire.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_hug.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -20285,12 +20320,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_upset.webp</t>
+          <t>resources/si/renna_si_hugclose.png</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_upset.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_hugclose.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -20307,164 +20342,10 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_upsetstare.webp</t>
+          <t>resources/si/renna_si_huglookaway.png</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_upsetstare.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Renna</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>resources/si/renna_newhair/renna_si_wake.webp</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_wake.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Renna</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>resources/si/renna_newhair/renna_si_watch.webp</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_watch.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Renna</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>resources/si/renna_newhair/renna_si_worry.webp</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_worry.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Renna</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>resources/si/renna_newhair/renna_si_write.webp</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_write.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Renna</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>resources/si/renna_si_hug.png</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_hug.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Renna</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>resources/si/renna_si_hugclose.png</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_hugclose.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Renna</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>resources/si/renna_si_huglookaway.png</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
         <is>
           <t>線上跑的是 renna_si_huglookaway.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
@@ -24560,42 +24441,47 @@
       </c>
     </row>
     <row r="17" ht="111" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>索菈娜</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>sorana_si_carrynouvelleshock2.webp</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="n"/>
-      <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>carrynouvelleshock2</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>1520</v>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
         <is>
           <t>resources/si/sorana_si_carrynouvelleshock2.webp</t>
         </is>
@@ -28542,7 +28428,11 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F26" s="6" t="n"/>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>1 張：anya_si_nod.png</t>
+        </is>
+      </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
           <t>量</t>

--- a/resources/si/_SI_差分總表.xlsx
+++ b/resources/si/_SI_差分總表.xlsx
@@ -22,9 +22,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="image - 2026-09-20t150842.343" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="image - 2026-09-20t151013.881" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="image - 2026-09-20t151141.942" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="索菈娜2" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="城鎮店主 NPC" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待接線・缺檔" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="隨從" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="索菈娜2" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="城鎮店主 NPC" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待接線・缺檔" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2549,31 +2550,6 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>96</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1333500" cy="1333500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="96" name="Image 96" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId96"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -2964,6 +2940,36 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1333500" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
   <oneCellAnchor>
     <from>
       <col>1</col>
@@ -7389,6 +7395,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId74"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>75</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1333500" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="75" name="Image 75" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId75"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -10546,7 +10577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L97"/>
+  <dimension ref="A1:L96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10699,7 +10730,7 @@
         </is>
       </c>
       <c r="H3" s="5" t="n">
-        <v>0.62</v>
+        <v>0.33</v>
       </c>
       <c r="I3" s="5" t="n">
         <v>4</v>
@@ -10750,7 +10781,7 @@
         </is>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.62</v>
+        <v>0.3</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>4</v>
@@ -12305,11 +12336,7 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>1 張：renna_si_hug.png</t>
-        </is>
-      </c>
+      <c r="F36" s="6" t="n"/>
       <c r="G36" s="5" t="inlineStr">
         <is>
           <t>量</t>
@@ -12390,12 +12417,12 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>renna_si_hugangry2.png</t>
+          <t>renna_si_hugclose.webp</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>hugangry2</t>
+          <t>hugclose</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -12420,12 +12447,12 @@
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>1024×1535</t>
+          <t>1024×1536</t>
         </is>
       </c>
       <c r="L38" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_hugangry2.png</t>
+          <t>resources/si/renna_si_hugclose.webp</t>
         </is>
       </c>
     </row>
@@ -12437,12 +12464,12 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>renna_si_hugclose.webp</t>
+          <t>renna_si_huglookaway.webp</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>hugclose</t>
+          <t>huglookaway</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -12450,11 +12477,7 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>1 張：renna_si_hugclose.png</t>
-        </is>
-      </c>
+      <c r="F39" s="6" t="n"/>
       <c r="G39" s="5" t="inlineStr">
         <is>
           <t>量</t>
@@ -12476,7 +12499,7 @@
       </c>
       <c r="L39" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_hugclose.webp</t>
+          <t>resources/si/renna_si_huglookaway.webp</t>
         </is>
       </c>
     </row>
@@ -12488,12 +12511,12 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>renna_si_huglookaway.webp</t>
+          <t>renna_si_hugserious.webp</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>huglookaway</t>
+          <t>hugserious</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -12501,11 +12524,7 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F40" s="6" t="inlineStr">
-        <is>
-          <t>1 張：renna_si_huglookaway.png</t>
-        </is>
-      </c>
+      <c r="F40" s="6" t="n"/>
       <c r="G40" s="5" t="inlineStr">
         <is>
           <t>量</t>
@@ -12527,7 +12546,7 @@
       </c>
       <c r="L40" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_huglookaway.webp</t>
+          <t>resources/si/renna_si_hugserious.webp</t>
         </is>
       </c>
     </row>
@@ -12539,12 +12558,12 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>renna_si_hugserious.webp</t>
+          <t>renna_si_hugshock.webp</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>hugserious</t>
+          <t>hugshock</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -12574,7 +12593,7 @@
       </c>
       <c r="L41" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_hugserious.webp</t>
+          <t>resources/si/renna_si_hugshock.webp</t>
         </is>
       </c>
     </row>
@@ -12586,12 +12605,12 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>renna_si_hugshock.webp</t>
+          <t>renna_si_hugshy.png</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>hugshock</t>
+          <t>hugshy</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -12621,7 +12640,7 @@
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_hugshock.webp</t>
+          <t>resources/si/renna_si_hugshy.png</t>
         </is>
       </c>
     </row>
@@ -12633,12 +12652,12 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>renna_si_hugshy.png</t>
+          <t>renna_si_hugtalk.webp</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>hugshy</t>
+          <t>hugtalk</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -12668,7 +12687,7 @@
       </c>
       <c r="L43" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_hugshy.png</t>
+          <t>resources/si/renna_si_hugtalk.webp</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12699,12 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>renna_si_hugtalk.webp</t>
+          <t>renna_si_hugtalk2.webp</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>hugtalk</t>
+          <t>hugtalk2</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -12715,7 +12734,7 @@
       </c>
       <c r="L44" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_hugtalk.webp</t>
+          <t>resources/si/renna_si_hugtalk2.webp</t>
         </is>
       </c>
     </row>
@@ -12727,12 +12746,12 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>renna_si_hugtalk2.webp</t>
+          <t>renna_si_intense.webp</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>hugtalk2</t>
+          <t>intense</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -12740,20 +12759,24 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F45" s="6" t="n"/>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>1 張：renna_newhair/</t>
+        </is>
+      </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
           <t>量</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
-        <v>0.274</v>
+        <v>0.629</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
@@ -12762,7 +12785,7 @@
       </c>
       <c r="L45" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_hugtalk2.webp</t>
+          <t>resources/si/renna_si_intense.webp</t>
         </is>
       </c>
     </row>
@@ -12774,12 +12797,12 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>renna_si_intense.webp</t>
+          <t>renna_si_intense2.webp</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>intense</t>
+          <t>intense2</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -12798,13 +12821,13 @@
         </is>
       </c>
       <c r="H46" s="5" t="n">
-        <v>0.629</v>
+        <v>0.51</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>1526</v>
+        <v>1520</v>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
@@ -12813,7 +12836,7 @@
       </c>
       <c r="L46" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_intense.webp</t>
+          <t>resources/si/renna_si_intense2.webp</t>
         </is>
       </c>
     </row>
@@ -12825,12 +12848,12 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>renna_si_intense2.webp</t>
+          <t>renna_si_invite.webp</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>intense2</t>
+          <t>invite</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -12849,13 +12872,13 @@
         </is>
       </c>
       <c r="H47" s="5" t="n">
-        <v>0.51</v>
+        <v>0.537</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>1520</v>
+        <v>1525</v>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
@@ -12864,7 +12887,7 @@
       </c>
       <c r="L47" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_intense2.webp</t>
+          <t>resources/si/renna_si_invite.webp</t>
         </is>
       </c>
     </row>
@@ -12876,12 +12899,12 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>renna_si_invite.webp</t>
+          <t>renna_si_laugh.webp</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>invite</t>
+          <t>laugh</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -12889,24 +12912,20 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F48" s="6" t="inlineStr">
-        <is>
-          <t>1 張：renna_newhair/</t>
-        </is>
-      </c>
+      <c r="F48" s="6" t="n"/>
       <c r="G48" s="5" t="inlineStr">
         <is>
           <t>量</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
-        <v>0.537</v>
+        <v>0.522</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>1525</v>
+        <v>1500</v>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
@@ -12915,7 +12934,7 @@
       </c>
       <c r="L48" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_invite.webp</t>
+          <t>resources/si/renna_si_laugh.webp</t>
         </is>
       </c>
     </row>
@@ -12927,12 +12946,12 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>renna_si_laugh.webp</t>
+          <t>renna_si_lookaside.webp</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>laugh</t>
+          <t>lookaside</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -12947,13 +12966,13 @@
         </is>
       </c>
       <c r="H49" s="5" t="n">
-        <v>0.522</v>
+        <v>0.513</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>1500</v>
+        <v>1519</v>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
@@ -12962,7 +12981,7 @@
       </c>
       <c r="L49" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_laugh.webp</t>
+          <t>resources/si/renna_si_lookaside.webp</t>
         </is>
       </c>
     </row>
@@ -12974,12 +12993,12 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>renna_si_lookaside.webp</t>
+          <t>renna_si_lookaway.webp</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>lookaside</t>
+          <t>lookaway</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -12987,20 +13006,24 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F50" s="6" t="n"/>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>1 張：renna_newhair/</t>
+        </is>
+      </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
           <t>量</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
-        <v>0.513</v>
+        <v>0.532</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>1519</v>
+        <v>1529</v>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
@@ -13009,7 +13032,7 @@
       </c>
       <c r="L50" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_lookaside.webp</t>
+          <t>resources/si/renna_si_lookaway.webp</t>
         </is>
       </c>
     </row>
@@ -13021,12 +13044,12 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>renna_si_lookaway.webp</t>
+          <t>renna_si_lookawaytalk.webp</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>lookaway</t>
+          <t>lookawaytalk</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -13045,13 +13068,13 @@
         </is>
       </c>
       <c r="H51" s="5" t="n">
-        <v>0.532</v>
+        <v>0.545</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>1529</v>
+        <v>1519</v>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
@@ -13060,7 +13083,7 @@
       </c>
       <c r="L51" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_lookaway.webp</t>
+          <t>resources/si/renna_si_lookawaytalk.webp</t>
         </is>
       </c>
     </row>
@@ -13072,12 +13095,12 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>renna_si_lookawaytalk.webp</t>
+          <t>renna_si_lookdown.webp</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>lookawaytalk</t>
+          <t>lookdown</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -13096,13 +13119,13 @@
         </is>
       </c>
       <c r="H52" s="5" t="n">
-        <v>0.545</v>
+        <v>0.548</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>1519</v>
+        <v>1524</v>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
@@ -13111,7 +13134,7 @@
       </c>
       <c r="L52" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_lookawaytalk.webp</t>
+          <t>resources/si/renna_si_lookdown.webp</t>
         </is>
       </c>
     </row>
@@ -13123,12 +13146,12 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>renna_si_lookdown.webp</t>
+          <t>renna_si_lookfaropen.webp</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>lookdown</t>
+          <t>lookfaropen</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -13136,24 +13159,20 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>1 張：renna_newhair/</t>
-        </is>
-      </c>
+      <c r="F53" s="6" t="n"/>
       <c r="G53" s="5" t="inlineStr">
         <is>
           <t>量</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
-        <v>0.548</v>
+        <v>0.572</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>1524</v>
+        <v>1517</v>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
@@ -13162,7 +13181,7 @@
       </c>
       <c r="L53" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_lookdown.webp</t>
+          <t>resources/si/renna_si_lookfaropen.webp</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13193,12 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>renna_si_lookfaropen.webp</t>
+          <t>renna_si_lookup.webp</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>lookfaropen</t>
+          <t>lookup</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -13187,20 +13206,24 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F54" s="6" t="n"/>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>1 張：renna_newhair/</t>
+        </is>
+      </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
           <t>量</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
-        <v>0.572</v>
+        <v>0.51</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>1517</v>
+        <v>1520</v>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
@@ -13209,7 +13232,7 @@
       </c>
       <c r="L54" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_lookfaropen.webp</t>
+          <t>resources/si/renna_si_lookup.webp</t>
         </is>
       </c>
     </row>
@@ -13221,12 +13244,12 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>renna_si_lookup.webp</t>
+          <t>renna_si_meltdown.webp</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>lookup</t>
+          <t>meltdown</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -13234,24 +13257,20 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F55" s="6" t="inlineStr">
-        <is>
-          <t>1 張：renna_newhair/</t>
-        </is>
-      </c>
+      <c r="F55" s="6" t="n"/>
       <c r="G55" s="5" t="inlineStr">
         <is>
           <t>量</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
-        <v>0.51</v>
+        <v>0.528</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>1520</v>
+        <v>1535</v>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
@@ -13260,7 +13279,7 @@
       </c>
       <c r="L55" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_lookup.webp</t>
+          <t>resources/si/renna_si_meltdown.webp</t>
         </is>
       </c>
     </row>
@@ -13272,12 +13291,12 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>renna_si_meltdown.webp</t>
+          <t>renna_si_meltdowncry.webp</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>meltdown</t>
+          <t>meltdowncry</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -13292,13 +13311,13 @@
         </is>
       </c>
       <c r="H56" s="5" t="n">
-        <v>0.528</v>
+        <v>0.607</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>1535</v>
+        <v>1532</v>
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
@@ -13307,7 +13326,7 @@
       </c>
       <c r="L56" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_meltdown.webp</t>
+          <t>resources/si/renna_si_meltdowncry.webp</t>
         </is>
       </c>
     </row>
@@ -13319,12 +13338,12 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>renna_si_meltdowncry.webp</t>
+          <t>renna_si_nod.webp</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>meltdowncry</t>
+          <t>nod</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -13339,22 +13358,22 @@
         </is>
       </c>
       <c r="H57" s="5" t="n">
-        <v>0.607</v>
+        <v>0.508</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>1532</v>
+        <v>1520</v>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>1024×1536</t>
+          <t>1024×1535</t>
         </is>
       </c>
       <c r="L57" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_meltdowncry.webp</t>
+          <t>resources/si/renna_si_nod.webp</t>
         </is>
       </c>
     </row>
@@ -13366,12 +13385,12 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>renna_si_nod.webp</t>
+          <t>renna_si_pause.webp</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>nod</t>
+          <t>pause</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -13379,29 +13398,33 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F58" s="6" t="n"/>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>1 張：renna_newhair/</t>
+        </is>
+      </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
           <t>量</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
-        <v>0.508</v>
+        <v>0.513</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>1520</v>
+        <v>1525</v>
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>1024×1535</t>
+          <t>1024×1536</t>
         </is>
       </c>
       <c r="L58" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_nod.webp</t>
+          <t>resources/si/renna_si_pause.webp</t>
         </is>
       </c>
     </row>
@@ -13413,12 +13436,12 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>renna_si_pause.webp</t>
+          <t>renna_si_pointmap.webp</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>pause</t>
+          <t>pointmap</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -13426,24 +13449,20 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>1 張：renna_newhair/</t>
-        </is>
-      </c>
+      <c r="F59" s="6" t="n"/>
       <c r="G59" s="5" t="inlineStr">
         <is>
           <t>量</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
-        <v>0.513</v>
+        <v>0.507</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>1525</v>
+        <v>1511</v>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
@@ -13452,7 +13471,7 @@
       </c>
       <c r="L59" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_pause.webp</t>
+          <t>resources/si/renna_si_pointmap.webp</t>
         </is>
       </c>
     </row>
@@ -13464,12 +13483,12 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>renna_si_pointmap.webp</t>
+          <t>renna_si_reach.webp</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>pointmap</t>
+          <t>reach</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -13484,13 +13503,13 @@
         </is>
       </c>
       <c r="H60" s="5" t="n">
-        <v>0.507</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>1511</v>
+        <v>1528</v>
       </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
@@ -13499,7 +13518,7 @@
       </c>
       <c r="L60" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_pointmap.webp</t>
+          <t>resources/si/renna_si_reach.webp</t>
         </is>
       </c>
     </row>
@@ -13511,12 +13530,12 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>renna_si_reach.webp</t>
+          <t>renna_si_reachcry.webp</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>reach</t>
+          <t>reachcry</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -13531,13 +13550,13 @@
         </is>
       </c>
       <c r="H61" s="5" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.608</v>
       </c>
       <c r="I61" s="5" t="n">
         <v>2</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>1528</v>
+        <v>1533</v>
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
@@ -13546,7 +13565,7 @@
       </c>
       <c r="L61" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_reach.webp</t>
+          <t>resources/si/renna_si_reachcry.webp</t>
         </is>
       </c>
     </row>
@@ -13558,12 +13577,12 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>renna_si_reachcry.webp</t>
+          <t>renna_si_relief.webp</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>reachcry</t>
+          <t>relief</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -13571,20 +13590,24 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F62" s="6" t="n"/>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>1 張：renna_newhair/</t>
+        </is>
+      </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
           <t>量</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
-        <v>0.608</v>
+        <v>0.518</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>1533</v>
+        <v>1525</v>
       </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
@@ -13593,7 +13616,7 @@
       </c>
       <c r="L62" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_reachcry.webp</t>
+          <t>resources/si/renna_si_relief.webp</t>
         </is>
       </c>
     </row>
@@ -13605,12 +13628,12 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>renna_si_relief.webp</t>
+          <t>renna_si_run.webp</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>relief</t>
+          <t>run</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -13618,24 +13641,20 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F63" s="6" t="inlineStr">
-        <is>
-          <t>1 張：renna_newhair/</t>
-        </is>
-      </c>
+      <c r="F63" s="6" t="n"/>
       <c r="G63" s="5" t="inlineStr">
         <is>
           <t>量</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
-        <v>0.518</v>
+        <v>0.611</v>
       </c>
       <c r="I63" s="5" t="n">
         <v>3</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>1525</v>
+        <v>1532</v>
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
@@ -13644,7 +13663,7 @@
       </c>
       <c r="L63" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_relief.webp</t>
+          <t>resources/si/renna_si_run.webp</t>
         </is>
       </c>
     </row>
@@ -13656,12 +13675,12 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>renna_si_run.webp</t>
+          <t>renna_si_sad.webp</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>run</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -13669,20 +13688,24 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F64" s="6" t="n"/>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>1 張：renna_newhair/</t>
+        </is>
+      </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
           <t>量</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
-        <v>0.611</v>
+        <v>0.52</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>1532</v>
+        <v>1517</v>
       </c>
       <c r="K64" s="5" t="inlineStr">
         <is>
@@ -13691,7 +13714,7 @@
       </c>
       <c r="L64" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_run.webp</t>
+          <t>resources/si/renna_si_sad.webp</t>
         </is>
       </c>
     </row>
@@ -13703,12 +13726,12 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>renna_si_sad.webp</t>
+          <t>renna_si_salute.webp</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>sad</t>
+          <t>salute</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -13716,24 +13739,20 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F65" s="6" t="inlineStr">
-        <is>
-          <t>1 張：renna_newhair/</t>
-        </is>
-      </c>
+      <c r="F65" s="6" t="n"/>
       <c r="G65" s="5" t="inlineStr">
         <is>
           <t>量</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
-        <v>0.52</v>
+        <v>0.486</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>1517</v>
+        <v>1495</v>
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
@@ -13742,7 +13761,7 @@
       </c>
       <c r="L65" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_sad.webp</t>
+          <t>resources/si/renna_si_salute.webp</t>
         </is>
       </c>
     </row>
@@ -13754,12 +13773,12 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>renna_si_salute.webp</t>
+          <t>renna_si_scare.webp</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>salute</t>
+          <t>scare</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -13774,13 +13793,13 @@
         </is>
       </c>
       <c r="H66" s="5" t="n">
-        <v>0.486</v>
+        <v>0.498</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>1495</v>
+        <v>1528</v>
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
@@ -13789,7 +13808,7 @@
       </c>
       <c r="L66" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_salute.webp</t>
+          <t>resources/si/renna_si_scare.webp</t>
         </is>
       </c>
     </row>
@@ -13801,12 +13820,12 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>renna_si_scare.webp</t>
+          <t>renna_si_scarecute.webp</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>scare</t>
+          <t>cutescare</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -13821,13 +13840,13 @@
         </is>
       </c>
       <c r="H67" s="5" t="n">
-        <v>0.498</v>
+        <v>0.537</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
@@ -13836,7 +13855,7 @@
       </c>
       <c r="L67" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_scare.webp</t>
+          <t>resources/si/renna_si_scarecute.webp</t>
         </is>
       </c>
     </row>
@@ -13848,12 +13867,12 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>renna_si_scarecute.webp</t>
+          <t>renna_si_scarejump.webp</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>cutescare</t>
+          <t>scarejump</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -13868,13 +13887,13 @@
         </is>
       </c>
       <c r="H68" s="5" t="n">
-        <v>0.537</v>
+        <v>0.632</v>
       </c>
       <c r="I68" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>1530</v>
+        <v>1533</v>
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
@@ -13883,7 +13902,7 @@
       </c>
       <c r="L68" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_scarecute.webp</t>
+          <t>resources/si/renna_si_scarejump.webp</t>
         </is>
       </c>
     </row>
@@ -13895,12 +13914,12 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>renna_si_scarejump.webp</t>
+          <t>renna_si_scream.webp</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>scarejump</t>
+          <t>scream</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -13915,13 +13934,13 @@
         </is>
       </c>
       <c r="H69" s="5" t="n">
-        <v>0.632</v>
+        <v>0.644</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>1533</v>
+        <v>1535</v>
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
@@ -13930,7 +13949,7 @@
       </c>
       <c r="L69" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_scarejump.webp</t>
+          <t>resources/si/renna_si_scream.webp</t>
         </is>
       </c>
     </row>
@@ -13942,12 +13961,12 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>renna_si_scream.webp</t>
+          <t>renna_si_shock.webp</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>scream</t>
+          <t>shock</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -13962,13 +13981,13 @@
         </is>
       </c>
       <c r="H70" s="5" t="n">
-        <v>0.644</v>
+        <v>0.492</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>1535</v>
+        <v>1530</v>
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
@@ -13977,7 +13996,7 @@
       </c>
       <c r="L70" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_scream.webp</t>
+          <t>resources/si/renna_si_shock.webp</t>
         </is>
       </c>
     </row>
@@ -13989,12 +14008,12 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>renna_si_shock.webp</t>
+          <t>renna_si_shockcalm.webp</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>shock</t>
+          <t>shockcalm</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -14009,13 +14028,13 @@
         </is>
       </c>
       <c r="H71" s="5" t="n">
-        <v>0.492</v>
+        <v>0.493</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>1530</v>
+        <v>1516</v>
       </c>
       <c r="K71" s="5" t="inlineStr">
         <is>
@@ -14024,7 +14043,7 @@
       </c>
       <c r="L71" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_shock.webp</t>
+          <t>resources/si/renna_si_shockcalm.webp</t>
         </is>
       </c>
     </row>
@@ -14036,12 +14055,12 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>renna_si_shockcalm.webp</t>
+          <t>renna_si_shockopen.webp</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>shockcalm</t>
+          <t>shockopen</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -14056,13 +14075,13 @@
         </is>
       </c>
       <c r="H72" s="5" t="n">
-        <v>0.493</v>
+        <v>0.5</v>
       </c>
       <c r="I72" s="5" t="n">
         <v>4</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>1516</v>
+        <v>1519</v>
       </c>
       <c r="K72" s="5" t="inlineStr">
         <is>
@@ -14071,7 +14090,7 @@
       </c>
       <c r="L72" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_shockcalm.webp</t>
+          <t>resources/si/renna_si_shockopen.webp</t>
         </is>
       </c>
     </row>
@@ -14083,12 +14102,12 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>renna_si_shockopen.webp</t>
+          <t>renna_si_shout.webp</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>shockopen</t>
+          <t>shout</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -14096,20 +14115,24 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F73" s="6" t="n"/>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>1 張：renna_newhair/</t>
+        </is>
+      </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
           <t>量</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
-        <v>0.5</v>
+        <v>0.549</v>
       </c>
       <c r="I73" s="5" t="n">
         <v>4</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>1519</v>
+        <v>1534</v>
       </c>
       <c r="K73" s="5" t="inlineStr">
         <is>
@@ -14118,7 +14141,7 @@
       </c>
       <c r="L73" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_shockopen.webp</t>
+          <t>resources/si/renna_si_shout.webp</t>
         </is>
       </c>
     </row>
@@ -14130,12 +14153,12 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>renna_si_shout.webp</t>
+          <t>renna_si_side.webp</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>shout</t>
+          <t>side</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -14143,24 +14166,20 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F74" s="6" t="inlineStr">
-        <is>
-          <t>1 張：renna_newhair/</t>
-        </is>
-      </c>
+      <c r="F74" s="6" t="n"/>
       <c r="G74" s="5" t="inlineStr">
         <is>
           <t>量</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
-        <v>0.549</v>
+        <v>0.503</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>1534</v>
+        <v>1502</v>
       </c>
       <c r="K74" s="5" t="inlineStr">
         <is>
@@ -14169,7 +14188,7 @@
       </c>
       <c r="L74" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_shout.webp</t>
+          <t>resources/si/renna_si_side.webp</t>
         </is>
       </c>
     </row>
@@ -14181,12 +14200,12 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>renna_si_side.webp</t>
+          <t>renna_si_sigh.webp</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>side</t>
+          <t>sigh</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -14201,13 +14220,13 @@
         </is>
       </c>
       <c r="H75" s="5" t="n">
-        <v>0.503</v>
+        <v>0.522</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>1502</v>
+        <v>1531</v>
       </c>
       <c r="K75" s="5" t="inlineStr">
         <is>
@@ -14216,7 +14235,7 @@
       </c>
       <c r="L75" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_side.webp</t>
+          <t>resources/si/renna_si_sigh.webp</t>
         </is>
       </c>
     </row>
@@ -14228,12 +14247,12 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>renna_si_sigh.webp</t>
+          <t>renna_si_sighsweat.webp</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>sigh</t>
+          <t>sighsweat</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -14248,13 +14267,13 @@
         </is>
       </c>
       <c r="H76" s="5" t="n">
-        <v>0.522</v>
+        <v>0.536</v>
       </c>
       <c r="I76" s="5" t="n">
         <v>2</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>1531</v>
+        <v>1525</v>
       </c>
       <c r="K76" s="5" t="inlineStr">
         <is>
@@ -14263,7 +14282,7 @@
       </c>
       <c r="L76" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_sigh.webp</t>
+          <t>resources/si/renna_si_sighsweat.webp</t>
         </is>
       </c>
     </row>
@@ -14275,12 +14294,12 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>renna_si_sighsweat.webp</t>
+          <t>renna_si_sipdrink.webp</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>sighsweat</t>
+          <t>sipdrink</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -14295,13 +14314,13 @@
         </is>
       </c>
       <c r="H77" s="5" t="n">
-        <v>0.536</v>
+        <v>0.492</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>1525</v>
+        <v>1513</v>
       </c>
       <c r="K77" s="5" t="inlineStr">
         <is>
@@ -14310,7 +14329,7 @@
       </c>
       <c r="L77" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_sighsweat.webp</t>
+          <t>resources/si/renna_si_sipdrink.webp</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14341,12 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>renna_si_sipdrink.webp</t>
+          <t>renna_si_sleepdesk.webp</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>sipdrink</t>
+          <t>sleepdesk</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -14342,13 +14361,13 @@
         </is>
       </c>
       <c r="H78" s="5" t="n">
-        <v>0.492</v>
+        <v>0.595</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>4</v>
+        <v>436</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>1513</v>
+        <v>1098</v>
       </c>
       <c r="K78" s="5" t="inlineStr">
         <is>
@@ -14357,7 +14376,7 @@
       </c>
       <c r="L78" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_sipdrink.webp</t>
+          <t>resources/si/renna_si_sleepdesk.webp</t>
         </is>
       </c>
     </row>
@@ -14369,12 +14388,12 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>renna_si_sleepdesk.webp</t>
+          <t>renna_si_smile.webp</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>sleepdesk</t>
+          <t>smile</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -14382,20 +14401,24 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F79" s="6" t="n"/>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>1 張：renna_newhair/</t>
+        </is>
+      </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
           <t>量</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
-        <v>0.595</v>
+        <v>0.518</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>436</v>
+        <v>5</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>1098</v>
+        <v>1529</v>
       </c>
       <c r="K79" s="5" t="inlineStr">
         <is>
@@ -14404,7 +14427,7 @@
       </c>
       <c r="L79" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_sleepdesk.webp</t>
+          <t>resources/si/renna_si_smile.webp</t>
         </is>
       </c>
     </row>
@@ -14416,12 +14439,12 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>renna_si_smile.webp</t>
+          <t>renna_si_smilesoft.webp</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>smile</t>
+          <t>smilesoft</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -14429,24 +14452,20 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F80" s="6" t="inlineStr">
-        <is>
-          <t>1 張：renna_newhair/</t>
-        </is>
-      </c>
+      <c r="F80" s="6" t="n"/>
       <c r="G80" s="5" t="inlineStr">
         <is>
           <t>量</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
-        <v>0.518</v>
+        <v>0.503</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>1529</v>
+        <v>1520</v>
       </c>
       <c r="K80" s="5" t="inlineStr">
         <is>
@@ -14455,7 +14474,7 @@
       </c>
       <c r="L80" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_smile.webp</t>
+          <t>resources/si/renna_si_smilesoft.webp</t>
         </is>
       </c>
     </row>
@@ -14467,12 +14486,12 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>renna_si_smilesoft.webp</t>
+          <t>renna_si_snivel.webp</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>smilesoft</t>
+          <t>snivel</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -14487,13 +14506,13 @@
         </is>
       </c>
       <c r="H81" s="5" t="n">
-        <v>0.503</v>
+        <v>0.534</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>1520</v>
+        <v>1525</v>
       </c>
       <c r="K81" s="5" t="inlineStr">
         <is>
@@ -14502,7 +14521,7 @@
       </c>
       <c r="L81" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_smilesoft.webp</t>
+          <t>resources/si/renna_si_snivel.webp</t>
         </is>
       </c>
     </row>
@@ -14514,12 +14533,12 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>renna_si_snivel.webp</t>
+          <t>renna_si_stare.webp</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>snivel</t>
+          <t>stare</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -14527,20 +14546,24 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F82" s="6" t="n"/>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>1 張：renna_newhair/</t>
+        </is>
+      </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
           <t>量</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
-        <v>0.534</v>
+        <v>0.515</v>
       </c>
       <c r="I82" s="5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>1525</v>
+        <v>1527</v>
       </c>
       <c r="K82" s="5" t="inlineStr">
         <is>
@@ -14549,7 +14572,7 @@
       </c>
       <c r="L82" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_snivel.webp</t>
+          <t>resources/si/renna_si_stare.webp</t>
         </is>
       </c>
     </row>
@@ -14561,12 +14584,12 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>renna_si_stare.webp</t>
+          <t>renna_si_surprise.webp</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>stare</t>
+          <t>surprise</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -14585,13 +14608,13 @@
         </is>
       </c>
       <c r="H83" s="5" t="n">
-        <v>0.515</v>
+        <v>0.498</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J83" s="5" t="n">
-        <v>1527</v>
+        <v>1524</v>
       </c>
       <c r="K83" s="5" t="inlineStr">
         <is>
@@ -14600,7 +14623,7 @@
       </c>
       <c r="L83" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_stare.webp</t>
+          <t>resources/si/renna_si_surprise.webp</t>
         </is>
       </c>
     </row>
@@ -14612,12 +14635,12 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>renna_si_surprise.webp</t>
+          <t>renna_si_surprised.webp</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>surprise</t>
+          <t>surprised</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -14625,24 +14648,20 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F84" s="6" t="inlineStr">
-        <is>
-          <t>1 張：renna_newhair/</t>
-        </is>
-      </c>
+      <c r="F84" s="6" t="n"/>
       <c r="G84" s="5" t="inlineStr">
         <is>
           <t>量</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
-        <v>0.498</v>
+        <v>0.502</v>
       </c>
       <c r="I84" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J84" s="5" t="n">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="K84" s="5" t="inlineStr">
         <is>
@@ -14651,7 +14670,7 @@
       </c>
       <c r="L84" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_surprise.webp</t>
+          <t>resources/si/renna_si_surprised.webp</t>
         </is>
       </c>
     </row>
@@ -14663,12 +14682,12 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>renna_si_surprised.webp</t>
+          <t>renna_si_talkserious.webp</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>surprised</t>
+          <t>talkserious</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -14676,20 +14695,24 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F85" s="6" t="n"/>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>1 張：renna_newhair/</t>
+        </is>
+      </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
           <t>量</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
-        <v>0.502</v>
+        <v>0.509</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J85" s="5" t="n">
-        <v>1522</v>
+        <v>1516</v>
       </c>
       <c r="K85" s="5" t="inlineStr">
         <is>
@@ -14698,7 +14721,7 @@
       </c>
       <c r="L85" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_surprised.webp</t>
+          <t>resources/si/renna_si_talkserious.webp</t>
         </is>
       </c>
     </row>
@@ -14710,12 +14733,12 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>renna_si_talkserious.webp</t>
+          <t>renna_si_talkwork.webp</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>talkserious</t>
+          <t>talkwork</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -14740,7 +14763,7 @@
         <v>3</v>
       </c>
       <c r="J86" s="5" t="n">
-        <v>1516</v>
+        <v>1519</v>
       </c>
       <c r="K86" s="5" t="inlineStr">
         <is>
@@ -14749,7 +14772,7 @@
       </c>
       <c r="L86" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_talkserious.webp</t>
+          <t>resources/si/renna_si_talkwork.webp</t>
         </is>
       </c>
     </row>
@@ -14761,12 +14784,12 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>renna_si_talkwork.webp</t>
+          <t>renna_si_think.webp</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>talkwork</t>
+          <t>think</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -14785,13 +14808,13 @@
         </is>
       </c>
       <c r="H87" s="5" t="n">
-        <v>0.509</v>
+        <v>0.515</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J87" s="5" t="n">
-        <v>1519</v>
+        <v>1530</v>
       </c>
       <c r="K87" s="5" t="inlineStr">
         <is>
@@ -14800,7 +14823,7 @@
       </c>
       <c r="L87" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_talkwork.webp</t>
+          <t>resources/si/renna_si_think.webp</t>
         </is>
       </c>
     </row>
@@ -14812,12 +14835,12 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>renna_si_think.webp</t>
+          <t>renna_si_tire.webp</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>think</t>
+          <t>tire</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -14836,13 +14859,13 @@
         </is>
       </c>
       <c r="H88" s="5" t="n">
-        <v>0.515</v>
+        <v>0.495</v>
       </c>
       <c r="I88" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J88" s="5" t="n">
-        <v>1530</v>
+        <v>1522</v>
       </c>
       <c r="K88" s="5" t="inlineStr">
         <is>
@@ -14851,7 +14874,7 @@
       </c>
       <c r="L88" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_think.webp</t>
+          <t>resources/si/renna_si_tire.webp</t>
         </is>
       </c>
     </row>
@@ -14863,12 +14886,12 @@
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>renna_si_tire.webp</t>
+          <t>renna_si_unbraid.webp</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>tire</t>
+          <t>unbraid</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -14876,24 +14899,20 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F89" s="6" t="inlineStr">
-        <is>
-          <t>1 張：renna_newhair/</t>
-        </is>
-      </c>
+      <c r="F89" s="6" t="n"/>
       <c r="G89" s="5" t="inlineStr">
         <is>
           <t>量</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
-        <v>0.495</v>
+        <v>0.55</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J89" s="5" t="n">
-        <v>1522</v>
+        <v>1528</v>
       </c>
       <c r="K89" s="5" t="inlineStr">
         <is>
@@ -14902,7 +14921,7 @@
       </c>
       <c r="L89" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_tire.webp</t>
+          <t>resources/si/renna_si_unbraid.webp</t>
         </is>
       </c>
     </row>
@@ -14914,12 +14933,12 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>renna_si_unbraid.webp</t>
+          <t>renna_si_upset.webp</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>unbraid</t>
+          <t>upset</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -14927,20 +14946,24 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F90" s="6" t="n"/>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>1 張：renna_newhair/</t>
+        </is>
+      </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
           <t>量</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
-        <v>0.55</v>
+        <v>0.507</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J90" s="5" t="n">
-        <v>1528</v>
+        <v>1524</v>
       </c>
       <c r="K90" s="5" t="inlineStr">
         <is>
@@ -14949,7 +14972,7 @@
       </c>
       <c r="L90" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_unbraid.webp</t>
+          <t>resources/si/renna_si_upset.webp</t>
         </is>
       </c>
     </row>
@@ -14961,12 +14984,12 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>renna_si_upset.webp</t>
+          <t>renna_si_upsetstare.webp</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>upset</t>
+          <t>upsetstare</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -14985,10 +15008,10 @@
         </is>
       </c>
       <c r="H91" s="5" t="n">
-        <v>0.507</v>
+        <v>0.503</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J91" s="5" t="n">
         <v>1524</v>
@@ -15000,7 +15023,7 @@
       </c>
       <c r="L91" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_upset.webp</t>
+          <t>resources/si/renna_si_upsetstare.webp</t>
         </is>
       </c>
     </row>
@@ -15012,12 +15035,12 @@
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>renna_si_upsetstare.webp</t>
+          <t>renna_si_wake.webp</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>upsetstare</t>
+          <t>wake</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -15036,13 +15059,13 @@
         </is>
       </c>
       <c r="H92" s="5" t="n">
-        <v>0.503</v>
+        <v>0.539</v>
       </c>
       <c r="I92" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J92" s="5" t="n">
-        <v>1524</v>
+        <v>1531</v>
       </c>
       <c r="K92" s="5" t="inlineStr">
         <is>
@@ -15051,7 +15074,7 @@
       </c>
       <c r="L92" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_upsetstare.webp</t>
+          <t>resources/si/renna_si_wake.webp</t>
         </is>
       </c>
     </row>
@@ -15063,12 +15086,12 @@
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>renna_si_wake.webp</t>
+          <t>renna_si_watch.webp</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>wake</t>
+          <t>watch</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -15087,13 +15110,13 @@
         </is>
       </c>
       <c r="H93" s="5" t="n">
-        <v>0.539</v>
+        <v>0.492</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J93" s="5" t="n">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="K93" s="5" t="inlineStr">
         <is>
@@ -15102,7 +15125,7 @@
       </c>
       <c r="L93" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_wake.webp</t>
+          <t>resources/si/renna_si_watch.webp</t>
         </is>
       </c>
     </row>
@@ -15114,12 +15137,12 @@
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>renna_si_watch.webp</t>
+          <t>renna_si_whisper.webp</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>watch</t>
+          <t>whisper</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -15127,24 +15150,20 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F94" s="6" t="inlineStr">
-        <is>
-          <t>1 張：renna_newhair/</t>
-        </is>
-      </c>
+      <c r="F94" s="6" t="n"/>
       <c r="G94" s="5" t="inlineStr">
         <is>
           <t>量</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
-        <v>0.492</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="I94" s="5" t="n">
         <v>7</v>
       </c>
       <c r="J94" s="5" t="n">
-        <v>1530</v>
+        <v>1519</v>
       </c>
       <c r="K94" s="5" t="inlineStr">
         <is>
@@ -15153,7 +15172,7 @@
       </c>
       <c r="L94" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_watch.webp</t>
+          <t>resources/si/renna_si_whisper.webp</t>
         </is>
       </c>
     </row>
@@ -15165,12 +15184,12 @@
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>renna_si_whisper.webp</t>
+          <t>renna_si_worry.webp</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>whisper</t>
+          <t>worry</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -15178,20 +15197,24 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F95" s="6" t="n"/>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>1 張：renna_newhair/</t>
+        </is>
+      </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
           <t>量</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J95" s="5" t="n">
-        <v>1519</v>
+        <v>1527</v>
       </c>
       <c r="K95" s="5" t="inlineStr">
         <is>
@@ -15200,7 +15223,7 @@
       </c>
       <c r="L95" s="6" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_whisper.webp</t>
+          <t>resources/si/renna_si_worry.webp</t>
         </is>
       </c>
     </row>
@@ -15212,12 +15235,12 @@
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>renna_si_worry.webp</t>
+          <t>renna_si_write.webp</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>worry</t>
+          <t>write</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -15236,13 +15259,13 @@
         </is>
       </c>
       <c r="H96" s="5" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.507</v>
       </c>
       <c r="I96" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J96" s="5" t="n">
-        <v>1527</v>
+        <v>1524</v>
       </c>
       <c r="K96" s="5" t="inlineStr">
         <is>
@@ -15250,57 +15273,6 @@
         </is>
       </c>
       <c r="L96" s="6" t="inlineStr">
-        <is>
-          <t>resources/si/renna_si_worry.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="111" customHeight="1">
-      <c r="A97" s="5" t="inlineStr">
-        <is>
-          <t>蕾娜</t>
-        </is>
-      </c>
-      <c r="C97" s="6" t="inlineStr">
-        <is>
-          <t>renna_si_write.webp</t>
-        </is>
-      </c>
-      <c r="D97" s="5" t="inlineStr">
-        <is>
-          <t>write</t>
-        </is>
-      </c>
-      <c r="E97" s="5" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F97" s="6" t="inlineStr">
-        <is>
-          <t>1 張：renna_newhair/</t>
-        </is>
-      </c>
-      <c r="G97" s="5" t="inlineStr">
-        <is>
-          <t>量</t>
-        </is>
-      </c>
-      <c r="H97" s="5" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="I97" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="J97" s="5" t="n">
-        <v>1524</v>
-      </c>
-      <c r="K97" s="5" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L97" s="6" t="inlineStr">
         <is>
           <t>resources/si/renna_si_write.webp</t>
         </is>
@@ -16480,17 +16452,17 @@
     <row r="2" ht="111" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>索菈娜</t>
+          <t>隨從</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>soranaanya_si_backcarry.webp</t>
+          <t>retainer_si_front.webp</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>backcarry</t>
+          <t>(base)</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -16505,10 +16477,10 @@
         </is>
       </c>
       <c r="H2" s="5" t="n">
-        <v>0.82</v>
+        <v>0.451</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J2" s="5" t="n">
         <v>1534</v>
@@ -16520,7 +16492,7 @@
       </c>
       <c r="L2" s="6" t="inlineStr">
         <is>
-          <t>resources/si/soranaanya_si_backcarry.webp</t>
+          <t>resources/si/retainer_si_front.webp</t>
         </is>
       </c>
     </row>
@@ -16531,6 +16503,144 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="42" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>角色</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>縮圖（抓臉）</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>檔名</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>差分鍵</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>已接線</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>另有版本</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>取景</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>fx</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>bot</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>尺寸</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>路徑</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="111" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>索菈娜</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>soranaanya_si_backcarry.webp</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>backcarry</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="n"/>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>1534</v>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L2" s="6" t="inlineStr">
+        <is>
+          <t>resources/si/soranaanya_si_backcarry.webp</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18268,13 +18378,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D94"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -18340,7 +18450,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>anya_si_happy.webp</t>
+          <t>anya_si_peace.webp</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -18362,7 +18472,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>anya_si_peace.webp</t>
+          <t>anya_si_side.webp</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -18379,12 +18489,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Anya</t>
+          <t>Gen_renna</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>anya_si_side.webp</t>
+          <t>gen_renna_si_blush.webp</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -18401,12 +18511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Anya</t>
+          <t>Luna</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>anya_si_smile.webp</t>
+          <t>luna_si_front.webp</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -18423,12 +18533,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gen_renna</t>
+          <t>Luna</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>gen_renna_si_blush.webp</t>
+          <t>luna_si_seat_lookdown.webp</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -18445,12 +18555,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Luna</t>
+          <t>Nouvelle_nun</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>luna_si_front.webp</t>
+          <t>nouvelle_nun_si_front.webp</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -18467,12 +18577,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Luna</t>
+          <t>Nouvelle</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>luna_si_seat_lookdown.webp</t>
+          <t>nouvelle_si_back.webp</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -18489,12 +18599,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nouvelle_nun</t>
+          <t>Nouvelle</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nouvelle_nun_si_front.webp</t>
+          <t>nouvelle_si_bye.webp</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -18516,7 +18626,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nouvelle_si_back.webp</t>
+          <t>nouvelle_si_expainsweat.webp</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -18538,7 +18648,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nouvelle_si_bye.webp</t>
+          <t>nouvelle_si_meetagain.webp</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -18560,7 +18670,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>nouvelle_si_expainsweat.webp</t>
+          <t>nouvelle_si_reliefbreath.webp</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -18582,7 +18692,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>nouvelle_si_meetagain.webp</t>
+          <t>nouvelle_si_scare.webp</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -18604,7 +18714,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>nouvelle_si_reliefbreath.webp</t>
+          <t>nouvelle_si_side.webp</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -18621,12 +18731,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nouvelle</t>
+          <t>f66a41f1-462b-4167-ab1e-4d235f012a0e</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>nouvelle_si_scare.webp</t>
+          <t>f66a41f1-462b-4167-ab1e-4d235f012a0e.png</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -18643,12 +18753,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nouvelle</t>
+          <t>f734e7ba-e7bb-457b-8cf7-66e13324c45d</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>nouvelle_si_side.webp</t>
+          <t>f734e7ba-e7bb-457b-8cf7-66e13324c45d.png</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -18665,12 +18775,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>f66a41f1-462b-4167-ab1e-4d235f012a0e</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>f66a41f1-462b-4167-ab1e-4d235f012a0e.png</t>
+          <t>renna_si_evalutatingclosemouth.webp</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -18687,12 +18797,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>f734e7ba-e7bb-457b-8cf7-66e13324c45d</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>f734e7ba-e7bb-457b-8cf7-66e13324c45d.png</t>
+          <t>renna_si_annoy.webp</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -18709,12 +18819,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Renna</t>
+          <t>Sorana</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>renna_si_evalutatingclosemouth.webp</t>
+          <t>sorana_si_q.webp</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -18731,12 +18841,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Renna</t>
+          <t>image - 2026-09-20T150615.066</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>renna_si_annoy.webp</t>
+          <t>image - 2026-09-20T150615.066.png</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -18753,12 +18863,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sorana</t>
+          <t>image - 2026-09-20T150842.343</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>sorana_si_furious.webp</t>
+          <t>image - 2026-09-20T150842.343.png</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -18775,12 +18885,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sorana</t>
+          <t>image - 2026-09-20T151013.881</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>sorana_si_q.webp</t>
+          <t>image - 2026-09-20T151013.881.png</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -18797,12 +18907,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T150615.066</t>
+          <t>image - 2026-09-20T151141.942</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T150615.066.png</t>
+          <t>image - 2026-09-20T151141.942.png</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -18819,12 +18929,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T150842.343</t>
+          <t>Torsten</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T150842.343.png</t>
+          <t>torsten_si_front.webp</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -18841,12 +18951,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T151013.881</t>
+          <t>Torsten</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T151013.881.png</t>
+          <t>torsten_si_q.webp</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -18863,12 +18973,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T151141.942</t>
+          <t>Xanya</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T151141.942.png</t>
+          <t>xanya_si_front.webp</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -18880,110 +18990,110 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>美術交了沒接線</t>
+          <t>指到但檔案不在</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Torsten</t>
+          <t>renna / hugangry2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>torsten_si_front.webp</t>
+          <t>resources/si/renna_si_hugangry2.png</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>在 script/speakers.js 的 ART 補一筆 expr，並量 fx／top／bot（§6.5）</t>
+          <t>路徑打錯，或美術還沒交 —— 演到那一句會回退基本立繪</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>美術交了沒接線</t>
+          <t>同差分的另一個版本</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Torsten</t>
+          <t>Npc_grocer</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>torsten_si_q.webp</t>
+          <t>resources/si/npc/npc_grocer_si_v2.webp</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>在 script/speakers.js 的 ART 補一筆 expr，並量 fx／top／bot（§6.5）</t>
+          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>美術交了沒接線</t>
+          <t>同差分的另一個版本</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Xanya</t>
+          <t>Npc_grocer</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>xanya_si_front.webp</t>
+          <t>resources/si/npc/npc_grocer_si_v3.webp</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>在 script/speakers.js 的 ART 補一筆 expr，並量 fx／top／bot（§6.5）</t>
+          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>指到但檔案不在</t>
+          <t>同差分的另一個版本</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>sorana / excite</t>
+          <t>Npc_grocer</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_excite.webp</t>
+          <t>resources/si/npc/npc_grocer_si_v4.webp</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>路徑打錯，或美術還沒交 —— 演到那一句會回退基本立繪</t>
+          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>指到但檔案不在</t>
+          <t>同差分的另一個版本</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>sorana / furiouscute</t>
+          <t>Npc_grocer</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_furiouscute.webp</t>
+          <t>resources/si/npc/npc_grocer_si_v5.webp</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>路徑打錯，或美術還沒交 —— 演到那一句會回退基本立繪</t>
+          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -18995,17 +19105,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Anya</t>
+          <t>Npc_guildcounter</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>resources/si/anya_si_nod.png</t>
+          <t>resources/si/npc/npc_guildcounter_si_v1.webp</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>線上跑的是 anya_si_nod.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_guildcounter_si_v5.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19017,17 +19127,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Npc_grocer</t>
+          <t>Npc_guildcounter</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_grocer_si_v2.webp</t>
+          <t>resources/si/npc/npc_guildcounter_si_v3.webp</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_guildcounter_si_v5.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19039,17 +19149,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Npc_grocer</t>
+          <t>Npc_guildcounter</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_grocer_si_v3.webp</t>
+          <t>resources/si/npc/npc_guildcounter_si_v4.webp</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_guildcounter_si_v5.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19061,17 +19171,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Npc_grocer</t>
+          <t>Npc_gunsmith</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_grocer_si_v4.webp</t>
+          <t>resources/si/npc/npc_gunsmith_si_v2.webp</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19083,17 +19193,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Npc_grocer</t>
+          <t>Npc_gunsmith</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_grocer_si_v5.webp</t>
+          <t>resources/si/npc/npc_gunsmith_si_v3.webp</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19105,17 +19215,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Npc_guildcounter</t>
+          <t>Npc_gunsmith</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_guildcounter_si_v1.webp</t>
+          <t>resources/si/npc/npc_gunsmith_si_v4.webp</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_guildcounter_si_v5.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19127,17 +19237,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Npc_guildcounter</t>
+          <t>Npc_gunsmith</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_guildcounter_si_v3.webp</t>
+          <t>resources/si/npc/npc_gunsmith_si_v5.webp</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_guildcounter_si_v5.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19149,17 +19259,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Npc_guildcounter</t>
+          <t>Cecilie</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_guildcounter_si_v4.webp</t>
+          <t>resources/si/old/cecilie_si_front.png</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_guildcounter_si_v5.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_front.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19171,17 +19281,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Npc_gunsmith</t>
+          <t>Cecilie</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_gunsmith_si_v2.webp</t>
+          <t>resources/si/old/cecilie_si_lookaside.png</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_lookaside.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19193,17 +19303,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Npc_gunsmith</t>
+          <t>Cecilie</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_gunsmith_si_v3.webp</t>
+          <t>resources/si/old/cecilie_si_sadback.png</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_sadback.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19215,17 +19325,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Npc_gunsmith</t>
+          <t>Cecilie</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_gunsmith_si_v4.webp</t>
+          <t>resources/si/old/cecilie_si_smile.png</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_smile.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19237,17 +19347,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Npc_gunsmith</t>
+          <t>Cecilie</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_gunsmith_si_v5.webp</t>
+          <t>resources/si/old/cecilie_si_tease.png</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_tease.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19264,12 +19374,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_front.png</t>
+          <t>resources/si/old/cecilie_si_upset.png</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_front.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_upset.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19281,17 +19391,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_lookaside.png</t>
+          <t>resources/si/renna_newhair/renna_si_argue.webp</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_lookaside.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_argue.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19303,17 +19413,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_sadback.png</t>
+          <t>resources/si/renna_newhair/renna_si_arguecute.webp</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_sadback.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_arguecute.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19325,17 +19435,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_smile.png</t>
+          <t>resources/si/renna_newhair/renna_si_ask.webp</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_smile.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_ask.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19347,17 +19457,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_tease.png</t>
+          <t>resources/si/renna_newhair/renna_si_askserious.webp</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_tease.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_askserious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19369,17 +19479,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_upset.png</t>
+          <t>resources/si/renna_newhair/renna_si_awkwerd.webp</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_upset.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_awkwerd.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19396,12 +19506,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_argue.webp</t>
+          <t>resources/si/renna_newhair/renna_si_blush.webp</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_argue.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_blush.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19418,12 +19528,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_arguecute.webp</t>
+          <t>resources/si/renna_newhair/renna_si_bow.webp</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_arguecute.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_bow.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19440,12 +19550,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_ask.webp</t>
+          <t>resources/si/renna_newhair/renna_si_callangry.webp</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_ask.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_callangry.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19462,12 +19572,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_askserious.webp</t>
+          <t>resources/si/renna_newhair/renna_si_chase.webp</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_askserious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_chase.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19484,12 +19594,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_awkwerd.webp</t>
+          <t>resources/si/renna_newhair/renna_si_chase2.webp</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_awkwerd.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_chase2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19506,12 +19616,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_blush.webp</t>
+          <t>resources/si/renna_newhair/renna_si_command.webp</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_blush.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_command.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19528,12 +19638,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_bow.webp</t>
+          <t>resources/si/renna_newhair/renna_si_covermouth.webp</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_bow.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_covermouth.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19550,12 +19660,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_callangry.webp</t>
+          <t>resources/si/renna_newhair/renna_si_cringe.webp</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_callangry.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_cringe.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19572,12 +19682,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_chase.webp</t>
+          <t>resources/si/renna_newhair/renna_si_curious.webp</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_chase.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_curious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19594,12 +19704,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_chase2.webp</t>
+          <t>resources/si/renna_newhair/renna_si_die.webp</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_chase2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_die.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19616,12 +19726,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_command.webp</t>
+          <t>resources/si/renna_newhair/renna_si_evaluate.webp</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_command.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_evaluate.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19638,12 +19748,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_covermouth.webp</t>
+          <t>resources/si/renna_newhair/renna_si_front.webp</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_covermouth.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_front.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19660,12 +19770,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_cringe.webp</t>
+          <t>resources/si/renna_newhair/renna_si_intense.webp</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_cringe.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_intense.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19682,12 +19792,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_curious.webp</t>
+          <t>resources/si/renna_newhair/renna_si_intense2.webp</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_curious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_intense2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19704,12 +19814,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_die.webp</t>
+          <t>resources/si/renna_newhair/renna_si_invite.webp</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_die.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_invite.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19726,12 +19836,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_evaluate.webp</t>
+          <t>resources/si/renna_newhair/renna_si_lookaway.webp</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_evaluate.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_lookaway.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19748,12 +19858,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_front.webp</t>
+          <t>resources/si/renna_newhair/renna_si_lookawaytalk.webp</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_front.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_lookawaytalk.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19770,12 +19880,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_intense.webp</t>
+          <t>resources/si/renna_newhair/renna_si_lookdown.webp</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_intense.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_lookdown.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19792,12 +19902,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_intense2.webp</t>
+          <t>resources/si/renna_newhair/renna_si_lookup.webp</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_intense2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_lookup.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19814,12 +19924,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_invite.webp</t>
+          <t>resources/si/renna_newhair/renna_si_pause.webp</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_invite.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_pause.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19836,12 +19946,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_lookaway.webp</t>
+          <t>resources/si/renna_newhair/renna_si_relief.webp</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_lookaway.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_relief.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19858,12 +19968,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_lookawaytalk.webp</t>
+          <t>resources/si/renna_newhair/renna_si_sad.webp</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_lookawaytalk.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_sad.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19880,12 +19990,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_lookdown.webp</t>
+          <t>resources/si/renna_newhair/renna_si_shout.webp</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_lookdown.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_shout.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19902,12 +20012,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_lookup.webp</t>
+          <t>resources/si/renna_newhair/renna_si_smile.webp</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_lookup.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_smile.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19924,12 +20034,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_pause.webp</t>
+          <t>resources/si/renna_newhair/renna_si_stare.webp</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_pause.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_stare.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19946,12 +20056,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_relief.webp</t>
+          <t>resources/si/renna_newhair/renna_si_surprise.webp</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_relief.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_surprise.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19968,12 +20078,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_sad.webp</t>
+          <t>resources/si/renna_newhair/renna_si_talkserious.webp</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_sad.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_talkserious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -19990,12 +20100,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_shout.webp</t>
+          <t>resources/si/renna_newhair/renna_si_talkwork.webp</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_shout.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_talkwork.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -20012,12 +20122,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_smile.webp</t>
+          <t>resources/si/renna_newhair/renna_si_think.webp</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_smile.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_think.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -20034,12 +20144,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_stare.webp</t>
+          <t>resources/si/renna_newhair/renna_si_tire.webp</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_stare.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_tire.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -20056,12 +20166,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_surprise.webp</t>
+          <t>resources/si/renna_newhair/renna_si_upset.webp</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_surprise.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_upset.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -20078,12 +20188,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_talkserious.webp</t>
+          <t>resources/si/renna_newhair/renna_si_upsetstare.webp</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_talkserious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_upsetstare.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -20100,12 +20210,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_talkwork.webp</t>
+          <t>resources/si/renna_newhair/renna_si_wake.webp</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_talkwork.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_wake.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -20122,12 +20232,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_think.webp</t>
+          <t>resources/si/renna_newhair/renna_si_watch.webp</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_think.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_watch.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -20144,12 +20254,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_tire.webp</t>
+          <t>resources/si/renna_newhair/renna_si_worry.webp</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_tire.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_worry.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -20166,188 +20276,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_upset.webp</t>
+          <t>resources/si/renna_newhair/renna_si_write.webp</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_upset.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Renna</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>resources/si/renna_newhair/renna_si_upsetstare.webp</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_upsetstare.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Renna</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>resources/si/renna_newhair/renna_si_wake.webp</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_wake.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Renna</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>resources/si/renna_newhair/renna_si_watch.webp</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_watch.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Renna</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>resources/si/renna_newhair/renna_si_worry.webp</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_worry.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Renna</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>resources/si/renna_newhair/renna_si_write.webp</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
           <t>線上跑的是 renna_si_write.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Renna</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>resources/si/renna_si_hug.png</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_hug.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Renna</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>resources/si/renna_si_hugclose.png</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_hugclose.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Renna</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>resources/si/renna_si_huglookaway.png</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_huglookaway.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -23656,7 +23590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L75"/>
+  <dimension ref="A1:L76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -23766,10 +23700,10 @@
         <v>0.5620000000000001</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>1590</v>
+        <v>1527</v>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
@@ -23813,10 +23747,10 @@
         <v>0.522</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>1593</v>
+        <v>1530</v>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
@@ -23860,10 +23794,10 @@
         <v>0.547</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>1593</v>
+        <v>1529</v>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
@@ -24612,10 +24546,10 @@
         <v>0.454</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>1591</v>
+        <v>1527</v>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
@@ -24659,10 +24593,10 @@
         <v>0.55</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>1579</v>
+        <v>1515</v>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
@@ -24706,10 +24640,10 @@
         <v>0.532</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>1587</v>
+        <v>1524</v>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
@@ -24800,10 +24734,10 @@
         <v>0.547</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>1587</v>
+        <v>1523</v>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
@@ -24894,10 +24828,10 @@
         <v>0.442</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>1592</v>
+        <v>1527</v>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
@@ -24941,10 +24875,10 @@
         <v>0.569</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>1592</v>
+        <v>1529</v>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
@@ -24988,10 +24922,10 @@
         <v>0.551</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>1593</v>
+        <v>1529</v>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
@@ -25012,12 +24946,12 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_excite2.webp</t>
+          <t>sorana_si_excite.webp</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>excite2</t>
+          <t>excite</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -25032,22 +24966,22 @@
         </is>
       </c>
       <c r="H29" s="5" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.674</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>1577</v>
+        <v>1521</v>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>1026×1532</t>
+          <t>1028×1529</t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_excite2.webp</t>
+          <t>resources/si/sorana_si_excite.webp</t>
         </is>
       </c>
     </row>
@@ -25059,12 +24993,12 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_front.webp</t>
+          <t>sorana_si_excite2.webp</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>front</t>
+          <t>excite2</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -25079,64 +25013,69 @@
         </is>
       </c>
       <c r="H30" s="5" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>1510</v>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>1026×1532</t>
+        </is>
+      </c>
+      <c r="L30" s="6" t="inlineStr">
+        <is>
+          <t>resources/si/sorana_si_excite2.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="111" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>索菈娜</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>sorana_si_front.webp</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>front</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="n">
         <v>0.659</v>
       </c>
-      <c r="I30" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>1592</v>
-      </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L30" s="6" t="inlineStr">
+      <c r="I31" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>1529</v>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L31" s="6" t="inlineStr">
         <is>
           <t>resources/si/sorana_si_front.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="111" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>索菈娜</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>sorana_si_furious.webp</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="n"/>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="n"/>
-      <c r="J31" s="2" t="n"/>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>1024×1535</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>resources/si/sorana_si_furious.webp</t>
         </is>
       </c>
     </row>
@@ -25148,12 +25087,12 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_furiousq.webp</t>
+          <t>sorana_si_furiouscute.webp</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>furiousq</t>
+          <t>furiouscute</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -25168,22 +25107,22 @@
         </is>
       </c>
       <c r="H32" s="5" t="n">
-        <v>0.535</v>
+        <v>0.474</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>1293</v>
+        <v>1527</v>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>1205×1306</t>
+          <t>1024×1535</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_furiousq.webp</t>
+          <t>resources/si/sorana_si_furiouscute.webp</t>
         </is>
       </c>
     </row>
@@ -25195,12 +25134,12 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_guard.webp</t>
+          <t>sorana_si_furiousq.webp</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>guard</t>
+          <t>furiousq</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -25215,22 +25154,22 @@
         </is>
       </c>
       <c r="H33" s="5" t="n">
-        <v>0.651</v>
+        <v>0.535</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>1527</v>
+        <v>1293</v>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>1024×1535</t>
+          <t>1205×1306</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_guard.webp</t>
+          <t>resources/si/sorana_si_furiousq.webp</t>
         </is>
       </c>
     </row>
@@ -25242,12 +25181,12 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_guardtalk.webp</t>
+          <t>sorana_si_guard.webp</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>guardtalk</t>
+          <t>guard</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -25262,13 +25201,13 @@
         </is>
       </c>
       <c r="H34" s="5" t="n">
-        <v>0.653</v>
+        <v>0.651</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
@@ -25277,7 +25216,7 @@
       </c>
       <c r="L34" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_guardtalk.webp</t>
+          <t>resources/si/sorana_si_guard.webp</t>
         </is>
       </c>
     </row>
@@ -25289,12 +25228,12 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_guardthink.webp</t>
+          <t>sorana_si_guardtalk.webp</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>guardthink</t>
+          <t>guardtalk</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -25309,22 +25248,22 @@
         </is>
       </c>
       <c r="H35" s="5" t="n">
-        <v>0.672</v>
+        <v>0.653</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J35" s="5" t="n">
         <v>1529</v>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>1024×1536</t>
+          <t>1024×1535</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_guardthink.webp</t>
+          <t>resources/si/sorana_si_guardtalk.webp</t>
         </is>
       </c>
     </row>
@@ -25336,12 +25275,12 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_hug.webp</t>
+          <t>sorana_si_guardthink.webp</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>hug</t>
+          <t>guardthink</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -25356,22 +25295,22 @@
         </is>
       </c>
       <c r="H36" s="5" t="n">
-        <v>0.408</v>
+        <v>0.672</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>1485</v>
+        <v>1529</v>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>1024×1535</t>
+          <t>1024×1536</t>
         </is>
       </c>
       <c r="L36" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_hug.webp</t>
+          <t>resources/si/sorana_si_guardthink.webp</t>
         </is>
       </c>
     </row>
@@ -25383,12 +25322,12 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_idea.webp</t>
+          <t>sorana_si_hug.webp</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>idea</t>
+          <t>hug</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -25403,22 +25342,22 @@
         </is>
       </c>
       <c r="H37" s="5" t="n">
-        <v>0.523</v>
+        <v>0.408</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>1525</v>
+        <v>1485</v>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>1024×1536</t>
+          <t>1024×1535</t>
         </is>
       </c>
       <c r="L37" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_idea.webp</t>
+          <t>resources/si/sorana_si_hug.webp</t>
         </is>
       </c>
     </row>
@@ -25430,12 +25369,12 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_lauaghbig.webp</t>
+          <t>sorana_si_idea.webp</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>lauaghbig</t>
+          <t>idea</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -25450,22 +25389,22 @@
         </is>
       </c>
       <c r="H38" s="5" t="n">
-        <v>0.492</v>
+        <v>0.523</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>1529</v>
+        <v>1525</v>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>1024×1535</t>
+          <t>1024×1536</t>
         </is>
       </c>
       <c r="L38" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_lauaghbig.webp</t>
+          <t>resources/si/sorana_si_idea.webp</t>
         </is>
       </c>
     </row>
@@ -25477,12 +25416,12 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_laugh.webp</t>
+          <t>sorana_si_lauaghbig.webp</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>laugh</t>
+          <t>lauaghbig</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -25497,22 +25436,22 @@
         </is>
       </c>
       <c r="H39" s="5" t="n">
-        <v>0.579</v>
+        <v>0.492</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J39" s="5" t="n">
         <v>1529</v>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>1024×1536</t>
+          <t>1024×1535</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_laugh.webp</t>
+          <t>resources/si/sorana_si_lauaghbig.webp</t>
         </is>
       </c>
     </row>
@@ -25524,12 +25463,12 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_lookaway.webp</t>
+          <t>sorana_si_laugh.webp</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>lookaway</t>
+          <t>laugh</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -25544,13 +25483,13 @@
         </is>
       </c>
       <c r="H40" s="5" t="n">
-        <v>0.61</v>
+        <v>0.579</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>1522</v>
+        <v>1529</v>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
@@ -25559,7 +25498,7 @@
       </c>
       <c r="L40" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_lookaway.webp</t>
+          <t>resources/si/sorana_si_laugh.webp</t>
         </is>
       </c>
     </row>
@@ -25571,12 +25510,12 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_nod.webp</t>
+          <t>sorana_si_lookaway.webp</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>nod</t>
+          <t>lookaway</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -25591,13 +25530,13 @@
         </is>
       </c>
       <c r="H41" s="5" t="n">
-        <v>0.529</v>
+        <v>0.61</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>1527</v>
+        <v>1522</v>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
@@ -25606,7 +25545,7 @@
       </c>
       <c r="L41" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_nod.webp</t>
+          <t>resources/si/sorana_si_lookaway.webp</t>
         </is>
       </c>
     </row>
@@ -25618,12 +25557,12 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_panic.webp</t>
+          <t>sorana_si_nod.webp</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>panic</t>
+          <t>nod</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -25638,13 +25577,13 @@
         </is>
       </c>
       <c r="H42" s="5" t="n">
-        <v>0.649</v>
+        <v>0.529</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>1522</v>
+        <v>1527</v>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
@@ -25653,7 +25592,7 @@
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_panic.webp</t>
+          <t>resources/si/sorana_si_nod.webp</t>
         </is>
       </c>
     </row>
@@ -25665,12 +25604,12 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_point.webp</t>
+          <t>sorana_si_panic.webp</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>point</t>
+          <t>panic</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -25685,111 +25624,111 @@
         </is>
       </c>
       <c r="H43" s="5" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>1522</v>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L43" s="6" t="inlineStr">
+        <is>
+          <t>resources/si/sorana_si_panic.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="111" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>索菈娜</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>sorana_si_point.webp</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="n"/>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="n">
         <v>0.543</v>
       </c>
-      <c r="I43" s="5" t="n">
+      <c r="I44" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="J43" s="5" t="n">
+      <c r="J44" s="5" t="n">
         <v>1523</v>
       </c>
-      <c r="K43" s="5" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L43" s="6" t="inlineStr">
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L44" s="6" t="inlineStr">
         <is>
           <t>resources/si/sorana_si_point.webp</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="111" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="45" ht="111" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>索菈娜</t>
         </is>
       </c>
-      <c r="B44" s="3" t="n"/>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="B45" s="3" t="n"/>
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>sorana_si_q.webp</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>✘ 未接線</t>
         </is>
       </c>
-      <c r="F44" s="4" t="n"/>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>估</t>
         </is>
       </c>
-      <c r="H44" s="2" t="n"/>
-      <c r="I44" s="2" t="n"/>
-      <c r="J44" s="2" t="n"/>
-      <c r="K44" s="2" t="inlineStr">
+      <c r="H45" s="2" t="n"/>
+      <c r="I45" s="2" t="n"/>
+      <c r="J45" s="2" t="n"/>
+      <c r="K45" s="2" t="inlineStr">
         <is>
           <t>1190×1322</t>
         </is>
       </c>
-      <c r="L44" s="4" t="inlineStr">
+      <c r="L45" s="4" t="inlineStr">
         <is>
           <t>resources/si/sorana_si_q.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="111" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>索菈娜</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>sorana_si_read.webp</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F45" s="6" t="n"/>
-      <c r="G45" s="5" t="inlineStr">
-        <is>
-          <t>量</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="I45" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="J45" s="5" t="n">
-        <v>1533</v>
-      </c>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L45" s="6" t="inlineStr">
-        <is>
-          <t>resources/si/sorana_si_read.webp</t>
         </is>
       </c>
     </row>
@@ -25801,12 +25740,12 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_readconfuse.webp</t>
+          <t>sorana_si_read.webp</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>readconfuse</t>
+          <t>read</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -25821,13 +25760,13 @@
         </is>
       </c>
       <c r="H46" s="5" t="n">
-        <v>0.671</v>
+        <v>0.64</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>1528</v>
+        <v>1533</v>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
@@ -25836,7 +25775,7 @@
       </c>
       <c r="L46" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_readconfuse.webp</t>
+          <t>resources/si/sorana_si_read.webp</t>
         </is>
       </c>
     </row>
@@ -25848,12 +25787,12 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_readhappy.webp</t>
+          <t>sorana_si_readconfuse.webp</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>readhappy</t>
+          <t>readconfuse</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -25868,13 +25807,13 @@
         </is>
       </c>
       <c r="H47" s="5" t="n">
-        <v>0.644</v>
+        <v>0.671</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>1531</v>
+        <v>1528</v>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
@@ -25883,7 +25822,7 @@
       </c>
       <c r="L47" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_readhappy.webp</t>
+          <t>resources/si/sorana_si_readconfuse.webp</t>
         </is>
       </c>
     </row>
@@ -25895,12 +25834,12 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_readsad.webp</t>
+          <t>sorana_si_readhappy.webp</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>readsad</t>
+          <t>readhappy</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -25915,13 +25854,13 @@
         </is>
       </c>
       <c r="H48" s="5" t="n">
-        <v>0.643</v>
+        <v>0.644</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
@@ -25930,7 +25869,7 @@
       </c>
       <c r="L48" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_readsad.webp</t>
+          <t>resources/si/sorana_si_readhappy.webp</t>
         </is>
       </c>
     </row>
@@ -25942,12 +25881,12 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_readshock.webp</t>
+          <t>sorana_si_readsad.webp</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>readshock</t>
+          <t>readsad</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -25962,13 +25901,13 @@
         </is>
       </c>
       <c r="H49" s="5" t="n">
-        <v>0.645</v>
+        <v>0.643</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>1522</v>
+        <v>1530</v>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
@@ -25977,7 +25916,7 @@
       </c>
       <c r="L49" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_readshock.webp</t>
+          <t>resources/si/sorana_si_readsad.webp</t>
         </is>
       </c>
     </row>
@@ -25989,12 +25928,12 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_ready.webp</t>
+          <t>sorana_si_readshock.webp</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>ready</t>
+          <t>readshock</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -26009,13 +25948,13 @@
         </is>
       </c>
       <c r="H50" s="5" t="n">
-        <v>0.631</v>
+        <v>0.645</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
@@ -26024,7 +25963,7 @@
       </c>
       <c r="L50" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_ready.webp</t>
+          <t>resources/si/sorana_si_readshock.webp</t>
         </is>
       </c>
     </row>
@@ -26036,12 +25975,12 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_readysmile.webp</t>
+          <t>sorana_si_ready.webp</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>readysmile</t>
+          <t>ready</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -26056,22 +25995,22 @@
         </is>
       </c>
       <c r="H51" s="5" t="n">
-        <v>0.578</v>
+        <v>0.631</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>1534</v>
+        <v>1521</v>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>1024×1535</t>
+          <t>1024×1536</t>
         </is>
       </c>
       <c r="L51" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_readysmile.webp</t>
+          <t>resources/si/sorana_si_ready.webp</t>
         </is>
       </c>
     </row>
@@ -26083,12 +26022,12 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_relief.webp</t>
+          <t>sorana_si_readysmile.webp</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>relief</t>
+          <t>readysmile</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -26103,22 +26042,22 @@
         </is>
       </c>
       <c r="H52" s="5" t="n">
-        <v>0.556</v>
+        <v>0.578</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>1518</v>
+        <v>1534</v>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>1024×1536</t>
+          <t>1024×1535</t>
         </is>
       </c>
       <c r="L52" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_relief.webp</t>
+          <t>resources/si/sorana_si_readysmile.webp</t>
         </is>
       </c>
     </row>
@@ -26130,12 +26069,12 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_remind.webp</t>
+          <t>sorana_si_relief.webp</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>remind</t>
+          <t>relief</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -26150,13 +26089,13 @@
         </is>
       </c>
       <c r="H53" s="5" t="n">
-        <v>0.523</v>
+        <v>0.556</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>1525</v>
+        <v>1518</v>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
@@ -26165,7 +26104,7 @@
       </c>
       <c r="L53" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_remind.webp</t>
+          <t>resources/si/sorana_si_relief.webp</t>
         </is>
       </c>
     </row>
@@ -26177,12 +26116,12 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_sad.webp</t>
+          <t>sorana_si_remind.webp</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>sad</t>
+          <t>remind</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -26197,22 +26136,22 @@
         </is>
       </c>
       <c r="H54" s="5" t="n">
-        <v>0.515</v>
+        <v>0.523</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>1024×1535</t>
+          <t>1024×1536</t>
         </is>
       </c>
       <c r="L54" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_sad.webp</t>
+          <t>resources/si/sorana_si_remind.webp</t>
         </is>
       </c>
     </row>
@@ -26224,12 +26163,12 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_salute.webp</t>
+          <t>sorana_si_sad.webp</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>salute</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -26244,22 +26183,22 @@
         </is>
       </c>
       <c r="H55" s="5" t="n">
-        <v>0.58</v>
+        <v>0.515</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>1525</v>
+        <v>1527</v>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>1024×1536</t>
+          <t>1024×1535</t>
         </is>
       </c>
       <c r="L55" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_salute.webp</t>
+          <t>resources/si/sorana_si_sad.webp</t>
         </is>
       </c>
     </row>
@@ -26271,12 +26210,12 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_scare.webp</t>
+          <t>sorana_si_salute.webp</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>scare</t>
+          <t>salute</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -26291,13 +26230,13 @@
         </is>
       </c>
       <c r="H56" s="5" t="n">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>1518</v>
+        <v>1525</v>
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
@@ -26306,7 +26245,7 @@
       </c>
       <c r="L56" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_scare.webp</t>
+          <t>resources/si/sorana_si_salute.webp</t>
         </is>
       </c>
     </row>
@@ -26318,12 +26257,12 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_serious.webp</t>
+          <t>sorana_si_scare.webp</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>serious</t>
+          <t>scare</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -26338,13 +26277,13 @@
         </is>
       </c>
       <c r="H57" s="5" t="n">
-        <v>0.576</v>
+        <v>0.54</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>1524</v>
+        <v>1518</v>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
@@ -26353,7 +26292,7 @@
       </c>
       <c r="L57" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_serious.webp</t>
+          <t>resources/si/sorana_si_scare.webp</t>
         </is>
       </c>
     </row>
@@ -26365,12 +26304,12 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_shy.webp</t>
+          <t>sorana_si_serious.webp</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>shy</t>
+          <t>serious</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -26385,13 +26324,13 @@
         </is>
       </c>
       <c r="H58" s="5" t="n">
-        <v>0.586</v>
+        <v>0.576</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>1531</v>
+        <v>1524</v>
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
@@ -26400,7 +26339,7 @@
       </c>
       <c r="L58" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_shy.webp</t>
+          <t>resources/si/sorana_si_serious.webp</t>
         </is>
       </c>
     </row>
@@ -26412,12 +26351,12 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_side.webp</t>
+          <t>sorana_si_shy.webp</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>(base)</t>
+          <t>shy</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -26432,13 +26371,13 @@
         </is>
       </c>
       <c r="H59" s="5" t="n">
-        <v>0.498</v>
+        <v>0.586</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>1526</v>
+        <v>1531</v>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
@@ -26447,7 +26386,7 @@
       </c>
       <c r="L59" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_side.webp</t>
+          <t>resources/si/sorana_si_shy.webp</t>
         </is>
       </c>
     </row>
@@ -26459,12 +26398,12 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_sleep.webp</t>
+          <t>sorana_si_side.webp</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>sleep</t>
+          <t>(base)</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -26479,22 +26418,22 @@
         </is>
       </c>
       <c r="H60" s="5" t="n">
-        <v>0.461</v>
+        <v>0.498</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>230</v>
+        <v>4</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>1424</v>
+        <v>1526</v>
       </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
-          <t>1024×1535</t>
+          <t>1024×1536</t>
         </is>
       </c>
       <c r="L60" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_sleep.webp</t>
+          <t>resources/si/sorana_si_side.webp</t>
         </is>
       </c>
     </row>
@@ -26506,12 +26445,12 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_smile.webp</t>
+          <t>sorana_si_sleep.webp</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>smile</t>
+          <t>sleep</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -26526,22 +26465,22 @@
         </is>
       </c>
       <c r="H61" s="5" t="n">
-        <v>0.528</v>
+        <v>0.461</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>9</v>
+        <v>230</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>1530</v>
+        <v>1424</v>
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>1024×1536</t>
+          <t>1024×1535</t>
         </is>
       </c>
       <c r="L61" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_smile.webp</t>
+          <t>resources/si/sorana_si_sleep.webp</t>
         </is>
       </c>
     </row>
@@ -26553,12 +26492,12 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_smirk.webp</t>
+          <t>sorana_si_smile.webp</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>smirk</t>
+          <t>smile</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -26573,13 +26512,13 @@
         </is>
       </c>
       <c r="H62" s="5" t="n">
-        <v>0.582</v>
+        <v>0.528</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
@@ -26588,7 +26527,7 @@
       </c>
       <c r="L62" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_smirk.webp</t>
+          <t>resources/si/sorana_si_smile.webp</t>
         </is>
       </c>
     </row>
@@ -26600,12 +26539,12 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_sorry.webp</t>
+          <t>sorana_si_smirk.webp</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>sorry</t>
+          <t>smirk</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -26620,10 +26559,10 @@
         </is>
       </c>
       <c r="H63" s="5" t="n">
-        <v>0.511</v>
+        <v>0.582</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J63" s="5" t="n">
         <v>1528</v>
@@ -26635,7 +26574,7 @@
       </c>
       <c r="L63" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_sorry.webp</t>
+          <t>resources/si/sorana_si_smirk.webp</t>
         </is>
       </c>
     </row>
@@ -26647,12 +26586,12 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_stare.webp</t>
+          <t>sorana_si_sorry.webp</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>stare</t>
+          <t>sorry</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -26667,10 +26606,10 @@
         </is>
       </c>
       <c r="H64" s="5" t="n">
-        <v>0.514</v>
+        <v>0.511</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J64" s="5" t="n">
         <v>1528</v>
@@ -26682,7 +26621,7 @@
       </c>
       <c r="L64" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_stare.webp</t>
+          <t>resources/si/sorana_si_sorry.webp</t>
         </is>
       </c>
     </row>
@@ -26694,12 +26633,12 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_surprise.webp</t>
+          <t>sorana_si_stare.webp</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>surprise</t>
+          <t>stare</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -26714,13 +26653,13 @@
         </is>
       </c>
       <c r="H65" s="5" t="n">
-        <v>0.537</v>
+        <v>0.514</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>1522</v>
+        <v>1528</v>
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
@@ -26729,7 +26668,7 @@
       </c>
       <c r="L65" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_surprise.webp</t>
+          <t>resources/si/sorana_si_stare.webp</t>
         </is>
       </c>
     </row>
@@ -26741,12 +26680,12 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_talk.webp</t>
+          <t>sorana_si_surprise.webp</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>talk</t>
+          <t>surprise</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -26761,13 +26700,13 @@
         </is>
       </c>
       <c r="H66" s="5" t="n">
-        <v>0.508</v>
+        <v>0.537</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>1525</v>
+        <v>1522</v>
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
@@ -26776,7 +26715,7 @@
       </c>
       <c r="L66" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_talk.webp</t>
+          <t>resources/si/sorana_si_surprise.webp</t>
         </is>
       </c>
     </row>
@@ -26788,12 +26727,12 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_talksmile.webp</t>
+          <t>sorana_si_talk.webp</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>talksmile</t>
+          <t>talk</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -26808,13 +26747,13 @@
         </is>
       </c>
       <c r="H67" s="5" t="n">
-        <v>0.512</v>
+        <v>0.508</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>1522</v>
+        <v>1525</v>
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
@@ -26823,7 +26762,7 @@
       </c>
       <c r="L67" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_talksmile.webp</t>
+          <t>resources/si/sorana_si_talk.webp</t>
         </is>
       </c>
     </row>
@@ -26835,12 +26774,12 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_tease.webp</t>
+          <t>sorana_si_talksmile.webp</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>tease</t>
+          <t>talksmile</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -26855,13 +26794,13 @@
         </is>
       </c>
       <c r="H68" s="5" t="n">
-        <v>0.583</v>
+        <v>0.512</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>1528</v>
+        <v>1522</v>
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
@@ -26870,7 +26809,7 @@
       </c>
       <c r="L68" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_tease.webp</t>
+          <t>resources/si/sorana_si_talksmile.webp</t>
         </is>
       </c>
     </row>
@@ -26882,12 +26821,12 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_think.webp</t>
+          <t>sorana_si_tease.webp</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>think</t>
+          <t>tease</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -26902,13 +26841,13 @@
         </is>
       </c>
       <c r="H69" s="5" t="n">
-        <v>0.529</v>
+        <v>0.583</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
@@ -26917,7 +26856,7 @@
       </c>
       <c r="L69" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_think.webp</t>
+          <t>resources/si/sorana_si_tease.webp</t>
         </is>
       </c>
     </row>
@@ -26929,12 +26868,12 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_tire.webp</t>
+          <t>sorana_si_think.webp</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>tire</t>
+          <t>think</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -26949,13 +26888,13 @@
         </is>
       </c>
       <c r="H70" s="5" t="n">
-        <v>0.511</v>
+        <v>0.529</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>1522</v>
+        <v>1527</v>
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
@@ -26964,7 +26903,7 @@
       </c>
       <c r="L70" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_tire.webp</t>
+          <t>resources/si/sorana_si_think.webp</t>
         </is>
       </c>
     </row>
@@ -26976,12 +26915,12 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_upset.webp</t>
+          <t>sorana_si_tire.webp</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>upset</t>
+          <t>tire</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -26996,13 +26935,13 @@
         </is>
       </c>
       <c r="H71" s="5" t="n">
-        <v>0.514</v>
+        <v>0.511</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>1526</v>
+        <v>1522</v>
       </c>
       <c r="K71" s="5" t="inlineStr">
         <is>
@@ -27011,7 +26950,7 @@
       </c>
       <c r="L71" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_upset.webp</t>
+          <t>resources/si/sorana_si_tire.webp</t>
         </is>
       </c>
     </row>
@@ -27023,12 +26962,12 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_watch.webp</t>
+          <t>sorana_si_upset.webp</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>watch</t>
+          <t>upset</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -27043,13 +26982,13 @@
         </is>
       </c>
       <c r="H72" s="5" t="n">
-        <v>0.68</v>
+        <v>0.514</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>1521</v>
+        <v>1526</v>
       </c>
       <c r="K72" s="5" t="inlineStr">
         <is>
@@ -27058,7 +26997,7 @@
       </c>
       <c r="L72" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_watch.webp</t>
+          <t>resources/si/sorana_si_upset.webp</t>
         </is>
       </c>
     </row>
@@ -27070,12 +27009,12 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_wave.webp</t>
+          <t>sorana_si_watch.webp</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>wave</t>
+          <t>watch</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -27090,13 +27029,13 @@
         </is>
       </c>
       <c r="H73" s="5" t="n">
-        <v>0.53</v>
+        <v>0.68</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>1527</v>
+        <v>1521</v>
       </c>
       <c r="K73" s="5" t="inlineStr">
         <is>
@@ -27105,7 +27044,7 @@
       </c>
       <c r="L73" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_wave.webp</t>
+          <t>resources/si/sorana_si_watch.webp</t>
         </is>
       </c>
     </row>
@@ -27117,12 +27056,12 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_whisper.webp</t>
+          <t>sorana_si_wave.webp</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>whisper</t>
+          <t>wave</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -27137,13 +27076,13 @@
         </is>
       </c>
       <c r="H74" s="5" t="n">
-        <v>0.524</v>
+        <v>0.53</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>1492</v>
+        <v>1527</v>
       </c>
       <c r="K74" s="5" t="inlineStr">
         <is>
@@ -27152,7 +27091,7 @@
       </c>
       <c r="L74" s="6" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_whisper.webp</t>
+          <t>resources/si/sorana_si_wave.webp</t>
         </is>
       </c>
     </row>
@@ -27164,12 +27103,12 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>sorana_si_worry.webp</t>
+          <t>sorana_si_whisper.webp</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>worry</t>
+          <t>whisper</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -27184,20 +27123,67 @@
         </is>
       </c>
       <c r="H75" s="5" t="n">
-        <v>0.543</v>
+        <v>0.524</v>
       </c>
       <c r="I75" s="5" t="n">
         <v>4</v>
       </c>
       <c r="J75" s="5" t="n">
+        <v>1524</v>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>1024×1535</t>
+        </is>
+      </c>
+      <c r="L75" s="6" t="inlineStr">
+        <is>
+          <t>resources/si/sorana_si_whisper.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="111" customHeight="1">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>索菈娜</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>sorana_si_worry.webp</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>worry</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="n"/>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J76" s="5" t="n">
         <v>1519</v>
       </c>
-      <c r="K75" s="5" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L75" s="6" t="inlineStr">
+      <c r="K76" s="5" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L76" s="6" t="inlineStr">
         <is>
           <t>resources/si/sorana_si_worry.webp</t>
         </is>
@@ -28037,42 +28023,47 @@
       </c>
     </row>
     <row r="18" ht="111" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>安雅</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>anya_si_happy.webp</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="n"/>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>1531</v>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
         <is>
           <t>resources/si/anya_si_happy.webp</t>
         </is>
@@ -28428,11 +28419,7 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>1 張：anya_si_nod.png</t>
-        </is>
-      </c>
+      <c r="F26" s="6" t="n"/>
       <c r="G26" s="5" t="inlineStr">
         <is>
           <t>量</t>
@@ -29060,42 +29047,47 @@
       </c>
     </row>
     <row r="40" ht="111" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>安雅</t>
         </is>
       </c>
-      <c r="B40" s="3" t="n"/>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>anya_si_smile.webp</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="n"/>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="n"/>
-      <c r="I40" s="2" t="n"/>
-      <c r="J40" s="2" t="n"/>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L40" s="4" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>smile</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="n"/>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>1526</v>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L40" s="6" t="inlineStr">
         <is>
           <t>resources/si/anya_si_smile.webp</t>
         </is>
@@ -30254,13 +30246,13 @@
         </is>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0.46</v>
+        <v>0.434</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>1516</v>
+        <v>1534</v>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
@@ -30301,13 +30293,13 @@
         </is>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0.46</v>
+        <v>0.434</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>1516</v>
+        <v>1534</v>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>

--- a/resources/si/_SI_差分總表.xlsx
+++ b/resources/si/_SI_差分總表.xlsx
@@ -22761,42 +22761,47 @@
       </c>
     </row>
     <row r="45" ht="111" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>諾薇兒</t>
         </is>
       </c>
-      <c r="B45" s="5" t="n"/>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>nouvelle_si_runcry.webp</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F45" s="6" t="n"/>
-      <c r="G45" s="4" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="n"/>
-      <c r="I45" s="4" t="n"/>
-      <c r="J45" s="4" t="n"/>
-      <c r="K45" s="4" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L45" s="6" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>runcry</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="n"/>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>1528</v>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
         <is>
           <t>resources/si/nouvelle_si_runcry.webp</t>
         </is>
@@ -25025,13 +25030,13 @@
     <row r="17" ht="111" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Mage</t>
+          <t>Molly</t>
         </is>
       </c>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>mage_si_barrier.webp</t>
+          <t>molly_si_ask.webp</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -25060,20 +25065,20 @@
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/mage_si_barrier.webp</t>
+          <t>resources/si/npc/molly_si_ask.webp</t>
         </is>
       </c>
     </row>
     <row r="18" ht="111" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Mage</t>
+          <t>Molly</t>
         </is>
       </c>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>mage_si_cast.webp</t>
+          <t>molly_si_closedtalk.webp</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -25102,20 +25107,20 @@
       </c>
       <c r="L18" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/mage_si_cast.webp</t>
+          <t>resources/si/npc/molly_si_closedtalk.webp</t>
         </is>
       </c>
     </row>
     <row r="19" ht="111" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Mage</t>
+          <t>Molly</t>
         </is>
       </c>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>mage_si_front.webp</t>
+          <t>molly_si_eyesmile.webp</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -25144,20 +25149,20 @@
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/mage_si_front.webp</t>
+          <t>resources/si/npc/molly_si_eyesmile.webp</t>
         </is>
       </c>
     </row>
     <row r="20" ht="111" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Mage</t>
+          <t>Molly</t>
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>mage_si_hurt.webp</t>
+          <t>molly_si_front.webp</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -25186,7 +25191,7 @@
       </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/mage_si_hurt.webp</t>
+          <t>resources/si/npc/molly_si_front.webp</t>
         </is>
       </c>
     </row>
@@ -25199,7 +25204,7 @@
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>molly_si_ask.webp</t>
+          <t>molly_si_gossip.webp</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -25228,7 +25233,7 @@
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/molly_si_ask.webp</t>
+          <t>resources/si/npc/molly_si_gossip.webp</t>
         </is>
       </c>
     </row>
@@ -25241,7 +25246,7 @@
       <c r="B22" s="5" t="n"/>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>molly_si_closedtalk.webp</t>
+          <t>molly_si_lookdown.webp</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -25270,7 +25275,7 @@
       </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/molly_si_closedtalk.webp</t>
+          <t>resources/si/npc/molly_si_lookdown.webp</t>
         </is>
       </c>
     </row>
@@ -25283,7 +25288,7 @@
       <c r="B23" s="5" t="n"/>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>molly_si_eyesmile.webp</t>
+          <t>molly_si_order.webp</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -25312,7 +25317,7 @@
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/molly_si_eyesmile.webp</t>
+          <t>resources/si/npc/molly_si_order.webp</t>
         </is>
       </c>
     </row>
@@ -25325,7 +25330,7 @@
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>molly_si_front.webp</t>
+          <t>molly_si_serious.webp</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -25354,7 +25359,7 @@
       </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/molly_si_front.webp</t>
+          <t>resources/si/npc/molly_si_serious.webp</t>
         </is>
       </c>
     </row>
@@ -25367,7 +25372,7 @@
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>molly_si_gossip.webp</t>
+          <t>molly_si_softsmile.webp</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -25396,7 +25401,7 @@
       </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/molly_si_gossip.webp</t>
+          <t>resources/si/npc/molly_si_softsmile.webp</t>
         </is>
       </c>
     </row>
@@ -25409,7 +25414,7 @@
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>molly_si_lookdown.webp</t>
+          <t>molly_si_stern.webp</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -25438,7 +25443,7 @@
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/molly_si_lookdown.webp</t>
+          <t>resources/si/npc/molly_si_stern.webp</t>
         </is>
       </c>
     </row>
@@ -25451,7 +25456,7 @@
       <c r="B27" s="5" t="n"/>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>molly_si_order.webp</t>
+          <t>molly_si_superior.webp</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -25480,7 +25485,7 @@
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/molly_si_order.webp</t>
+          <t>resources/si/npc/molly_si_superior.webp</t>
         </is>
       </c>
     </row>
@@ -25493,7 +25498,7 @@
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>molly_si_serious.webp</t>
+          <t>molly_si_surprise.webp</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -25522,7 +25527,7 @@
       </c>
       <c r="L28" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/molly_si_serious.webp</t>
+          <t>resources/si/npc/molly_si_surprise.webp</t>
         </is>
       </c>
     </row>
@@ -25535,7 +25540,7 @@
       <c r="B29" s="5" t="n"/>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>molly_si_softsmile.webp</t>
+          <t>molly_si_talk.webp</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -25564,7 +25569,7 @@
       </c>
       <c r="L29" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/molly_si_softsmile.webp</t>
+          <t>resources/si/npc/molly_si_talk.webp</t>
         </is>
       </c>
     </row>
@@ -25577,7 +25582,7 @@
       <c r="B30" s="5" t="n"/>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>molly_si_stern.webp</t>
+          <t>molly_si_think.webp</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -25606,7 +25611,7 @@
       </c>
       <c r="L30" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/molly_si_stern.webp</t>
+          <t>resources/si/npc/molly_si_think.webp</t>
         </is>
       </c>
     </row>
@@ -25619,7 +25624,7 @@
       <c r="B31" s="5" t="n"/>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>molly_si_superior.webp</t>
+          <t>molly_si_whisper.webp</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -25648,20 +25653,20 @@
       </c>
       <c r="L31" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/molly_si_superior.webp</t>
+          <t>resources/si/npc/molly_si_whisper.webp</t>
         </is>
       </c>
     </row>
     <row r="32" ht="111" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Molly</t>
+          <t>Npc_aaron</t>
         </is>
       </c>
       <c r="B32" s="5" t="n"/>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>molly_si_surprise.webp</t>
+          <t>npc_aaron_si_trial.png</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -25690,20 +25695,20 @@
       </c>
       <c r="L32" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/molly_si_surprise.webp</t>
+          <t>resources/si/npc/_trial/npc_aaron_si_trial.png</t>
         </is>
       </c>
     </row>
     <row r="33" ht="111" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Molly</t>
+          <t>Npc_molly</t>
         </is>
       </c>
       <c r="B33" s="5" t="n"/>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>molly_si_talk.webp</t>
+          <t>npc_molly_si_trial.png</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -25732,20 +25737,20 @@
       </c>
       <c r="L33" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/molly_si_talk.webp</t>
+          <t>resources/si/npc/_trial/npc_molly_si_trial.png</t>
         </is>
       </c>
     </row>
     <row r="34" ht="111" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Molly</t>
+          <t>Npc_robert</t>
         </is>
       </c>
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>molly_si_think.webp</t>
+          <t>npc_robert_si_trial.png</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -25774,20 +25779,20 @@
       </c>
       <c r="L34" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/molly_si_think.webp</t>
+          <t>resources/si/npc/_trial/npc_robert_si_trial.png</t>
         </is>
       </c>
     </row>
     <row r="35" ht="111" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Molly</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="B35" s="5" t="n"/>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>molly_si_whisper.webp</t>
+          <t>robert_si_blindeye.webp</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -25816,20 +25821,20 @@
       </c>
       <c r="L35" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/molly_si_whisper.webp</t>
+          <t>resources/si/npc/robert_si_blindeye.webp</t>
         </is>
       </c>
     </row>
     <row r="36" ht="111" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Npc_aaron</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>npc_aaron_si_trial.png</t>
+          <t>robert_si_bow.webp</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -25858,20 +25863,20 @@
       </c>
       <c r="L36" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/_trial/npc_aaron_si_trial.png</t>
+          <t>resources/si/npc/robert_si_bow.webp</t>
         </is>
       </c>
     </row>
     <row r="37" ht="111" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Npc_commander</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>npc_commander_si_front.webp</t>
+          <t>robert_si_closedtalk.webp</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -25900,20 +25905,20 @@
       </c>
       <c r="L37" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_commander_si_front.webp</t>
+          <t>resources/si/npc/robert_si_closedtalk.webp</t>
         </is>
       </c>
     </row>
     <row r="38" ht="111" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Npc_molly</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="B38" s="5" t="n"/>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>npc_molly_si_trial.png</t>
+          <t>robert_si_front.webp</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -25942,20 +25947,20 @@
       </c>
       <c r="L38" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/_trial/npc_molly_si_trial.png</t>
+          <t>resources/si/npc/robert_si_front.webp</t>
         </is>
       </c>
     </row>
     <row r="39" ht="111" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Npc_robert</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="B39" s="5" t="n"/>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>npc_robert_si_trial.png</t>
+          <t>robert_si_sideeye.webp</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -25984,7 +25989,7 @@
       </c>
       <c r="L39" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/_trial/npc_robert_si_trial.png</t>
+          <t>resources/si/npc/robert_si_sideeye.webp</t>
         </is>
       </c>
     </row>
@@ -25997,7 +26002,7 @@
       <c r="B40" s="5" t="n"/>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>robert_si_blindeye.webp</t>
+          <t>robert_si_surprise.webp</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -26026,7 +26031,7 @@
       </c>
       <c r="L40" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/robert_si_blindeye.webp</t>
+          <t>resources/si/npc/robert_si_surprise.webp</t>
         </is>
       </c>
     </row>
@@ -26039,7 +26044,7 @@
       <c r="B41" s="5" t="n"/>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>robert_si_bow.webp</t>
+          <t>robert_si_talk.webp</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -26068,20 +26073,20 @@
       </c>
       <c r="L41" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/robert_si_bow.webp</t>
+          <t>resources/si/npc/robert_si_talk.webp</t>
         </is>
       </c>
     </row>
     <row r="42" ht="111" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>f734e7ba-e7bb-457b-8cf7-66e13324c45d</t>
         </is>
       </c>
       <c r="B42" s="5" t="n"/>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>robert_si_closedtalk.webp</t>
+          <t>f734e7ba-e7bb-457b-8cf7-66e13324c45d.png</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -26110,234 +26115,259 @@
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/robert_si_closedtalk.webp</t>
+          <t>resources/si/npc/f734e7ba-e7bb-457b-8cf7-66e13324c45d.png</t>
         </is>
       </c>
     </row>
     <row r="43" ht="111" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>Robert</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="n"/>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>robert_si_front.webp</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="n"/>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="n"/>
-      <c r="I43" s="4" t="n"/>
-      <c r="J43" s="4" t="n"/>
-      <c r="K43" s="4" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L43" s="6" t="inlineStr">
-        <is>
-          <t>resources/si/npc/robert_si_front.webp</t>
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>前台</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>npc_hotel_capital.webp</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>(base)</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="n"/>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>1535</v>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/npc/npc_hotel_capital.webp</t>
         </is>
       </c>
     </row>
     <row r="44" ht="111" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>Robert</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="n"/>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>robert_si_sideeye.webp</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F44" s="6" t="n"/>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="n"/>
-      <c r="I44" s="4" t="n"/>
-      <c r="J44" s="4" t="n"/>
-      <c r="K44" s="4" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L44" s="6" t="inlineStr">
-        <is>
-          <t>resources/si/npc/robert_si_sideeye.webp</t>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>司祭</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>npc_np_priest.webp</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>(base)</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="n"/>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>1527</v>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/npc/npc_np_priest.webp</t>
         </is>
       </c>
     </row>
     <row r="45" ht="111" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>Robert</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="n"/>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>robert_si_surprise.webp</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F45" s="6" t="n"/>
-      <c r="G45" s="4" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="n"/>
-      <c r="I45" s="4" t="n"/>
-      <c r="J45" s="4" t="n"/>
-      <c r="K45" s="4" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L45" s="6" t="inlineStr">
-        <is>
-          <t>resources/si/npc/robert_si_surprise.webp</t>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>娜塔莉</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>npc_natalia_si_dead.webp</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>dead</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="n"/>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>1535</v>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/npc/npc_natalia_si_dead.webp</t>
         </is>
       </c>
     </row>
     <row r="46" ht="111" customHeight="1">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>Robert</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="n"/>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>robert_si_talk.webp</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F46" s="6" t="n"/>
-      <c r="G46" s="4" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="n"/>
-      <c r="I46" s="4" t="n"/>
-      <c r="J46" s="4" t="n"/>
-      <c r="K46" s="4" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L46" s="6" t="inlineStr">
-        <is>
-          <t>resources/si/npc/robert_si_talk.webp</t>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>娜塔莉</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>npc_natalia_si_die.webp</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>(base)</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="n"/>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>1535</v>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/npc/npc_natalia_si_die.webp</t>
         </is>
       </c>
     </row>
     <row r="47" ht="111" customHeight="1">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>f734e7ba-e7bb-457b-8cf7-66e13324c45d</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="n"/>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>f734e7ba-e7bb-457b-8cf7-66e13324c45d.png</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F47" s="6" t="n"/>
-      <c r="G47" s="4" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="n"/>
-      <c r="I47" s="4" t="n"/>
-      <c r="J47" s="4" t="n"/>
-      <c r="K47" s="4" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L47" s="6" t="inlineStr">
-        <is>
-          <t>resources/si/npc/f734e7ba-e7bb-457b-8cf7-66e13324c45d.png</t>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>小女孩</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>npc_ss_loti_ask.webp</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>(base)</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="n"/>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>0.477</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>1527</v>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/npc/npc_ss_loti_ask.webp</t>
         </is>
       </c>
     </row>
     <row r="48" ht="111" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>前台</t>
+          <t>小女孩</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>npc_hotel_capital.webp</t>
+          <t>npc_ss_loti_cry.webp</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>(base)</t>
+          <t>cry</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -26352,13 +26382,13 @@
         </is>
       </c>
       <c r="H48" s="2" t="n">
-        <v>0.494</v>
+        <v>0.46</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1535</v>
+        <v>1520</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -26367,24 +26397,24 @@
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_hotel_capital.webp</t>
+          <t>resources/si/npc/npc_ss_loti_cry.webp</t>
         </is>
       </c>
     </row>
     <row r="49" ht="111" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>司祭</t>
+          <t>小女孩</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>npc_np_priest.webp</t>
+          <t>npc_ss_loti_give.webp</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>(base)</t>
+          <t>give</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -26399,13 +26429,13 @@
         </is>
       </c>
       <c r="H49" s="2" t="n">
-        <v>0.46</v>
+        <v>0.463</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
@@ -26414,24 +26444,24 @@
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_np_priest.webp</t>
+          <t>resources/si/npc/npc_ss_loti_give.webp</t>
         </is>
       </c>
     </row>
     <row r="50" ht="111" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>娜塔莉</t>
+          <t>小女孩</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>npc_natalia_si_dead.webp</t>
+          <t>npc_ss_loti_guard.webp</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>dead</t>
+          <t>guard</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -26446,13 +26476,13 @@
         </is>
       </c>
       <c r="H50" s="2" t="n">
-        <v>0.363</v>
+        <v>0.51</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1535</v>
+        <v>1529</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
@@ -26461,24 +26491,24 @@
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_natalia_si_dead.webp</t>
+          <t>resources/si/npc/npc_ss_loti_guard.webp</t>
         </is>
       </c>
     </row>
     <row r="51" ht="111" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>娜塔莉</t>
+          <t>小女孩</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>npc_natalia_si_die.webp</t>
+          <t>npc_ss_loti_happy.webp</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>(base)</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -26493,13 +26523,13 @@
         </is>
       </c>
       <c r="H51" s="2" t="n">
-        <v>0.363</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>103</v>
+        <v>29</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1535</v>
+        <v>1523</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
@@ -26508,7 +26538,7 @@
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_natalia_si_die.webp</t>
+          <t>resources/si/npc/npc_ss_loti_happy.webp</t>
         </is>
       </c>
     </row>
@@ -26520,12 +26550,12 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_loti_ask.webp</t>
+          <t>npc_ss_loti_sad.webp</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>(base)</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -26540,13 +26570,13 @@
         </is>
       </c>
       <c r="H52" s="2" t="n">
-        <v>0.477</v>
+        <v>0.475</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1527</v>
+        <v>1523</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -26555,7 +26585,7 @@
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_loti_ask.webp</t>
+          <t>resources/si/npc/npc_ss_loti_sad.webp</t>
         </is>
       </c>
     </row>
@@ -26567,12 +26597,12 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_loti_cry.webp</t>
+          <t>npc_ss_loti_shock.webp</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>cry</t>
+          <t>shock</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -26587,13 +26617,13 @@
         </is>
       </c>
       <c r="H53" s="2" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1520</v>
+        <v>1530</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
@@ -26602,24 +26632,24 @@
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_loti_cry.webp</t>
+          <t>resources/si/npc/npc_ss_loti_shock.webp</t>
         </is>
       </c>
     </row>
     <row r="54" ht="111" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>小女孩</t>
+          <t>少女</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_loti_give.webp</t>
+          <t>npc_ss_lofa_complain.webp</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>give</t>
+          <t>complain</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -26634,13 +26664,13 @@
         </is>
       </c>
       <c r="H54" s="2" t="n">
-        <v>0.463</v>
+        <v>0.488</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -26649,24 +26679,24 @@
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_loti_give.webp</t>
+          <t>resources/si/npc/npc_ss_lofa_complain.webp</t>
         </is>
       </c>
     </row>
     <row r="55" ht="111" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>小女孩</t>
+          <t>少女</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_loti_guard.webp</t>
+          <t>npc_ss_lofa_cry.webp</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>guard</t>
+          <t>cry</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -26681,39 +26711,39 @@
         </is>
       </c>
       <c r="H55" s="2" t="n">
-        <v>0.51</v>
+        <v>0.464</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1529</v>
+        <v>1525</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>1024×1536</t>
+          <t>1024×1535</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_loti_guard.webp</t>
+          <t>resources/si/npc/npc_ss_lofa_cry.webp</t>
         </is>
       </c>
     </row>
     <row r="56" ht="111" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>小女孩</t>
+          <t>少女</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_loti_happy.webp</t>
+          <t>npc_ss_lofa_cryhug.webp</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>cryhug</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -26728,13 +26758,13 @@
         </is>
       </c>
       <c r="H56" s="2" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.594</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1523</v>
+        <v>1530</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -26743,24 +26773,24 @@
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_loti_happy.webp</t>
+          <t>resources/si/npc/npc_ss_lofa_cryhug.webp</t>
         </is>
       </c>
     </row>
     <row r="57" ht="111" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>小女孩</t>
+          <t>少女</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_loti_sad.webp</t>
+          <t>npc_ss_lofa_front.webp</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>sad</t>
+          <t>(base)</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -26775,13 +26805,13 @@
         </is>
       </c>
       <c r="H57" s="2" t="n">
-        <v>0.475</v>
+        <v>0.431</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1523</v>
+        <v>1529</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
@@ -26790,24 +26820,24 @@
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_loti_sad.webp</t>
+          <t>resources/si/npc/npc_ss_lofa_front.webp</t>
         </is>
       </c>
     </row>
     <row r="58" ht="111" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>小女孩</t>
+          <t>少女</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_loti_shock.webp</t>
+          <t>npc_ss_lofa_lookaway.webp</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>shock</t>
+          <t>lookaway</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -26822,13 +26852,13 @@
         </is>
       </c>
       <c r="H58" s="2" t="n">
-        <v>0.461</v>
+        <v>0.454</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1530</v>
+        <v>1523</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
@@ -26837,7 +26867,7 @@
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_loti_shock.webp</t>
+          <t>resources/si/npc/npc_ss_lofa_lookaway.webp</t>
         </is>
       </c>
     </row>
@@ -26849,12 +26879,12 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_lofa_complain.webp</t>
+          <t>npc_ss_lofa_talk.webp</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>complain</t>
+          <t>talk</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -26869,13 +26899,13 @@
         </is>
       </c>
       <c r="H59" s="2" t="n">
-        <v>0.488</v>
+        <v>0.464</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
@@ -26884,24 +26914,24 @@
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_lofa_complain.webp</t>
+          <t>resources/si/npc/npc_ss_lofa_talk.webp</t>
         </is>
       </c>
     </row>
     <row r="60" ht="111" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>少女</t>
+          <t>店主</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_lofa_cry.webp</t>
+          <t>npc_capital_gunstore_si.webp</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>cry</t>
+          <t>(base)</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -26916,39 +26946,39 @@
         </is>
       </c>
       <c r="H60" s="2" t="n">
-        <v>0.464</v>
+        <v>0.476</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1525</v>
+        <v>1531</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>1024×1535</t>
+          <t>1024×1536</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_lofa_cry.webp</t>
+          <t>resources/si/npc/npc_capital_gunstore_si.webp</t>
         </is>
       </c>
     </row>
     <row r="61" ht="111" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>少女</t>
+          <t>店主</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_lofa_cryhug.webp</t>
+          <t>npc_grocer_si_v1.webp</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>cryhug</t>
+          <t>(base)</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -26956,20 +26986,24 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F61" s="3" t="n"/>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>4 張：npc_grocer_si_v2.webp、npc_grocer_si_v3.webp、npc_grocer_si_v4.webp…</t>
+        </is>
+      </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
           <t>量</t>
         </is>
       </c>
       <c r="H61" s="2" t="n">
-        <v>0.594</v>
+        <v>0.442</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1530</v>
+        <v>1527</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
@@ -26978,19 +27012,19 @@
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_lofa_cryhug.webp</t>
+          <t>resources/si/npc/npc_grocer_si_v1.webp</t>
         </is>
       </c>
     </row>
     <row r="62" ht="111" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>少女</t>
+          <t>店主</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_lofa_front.webp</t>
+          <t>npc_grocerie_si.webp</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -27010,13 +27044,13 @@
         </is>
       </c>
       <c r="H62" s="2" t="n">
-        <v>0.431</v>
+        <v>0.434</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1529</v>
+        <v>1533</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
@@ -27025,24 +27059,24 @@
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_lofa_front.webp</t>
+          <t>resources/si/npc/npc_grocerie_si.webp</t>
         </is>
       </c>
     </row>
     <row r="63" ht="111" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>少女</t>
+          <t>店主</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_lofa_lookaway.webp</t>
+          <t>npc_grocery_si_northport.webp</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>lookaway</t>
+          <t>(base)</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -27057,13 +27091,13 @@
         </is>
       </c>
       <c r="H63" s="2" t="n">
-        <v>0.454</v>
+        <v>0.515</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1523</v>
+        <v>1531</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
@@ -27072,24 +27106,24 @@
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_lofa_lookaway.webp</t>
+          <t>resources/si/npc/npc_grocery_si_northport.webp</t>
         </is>
       </c>
     </row>
     <row r="64" ht="111" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>少女</t>
+          <t>店主</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_lofa_talk.webp</t>
+          <t>npc_gunsmith_si_northport.webp</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>talk</t>
+          <t>(base)</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -27104,13 +27138,13 @@
         </is>
       </c>
       <c r="H64" s="2" t="n">
-        <v>0.464</v>
+        <v>0.547</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1530</v>
+        <v>1524</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
@@ -27119,7 +27153,7 @@
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_lofa_talk.webp</t>
+          <t>resources/si/npc/npc_gunsmith_si_northport.webp</t>
         </is>
       </c>
     </row>
@@ -27131,7 +27165,7 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>npc_capital_gunstore_si.webp</t>
+          <t>npc_gunsmith_si_v1.webp</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -27144,20 +27178,24 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F65" s="3" t="n"/>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>4 張：npc_gunsmith_si_v2.webp、npc_gunsmith_si_v3.webp、npc_gunsmith_si_v4.webp…</t>
+        </is>
+      </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
           <t>量</t>
         </is>
       </c>
       <c r="H65" s="2" t="n">
-        <v>0.476</v>
+        <v>0.546</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1531</v>
+        <v>1506</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
@@ -27166,19 +27204,19 @@
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_capital_gunstore_si.webp</t>
+          <t>resources/si/npc/npc_gunsmith_si_v1.webp</t>
         </is>
       </c>
     </row>
     <row r="66" ht="111" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>店主</t>
+          <t>指揮官</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>npc_grocer_si_v1.webp</t>
+          <t>npc_commander_si_front.webp</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -27191,24 +27229,20 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>4 張：npc_grocer_si_v2.webp、npc_grocer_si_v3.webp、npc_grocer_si_v4.webp…</t>
-        </is>
-      </c>
+      <c r="F66" s="3" t="n"/>
       <c r="G66" s="2" t="inlineStr">
         <is>
           <t>量</t>
         </is>
       </c>
       <c r="H66" s="2" t="n">
-        <v>0.442</v>
+        <v>0.53</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
@@ -27217,19 +27251,19 @@
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_grocer_si_v1.webp</t>
+          <t>resources/si/npc/npc_commander_si_front.webp</t>
         </is>
       </c>
     </row>
     <row r="67" ht="111" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>店主</t>
+          <t>村民</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>npc_grocerie_si.webp</t>
+          <t>npc_shinier_grocery_si.webp</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -27249,13 +27283,13 @@
         </is>
       </c>
       <c r="H67" s="2" t="n">
-        <v>0.434</v>
+        <v>0.542</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1533</v>
+        <v>1530</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
@@ -27264,19 +27298,19 @@
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_grocerie_si.webp</t>
+          <t>resources/si/npc/npc_shinier_grocery_si.webp</t>
         </is>
       </c>
     </row>
     <row r="68" ht="111" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>店主</t>
+          <t>村民</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>npc_grocery_si_northport.webp</t>
+          <t>npc_shinier_gunsmith_si.webp</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -27296,10 +27330,10 @@
         </is>
       </c>
       <c r="H68" s="2" t="n">
-        <v>0.515</v>
+        <v>0.603</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="J68" s="2" t="n">
         <v>1531</v>
@@ -27311,19 +27345,19 @@
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_grocery_si_northport.webp</t>
+          <t>resources/si/npc/npc_shinier_gunsmith_si.webp</t>
         </is>
       </c>
     </row>
     <row r="69" ht="111" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>店主</t>
+          <t>村民</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>npc_gunsmith_si_northport.webp</t>
+          <t>npc_shinier_hunter_si.webp</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -27343,10 +27377,10 @@
         </is>
       </c>
       <c r="H69" s="2" t="n">
-        <v>0.547</v>
+        <v>0.421</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J69" s="2" t="n">
         <v>1524</v>
@@ -27358,19 +27392,19 @@
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_gunsmith_si_northport.webp</t>
+          <t>resources/si/npc/npc_shinier_hunter_si.webp</t>
         </is>
       </c>
     </row>
     <row r="70" ht="111" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>店主</t>
+          <t>村長</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>npc_gunsmith_si_v1.webp</t>
+          <t>npc_shinier_chief_si.webp</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -27383,24 +27417,20 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t>4 張：npc_gunsmith_si_v2.webp、npc_gunsmith_si_v3.webp、npc_gunsmith_si_v4.webp…</t>
-        </is>
-      </c>
+      <c r="F70" s="3" t="n"/>
       <c r="G70" s="2" t="inlineStr">
         <is>
           <t>量</t>
         </is>
       </c>
       <c r="H70" s="2" t="n">
-        <v>0.546</v>
+        <v>0.537</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1506</v>
+        <v>1520</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
@@ -27409,19 +27439,19 @@
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_gunsmith_si_v1.webp</t>
+          <t>resources/si/npc/npc_shinier_chief_si.webp</t>
         </is>
       </c>
     </row>
     <row r="71" ht="111" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>村民</t>
+          <t>櫃台</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>npc_shinier_grocery_si.webp</t>
+          <t>guildcounterca_si.webp</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -27441,13 +27471,13 @@
         </is>
       </c>
       <c r="H71" s="2" t="n">
-        <v>0.542</v>
+        <v>0.511</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1530</v>
+        <v>1526</v>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
@@ -27456,19 +27486,19 @@
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_shinier_grocery_si.webp</t>
+          <t>resources/si/guildcounterca_si.webp</t>
         </is>
       </c>
     </row>
     <row r="72" ht="111" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>村民</t>
+          <t>櫃台</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>npc_shinier_gunsmith_si.webp</t>
+          <t>npc_guildcounter_si_northport.webp</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -27488,13 +27518,13 @@
         </is>
       </c>
       <c r="H72" s="2" t="n">
-        <v>0.603</v>
+        <v>0.49</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1531</v>
+        <v>1522</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
@@ -27503,19 +27533,19 @@
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_shinier_gunsmith_si.webp</t>
+          <t>resources/si/npc/npc_guildcounter_si_northport.webp</t>
         </is>
       </c>
     </row>
     <row r="73" ht="111" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>村民</t>
+          <t>櫃台</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>npc_shinier_hunter_si.webp</t>
+          <t>npc_guildcounter_si_v5.webp</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -27528,20 +27558,24 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F73" s="3" t="n"/>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>3 張：npc_guildcounter_si_v1.webp、npc_guildcounter_si_v3.webp、npc_guildcounter_si_v4.webp</t>
+        </is>
+      </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
           <t>量</t>
         </is>
       </c>
       <c r="H73" s="2" t="n">
-        <v>0.421</v>
+        <v>0.492</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1524</v>
+        <v>1531</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
@@ -27550,24 +27584,24 @@
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_shinier_hunter_si.webp</t>
+          <t>resources/si/npc/npc_guildcounter_si_v5.webp</t>
         </is>
       </c>
     </row>
     <row r="74" ht="111" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>村長</t>
+          <t>櫃台</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>npc_shinier_chief_si.webp</t>
+          <t>npc_ss_cityhall_cringe.webp</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>(base)</t>
+          <t>cringe</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -27582,10 +27616,10 @@
         </is>
       </c>
       <c r="H74" s="2" t="n">
-        <v>0.537</v>
+        <v>0.494</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>1520</v>
@@ -27597,7 +27631,7 @@
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_shinier_chief_si.webp</t>
+          <t>resources/si/npc/npc_ss_cityhall_cringe.webp</t>
         </is>
       </c>
     </row>
@@ -27609,7 +27643,7 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>guildcounterca_si.webp</t>
+          <t>npc_ss_cityhall_front.webp</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -27629,13 +27663,13 @@
         </is>
       </c>
       <c r="H75" s="2" t="n">
-        <v>0.511</v>
+        <v>0.582</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1526</v>
+        <v>1511</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
@@ -27644,19 +27678,19 @@
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>resources/si/guildcounterca_si.webp</t>
+          <t>resources/si/npc/npc_ss_cityhall_front.webp</t>
         </is>
       </c>
     </row>
     <row r="76" ht="111" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>櫃台</t>
+          <t>獵人</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>npc_guildcounter_si_northport.webp</t>
+          <t>npc_ep_si_bounty.webp</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -27676,13 +27710,13 @@
         </is>
       </c>
       <c r="H76" s="2" t="n">
-        <v>0.49</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1522</v>
+        <v>1535</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
@@ -27691,19 +27725,19 @@
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_guildcounter_si_northport.webp</t>
+          <t>resources/si/npc/npc_ep_si_bounty.webp</t>
         </is>
       </c>
     </row>
     <row r="77" ht="111" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>櫃台</t>
+          <t>獵人</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>npc_guildcounter_si_v5.webp</t>
+          <t>npc_guildhunter_si.webp</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -27716,24 +27750,20 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F77" s="3" t="inlineStr">
-        <is>
-          <t>3 張：npc_guildcounter_si_v1.webp、npc_guildcounter_si_v3.webp、npc_guildcounter_si_v4.webp</t>
-        </is>
-      </c>
+      <c r="F77" s="3" t="n"/>
       <c r="G77" s="2" t="inlineStr">
         <is>
           <t>量</t>
         </is>
       </c>
       <c r="H77" s="2" t="n">
-        <v>0.492</v>
+        <v>0.485</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
@@ -27742,24 +27772,24 @@
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_guildcounter_si_v5.webp</t>
+          <t>resources/si/npc/npc_guildhunter_si.webp</t>
         </is>
       </c>
     </row>
     <row r="78" ht="111" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>櫃台</t>
+          <t>獵人</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_cityhall_cringe.webp</t>
+          <t>npc_guildhunter_si_attack.webp</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>cringe</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -27774,13 +27804,13 @@
         </is>
       </c>
       <c r="H78" s="2" t="n">
-        <v>0.494</v>
+        <v>0.546</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1520</v>
+        <v>1535</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
@@ -27789,24 +27819,24 @@
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_cityhall_cringe.webp</t>
+          <t>resources/si/npc/npc_guildhunter_si_attack.webp</t>
         </is>
       </c>
     </row>
     <row r="79" ht="111" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>櫃台</t>
+          <t>獵人</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_cityhall_front.webp</t>
+          <t>npc_guildhunter_si_lost.webp</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>(base)</t>
+          <t>lost</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -27821,13 +27851,13 @@
         </is>
       </c>
       <c r="H79" s="2" t="n">
-        <v>0.582</v>
+        <v>0.487</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1511</v>
+        <v>1529</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
@@ -27836,7 +27866,7 @@
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_cityhall_front.webp</t>
+          <t>resources/si/npc/npc_guildhunter_si_lost.webp</t>
         </is>
       </c>
     </row>
@@ -27848,12 +27878,12 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>npc_ep_si_bounty.webp</t>
+          <t>npc_guildhunter_si_shock.webp</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>(base)</t>
+          <t>shock</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -27868,10 +27898,10 @@
         </is>
       </c>
       <c r="H80" s="2" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.453</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J80" s="2" t="n">
         <v>1535</v>
@@ -27883,19 +27913,19 @@
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ep_si_bounty.webp</t>
+          <t>resources/si/npc/npc_guildhunter_si_shock.webp</t>
         </is>
       </c>
     </row>
     <row r="81" ht="111" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>獵人</t>
+          <t>瑪麗亞</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>npc_guildhunter_si.webp</t>
+          <t>npc_shinier_cook_si.webp</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -27915,13 +27945,13 @@
         </is>
       </c>
       <c r="H81" s="2" t="n">
-        <v>0.485</v>
+        <v>0.463</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1529</v>
+        <v>1522</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
@@ -27930,24 +27960,24 @@
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_guildhunter_si.webp</t>
+          <t>resources/si/npc/npc_shinier_cook_si.webp</t>
         </is>
       </c>
     </row>
     <row r="82" ht="111" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>獵人</t>
+          <t>科爾文</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>npc_guildhunter_si_attack.webp</t>
+          <t>corvin_si_ecstasy.webp</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>attack</t>
+          <t>ecstasy</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -27962,13 +27992,13 @@
         </is>
       </c>
       <c r="H82" s="2" t="n">
-        <v>0.546</v>
+        <v>0.443</v>
       </c>
       <c r="I82" s="2" t="n">
         <v>0</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1535</v>
+        <v>1525</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
@@ -27977,24 +28007,24 @@
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_guildhunter_si_attack.webp</t>
+          <t>resources/si/npc/corvin_si_ecstasy.webp</t>
         </is>
       </c>
     </row>
     <row r="83" ht="111" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>獵人</t>
+          <t>科爾文</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>npc_guildhunter_si_lost.webp</t>
+          <t>corvin_si_front.webp</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>lost</t>
+          <t>(base)</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -28009,13 +28039,13 @@
         </is>
       </c>
       <c r="H83" s="2" t="n">
-        <v>0.487</v>
+        <v>0.459</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
@@ -28024,24 +28054,24 @@
       </c>
       <c r="L83" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_guildhunter_si_lost.webp</t>
+          <t>resources/si/npc/corvin_si_front.webp</t>
         </is>
       </c>
     </row>
     <row r="84" ht="111" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>獵人</t>
+          <t>科爾文</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>npc_guildhunter_si_shock.webp</t>
+          <t>corvin_si_lookaside.webp</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>shock</t>
+          <t>lookaside</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -28056,13 +28086,13 @@
         </is>
       </c>
       <c r="H84" s="2" t="n">
-        <v>0.453</v>
+        <v>0.501</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
@@ -28071,24 +28101,24 @@
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_guildhunter_si_shock.webp</t>
+          <t>resources/si/npc/corvin_si_lookaside.webp</t>
         </is>
       </c>
     </row>
     <row r="85" ht="111" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>瑪麗亞</t>
+          <t>科爾文</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>npc_shinier_cook_si.webp</t>
+          <t>corvin_si_read.webp</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>(base)</t>
+          <t>read</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -28103,13 +28133,13 @@
         </is>
       </c>
       <c r="H85" s="2" t="n">
-        <v>0.463</v>
+        <v>0.459</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1522</v>
+        <v>1532</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
@@ -28118,7 +28148,7 @@
       </c>
       <c r="L85" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_shinier_cook_si.webp</t>
+          <t>resources/si/npc/corvin_si_read.webp</t>
         </is>
       </c>
     </row>
@@ -28130,12 +28160,12 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>corvin_si_ecstasy.webp</t>
+          <t>corvin_si_shock.webp</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>ecstasy</t>
+          <t>shock</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -28150,13 +28180,13 @@
         </is>
       </c>
       <c r="H86" s="2" t="n">
-        <v>0.443</v>
+        <v>0.462</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1525</v>
+        <v>1533</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
@@ -28165,7 +28195,7 @@
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/corvin_si_ecstasy.webp</t>
+          <t>resources/si/npc/corvin_si_shock.webp</t>
         </is>
       </c>
     </row>
@@ -28177,12 +28207,12 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>corvin_si_front.webp</t>
+          <t>corvin_si_smile.webp</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>(base)</t>
+          <t>smile</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -28197,13 +28227,13 @@
         </is>
       </c>
       <c r="H87" s="2" t="n">
-        <v>0.459</v>
+        <v>0.451</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
@@ -28212,7 +28242,7 @@
       </c>
       <c r="L87" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/corvin_si_front.webp</t>
+          <t>resources/si/npc/corvin_si_smile.webp</t>
         </is>
       </c>
     </row>
@@ -28224,12 +28254,12 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>corvin_si_lookaside.webp</t>
+          <t>corvin_si_stare.webp</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>lookaside</t>
+          <t>stare</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -28244,13 +28274,13 @@
         </is>
       </c>
       <c r="H88" s="2" t="n">
-        <v>0.501</v>
+        <v>0.455</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
@@ -28259,7 +28289,7 @@
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/corvin_si_lookaside.webp</t>
+          <t>resources/si/npc/corvin_si_stare.webp</t>
         </is>
       </c>
     </row>
@@ -28271,12 +28301,12 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>corvin_si_read.webp</t>
+          <t>corvin_si_talk.webp</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>talk</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -28297,7 +28327,7 @@
         <v>6</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
@@ -28306,7 +28336,7 @@
       </c>
       <c r="L89" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/corvin_si_read.webp</t>
+          <t>resources/si/npc/corvin_si_talk.webp</t>
         </is>
       </c>
     </row>
@@ -28318,12 +28348,12 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>corvin_si_shock.webp</t>
+          <t>corvin_si_think.webp</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>shock</t>
+          <t>think</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -28338,13 +28368,13 @@
         </is>
       </c>
       <c r="H90" s="2" t="n">
-        <v>0.462</v>
+        <v>0.45</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1533</v>
+        <v>1530</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
@@ -28353,24 +28383,24 @@
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/corvin_si_shock.webp</t>
+          <t>resources/si/npc/corvin_si_think.webp</t>
         </is>
       </c>
     </row>
     <row r="91" ht="111" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>科爾文</t>
+          <t>群眾</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>corvin_si_smile.webp</t>
+          <t>npc_northport_crowd.webp</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>smile</t>
+          <t>(base)</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -28385,13 +28415,13 @@
         </is>
       </c>
       <c r="H91" s="2" t="n">
-        <v>0.451</v>
+        <v>0.37</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
@@ -28400,24 +28430,24 @@
       </c>
       <c r="L91" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/corvin_si_smile.webp</t>
+          <t>resources/si/npc/npc_northport_crowd.webp</t>
         </is>
       </c>
     </row>
     <row r="92" ht="111" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>科爾文</t>
+          <t>謎之術師</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>corvin_si_stare.webp</t>
+          <t>mage_si_barrier.webp</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>stare</t>
+          <t>barrier</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -28432,13 +28462,13 @@
         </is>
       </c>
       <c r="H92" s="2" t="n">
-        <v>0.455</v>
+        <v>0.43</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
@@ -28447,71 +28477,66 @@
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/corvin_si_stare.webp</t>
+          <t>resources/si/npc/mage_si_barrier.webp</t>
         </is>
       </c>
     </row>
     <row r="93" ht="111" customHeight="1">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>科爾文</t>
-        </is>
-      </c>
-      <c r="C93" s="3" t="inlineStr">
-        <is>
-          <t>corvin_si_talk.webp</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>talk</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F93" s="3" t="n"/>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>量</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="n">
-        <v>0.459</v>
-      </c>
-      <c r="I93" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J93" s="2" t="n">
-        <v>1531</v>
-      </c>
-      <c r="K93" s="2" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L93" s="3" t="inlineStr">
-        <is>
-          <t>resources/si/npc/corvin_si_talk.webp</t>
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>謎之術師</t>
+        </is>
+      </c>
+      <c r="B93" s="5" t="n"/>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>mage_si_cast.webp</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>✘ 未接線</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="n"/>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>估</t>
+        </is>
+      </c>
+      <c r="H93" s="4" t="n"/>
+      <c r="I93" s="4" t="n"/>
+      <c r="J93" s="4" t="n"/>
+      <c r="K93" s="4" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L93" s="6" t="inlineStr">
+        <is>
+          <t>resources/si/npc/mage_si_cast.webp</t>
         </is>
       </c>
     </row>
     <row r="94" ht="111" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>科爾文</t>
+          <t>謎之術師</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>corvin_si_think.webp</t>
+          <t>mage_si_front.webp</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>think</t>
+          <t>(base)</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -28526,10 +28551,10 @@
         </is>
       </c>
       <c r="H94" s="2" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J94" s="2" t="n">
         <v>1530</v>
@@ -28541,24 +28566,24 @@
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/corvin_si_think.webp</t>
+          <t>resources/si/npc/mage_si_front.webp</t>
         </is>
       </c>
     </row>
     <row r="95" ht="111" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>群眾</t>
+          <t>謎之術師</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>npc_northport_crowd.webp</t>
+          <t>mage_si_hurt.webp</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>(base)</t>
+          <t>hurt</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -28573,13 +28598,13 @@
         </is>
       </c>
       <c r="H95" s="2" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1527</v>
+        <v>1514</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
@@ -28588,7 +28613,7 @@
       </c>
       <c r="L95" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_northport_crowd.webp</t>
+          <t>resources/si/npc/mage_si_hurt.webp</t>
         </is>
       </c>
     </row>
@@ -29121,7 +29146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D145"/>
+  <dimension ref="A1:D137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -29231,7 +29256,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>anya_si_sad.webp</t>
+          <t>anya_si_side.webp</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -29248,12 +29273,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Anya</t>
+          <t>Luna</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>anya_si_shakehead.webp</t>
+          <t>luna_si_front.webp</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -29270,12 +29295,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Anya</t>
+          <t>Luna</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>anya_si_side.webp</t>
+          <t>luna_si_seat_lookdown.webp</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -29292,12 +29317,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Nouvelle_nun</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cecilie_si_teary.webp</t>
+          <t>nouvelle_nun_si_front.webp</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -29314,12 +29339,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Luna</t>
+          <t>Nouvelle</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>luna_si_front.webp</t>
+          <t>nouvelle_si_back.webp</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -29336,12 +29361,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Luna</t>
+          <t>Nouvelle</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>luna_si_seat_lookdown.webp</t>
+          <t>nouvelle_si_bye.webp</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -29358,12 +29383,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nouvelle_nun</t>
+          <t>Nouvelle</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nouvelle_nun_si_front.webp</t>
+          <t>nouvelle_si_expainsweat.webp</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -29385,7 +29410,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nouvelle_si_back.webp</t>
+          <t>nouvelle_si_meetagain.webp</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -29407,7 +29432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>nouvelle_si_bye.webp</t>
+          <t>nouvelle_si_reliefbreath.webp</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -29429,7 +29454,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>nouvelle_si_expainsweat.webp</t>
+          <t>nouvelle_si_scare.webp</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -29451,7 +29476,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>nouvelle_si_meetagain.webp</t>
+          <t>nouvelle_si_side.webp</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -29468,12 +29493,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nouvelle</t>
+          <t>Npc_aaron</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>nouvelle_si_reliefbreath.webp</t>
+          <t>npc_aaron_si_trial.png</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -29490,12 +29515,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nouvelle</t>
+          <t>Npc_molly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>nouvelle_si_runcry.webp</t>
+          <t>npc_molly_si_trial.png</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -29512,12 +29537,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nouvelle</t>
+          <t>Npc_robert</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>nouvelle_si_scare.webp</t>
+          <t>npc_robert_si_trial.png</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -29534,12 +29559,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nouvelle</t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>nouvelle_si_side.webp</t>
+          <t>aaron_si_angry.webp</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -29556,12 +29581,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Npc_aaron</t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>npc_aaron_si_trial.png</t>
+          <t>aaron_si_armscross.webp</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -29578,12 +29603,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Npc_molly</t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>npc_molly_si_trial.png</t>
+          <t>aaron_si_attention.webp</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -29600,12 +29625,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Npc_robert</t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>npc_robert_si_trial.png</t>
+          <t>aaron_si_blindeye.webp</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -29627,7 +29652,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>aaron_si_angry.webp</t>
+          <t>aaron_si_closedsmile.webp</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -29649,7 +29674,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>aaron_si_armscross.webp</t>
+          <t>aaron_si_confused.webp</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -29671,7 +29696,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>aaron_si_attention.webp</t>
+          <t>aaron_si_draw.webp</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -29693,7 +29718,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>aaron_si_blindeye.webp</t>
+          <t>aaron_si_front.webp</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -29715,7 +29740,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>aaron_si_closedsmile.webp</t>
+          <t>aaron_si_signal.webp</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -29732,12 +29757,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Church_guard</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>aaron_si_confused.webp</t>
+          <t>church_guard_si_a.webp</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -29754,12 +29779,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Church_guard</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>aaron_si_draw.webp</t>
+          <t>church_guard_si_b.webp</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -29776,12 +29801,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Church_guard</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>aaron_si_front.webp</t>
+          <t>church_guard_si_c.webp</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -29798,12 +29823,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Church_guard</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>aaron_si_signal.webp</t>
+          <t>church_guard_si_d.webp</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -29825,7 +29850,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>church_guard_si_a.webp</t>
+          <t>church_guard_si_e.webp</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -29847,7 +29872,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>church_guard_si_b.webp</t>
+          <t>church_guard_si_f.webp</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -29864,12 +29889,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Church_guard</t>
+          <t>f734e7ba-e7bb-457b-8cf7-66e13324c45d</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>church_guard_si_c.webp</t>
+          <t>f734e7ba-e7bb-457b-8cf7-66e13324c45d.png</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -29886,12 +29911,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Church_guard</t>
+          <t>Mage</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>church_guard_si_d.webp</t>
+          <t>mage_si_cast.webp</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -29908,12 +29933,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Church_guard</t>
+          <t>Molly</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>church_guard_si_e.webp</t>
+          <t>molly_si_ask.webp</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -29930,12 +29955,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Church_guard</t>
+          <t>Molly</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>church_guard_si_f.webp</t>
+          <t>molly_si_closedtalk.webp</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -29952,12 +29977,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>f734e7ba-e7bb-457b-8cf7-66e13324c45d</t>
+          <t>Molly</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>f734e7ba-e7bb-457b-8cf7-66e13324c45d.png</t>
+          <t>molly_si_eyesmile.webp</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -29974,12 +29999,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mage</t>
+          <t>Molly</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>mage_si_barrier.webp</t>
+          <t>molly_si_front.webp</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -29996,12 +30021,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mage</t>
+          <t>Molly</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>mage_si_cast.webp</t>
+          <t>molly_si_gossip.webp</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -30018,12 +30043,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mage</t>
+          <t>Molly</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>mage_si_front.webp</t>
+          <t>molly_si_lookdown.webp</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -30040,12 +30065,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mage</t>
+          <t>Molly</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>mage_si_hurt.webp</t>
+          <t>molly_si_order.webp</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -30067,7 +30092,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>molly_si_ask.webp</t>
+          <t>molly_si_serious.webp</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -30089,7 +30114,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>molly_si_closedtalk.webp</t>
+          <t>molly_si_softsmile.webp</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -30111,7 +30136,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>molly_si_eyesmile.webp</t>
+          <t>molly_si_stern.webp</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -30133,7 +30158,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>molly_si_front.webp</t>
+          <t>molly_si_superior.webp</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -30155,7 +30180,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>molly_si_gossip.webp</t>
+          <t>molly_si_surprise.webp</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -30177,7 +30202,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>molly_si_lookdown.webp</t>
+          <t>molly_si_talk.webp</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -30199,7 +30224,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>molly_si_order.webp</t>
+          <t>molly_si_think.webp</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -30221,7 +30246,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>molly_si_serious.webp</t>
+          <t>molly_si_whisper.webp</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -30238,12 +30263,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Molly</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>molly_si_softsmile.webp</t>
+          <t>robert_si_blindeye.webp</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -30260,12 +30285,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Molly</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>molly_si_stern.webp</t>
+          <t>robert_si_bow.webp</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -30282,12 +30307,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Molly</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>molly_si_superior.webp</t>
+          <t>robert_si_closedtalk.webp</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -30304,12 +30329,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Molly</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>molly_si_surprise.webp</t>
+          <t>robert_si_front.webp</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -30326,12 +30351,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Molly</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>molly_si_talk.webp</t>
+          <t>robert_si_sideeye.webp</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -30348,12 +30373,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Molly</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>molly_si_think.webp</t>
+          <t>robert_si_surprise.webp</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -30370,12 +30395,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Molly</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>molly_si_whisper.webp</t>
+          <t>robert_si_talk.webp</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -30392,12 +30417,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Npc_commander</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>npc_commander_si_front.webp</t>
+          <t>renna_si_evalutatingclosemouth.webp</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -30414,12 +30439,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>robert_si_blindeye.webp</t>
+          <t>renna_si_annoy.webp</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -30436,12 +30461,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Sorana</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>robert_si_bow.webp</t>
+          <t>sorana_si_q.webp</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -30458,12 +30483,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>image - 2026-09-20T150615.066</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>robert_si_closedtalk.webp</t>
+          <t>image - 2026-09-20T150615.066.png</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -30480,12 +30505,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>image - 2026-09-20T150842.343</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>robert_si_front.webp</t>
+          <t>image - 2026-09-20T150842.343.png</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -30502,12 +30527,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>image - 2026-09-20T151013.881</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>robert_si_sideeye.webp</t>
+          <t>image - 2026-09-20T151013.881.png</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -30524,12 +30549,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>image - 2026-09-20T151141.942</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>robert_si_surprise.webp</t>
+          <t>image - 2026-09-20T151141.942.png</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -30546,12 +30571,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Torsten</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>robert_si_talk.webp</t>
+          <t>torsten_si_front.webp</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -30568,12 +30593,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Renna</t>
+          <t>Torsten</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>renna_si_evalutatingclosemouth.webp</t>
+          <t>torsten_si_q.webp</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -30590,12 +30615,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Renna</t>
+          <t>Xanya</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>renna_si_annoy.webp</t>
+          <t>xanya_si_front.webp</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -30607,176 +30632,176 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>美術交了沒接線</t>
+          <t>同差分的另一個版本</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sorana</t>
+          <t>Anya</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>sorana_si_q.webp</t>
+          <t>resources/si/anya_si_nod.png</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>在 script/speakers.js 的 ART 補一筆 expr，並量 fx／top／bot（§6.5）</t>
+          <t>線上跑的是 anya_si_nod.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>美術交了沒接線</t>
+          <t>同差分的另一個版本</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T150615.066</t>
+          <t>Cecilie</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T150615.066.png</t>
+          <t>resources/si/cecilie_si_saintinstall.png</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>在 script/speakers.js 的 ART 補一筆 expr，並量 fx／top／bot（§6.5）</t>
+          <t>線上跑的是 cecilie_si_saintinstall.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>美術交了沒接線</t>
+          <t>同差分的另一個版本</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T150842.343</t>
+          <t>Misha</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T150842.343.png</t>
+          <t>resources/si/misha_si_fight.png</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>在 script/speakers.js 的 ART 補一筆 expr，並量 fx／top／bot（§6.5）</t>
+          <t>線上跑的是 misha_si_fight.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>美術交了沒接線</t>
+          <t>同差分的另一個版本</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T151013.881</t>
+          <t>Misha</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T151013.881.png</t>
+          <t>resources/si/misha_si_ni.png</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>在 script/speakers.js 的 ART 補一筆 expr，並量 fx／top／bot（§6.5）</t>
+          <t>線上跑的是 misha_si_ni.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>美術交了沒接線</t>
+          <t>同差分的另一個版本</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T151141.942</t>
+          <t>Nouvelle</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T151141.942.png</t>
+          <t>resources/si/nouvelle_si_gossip1.png</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>在 script/speakers.js 的 ART 補一筆 expr，並量 fx／top／bot（§6.5）</t>
+          <t>線上跑的是 nouvelle_si_gossip1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>美術交了沒接線</t>
+          <t>同差分的另一個版本</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Torsten</t>
+          <t>Nouvelle</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>torsten_si_front.webp</t>
+          <t>resources/si/nouvelle_si_salute.png</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>在 script/speakers.js 的 ART 補一筆 expr，並量 fx／top／bot（§6.5）</t>
+          <t>線上跑的是 nouvelle_si_salute.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>美術交了沒接線</t>
+          <t>同差分的另一個版本</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Torsten</t>
+          <t>Nouvelle</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>torsten_si_q.webp</t>
+          <t>resources/si/nouvelle_si_sigh.png</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>在 script/speakers.js 的 ART 補一筆 expr，並量 fx／top／bot（§6.5）</t>
+          <t>線上跑的是 nouvelle_si_sigh.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>美術交了沒接線</t>
+          <t>同差分的另一個版本</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Xanya</t>
+          <t>Npc_grocer</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>xanya_si_front.webp</t>
+          <t>resources/si/npc/npc_grocer_si_v2.webp</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>在 script/speakers.js 的 ART 補一筆 expr，並量 fx／top／bot（§6.5）</t>
+          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -30788,17 +30813,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Anya</t>
+          <t>Npc_grocer</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>resources/si/anya_si_nod.png</t>
+          <t>resources/si/npc/npc_grocer_si_v3.webp</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>線上跑的是 anya_si_nod.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -30810,17 +30835,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Npc_grocer</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>resources/si/cecilie_si_saintinstall.png</t>
+          <t>resources/si/npc/npc_grocer_si_v4.webp</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_saintinstall.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -30832,17 +30857,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Misha</t>
+          <t>Npc_grocer</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>resources/si/misha_si_fight.png</t>
+          <t>resources/si/npc/npc_grocer_si_v5.webp</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>線上跑的是 misha_si_fight.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -30854,17 +30879,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Misha</t>
+          <t>Npc_guildcounter</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>resources/si/misha_si_ni.png</t>
+          <t>resources/si/npc/npc_guildcounter_si_v1.webp</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>線上跑的是 misha_si_ni.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_guildcounter_si_v5.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -30876,17 +30901,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Nouvelle</t>
+          <t>Npc_guildcounter</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>resources/si/nouvelle_si_gossip1.png</t>
+          <t>resources/si/npc/npc_guildcounter_si_v3.webp</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>線上跑的是 nouvelle_si_gossip1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_guildcounter_si_v5.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -30898,17 +30923,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Nouvelle</t>
+          <t>Npc_guildcounter</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>resources/si/nouvelle_si_salute.png</t>
+          <t>resources/si/npc/npc_guildcounter_si_v4.webp</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>線上跑的是 nouvelle_si_salute.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_guildcounter_si_v5.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -30920,17 +30945,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Nouvelle</t>
+          <t>Npc_gunsmith</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>resources/si/nouvelle_si_sigh.png</t>
+          <t>resources/si/npc/npc_gunsmith_si_v2.webp</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>線上跑的是 nouvelle_si_sigh.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -30942,17 +30967,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Npc_grocer</t>
+          <t>Npc_gunsmith</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_grocer_si_v2.webp</t>
+          <t>resources/si/npc/npc_gunsmith_si_v3.webp</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -30964,17 +30989,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Npc_grocer</t>
+          <t>Npc_gunsmith</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_grocer_si_v3.webp</t>
+          <t>resources/si/npc/npc_gunsmith_si_v4.webp</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -30986,17 +31011,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Npc_grocer</t>
+          <t>Npc_gunsmith</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_grocer_si_v4.webp</t>
+          <t>resources/si/npc/npc_gunsmith_si_v5.webp</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31008,17 +31033,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Npc_grocer</t>
+          <t>Cecilie</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_grocer_si_v5.webp</t>
+          <t>resources/si/old/cecilie_si_front.png</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_front.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31030,17 +31055,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Npc_guildcounter</t>
+          <t>Cecilie</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_guildcounter_si_v1.webp</t>
+          <t>resources/si/old/cecilie_si_lookaside.png</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_guildcounter_si_v5.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_lookaside.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31052,17 +31077,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Npc_guildcounter</t>
+          <t>Cecilie</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_guildcounter_si_v3.webp</t>
+          <t>resources/si/old/cecilie_si_sadback.png</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_guildcounter_si_v5.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_sadback.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31074,17 +31099,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Npc_guildcounter</t>
+          <t>Cecilie</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_guildcounter_si_v4.webp</t>
+          <t>resources/si/old/cecilie_si_smile.png</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_guildcounter_si_v5.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_smile.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31096,17 +31121,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Npc_gunsmith</t>
+          <t>Cecilie</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_gunsmith_si_v2.webp</t>
+          <t>resources/si/old/cecilie_si_tease.png</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_tease.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31118,17 +31143,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Npc_gunsmith</t>
+          <t>Cecilie</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_gunsmith_si_v3.webp</t>
+          <t>resources/si/old/cecilie_si_upset.png</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_upset.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31140,17 +31165,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Npc_gunsmith</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_gunsmith_si_v4.webp</t>
+          <t>resources/si/renna_newhair/renna_si_argue.webp</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_argue.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31162,17 +31187,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Npc_gunsmith</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_gunsmith_si_v5.webp</t>
+          <t>resources/si/renna_newhair/renna_si_arguecute.webp</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_arguecute.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31184,17 +31209,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_front.png</t>
+          <t>resources/si/renna_newhair/renna_si_ask.webp</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_front.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_ask.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31206,17 +31231,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_lookaside.png</t>
+          <t>resources/si/renna_newhair/renna_si_askserious.webp</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_lookaside.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_askserious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31228,17 +31253,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_sadback.png</t>
+          <t>resources/si/renna_newhair/renna_si_awkwerd.webp</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_sadback.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_awkwerd.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31250,17 +31275,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_smile.png</t>
+          <t>resources/si/renna_newhair/renna_si_blush.webp</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_smile.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_blush.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31272,17 +31297,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_tease.png</t>
+          <t>resources/si/renna_newhair/renna_si_bow.webp</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_tease.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_bow.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31294,17 +31319,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_upset.png</t>
+          <t>resources/si/renna_newhair/renna_si_callangry.webp</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_upset.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_callangry.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31321,12 +31346,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_argue.webp</t>
+          <t>resources/si/renna_newhair/renna_si_chase.webp</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_argue.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_chase.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31343,12 +31368,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_arguecute.webp</t>
+          <t>resources/si/renna_newhair/renna_si_chase2.webp</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_arguecute.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_chase2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31365,12 +31390,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_ask.webp</t>
+          <t>resources/si/renna_newhair/renna_si_command.webp</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_ask.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_command.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31387,12 +31412,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_askserious.webp</t>
+          <t>resources/si/renna_newhair/renna_si_covermouth.webp</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_askserious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_covermouth.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31409,12 +31434,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_awkwerd.webp</t>
+          <t>resources/si/renna_newhair/renna_si_cringe.webp</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_awkwerd.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_cringe.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31431,12 +31456,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_blush.webp</t>
+          <t>resources/si/renna_newhair/renna_si_curious.webp</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_blush.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_curious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31453,12 +31478,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_bow.webp</t>
+          <t>resources/si/renna_newhair/renna_si_die.webp</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_bow.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_die.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31475,12 +31500,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_callangry.webp</t>
+          <t>resources/si/renna_newhair/renna_si_evaluate.webp</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_callangry.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_evaluate.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31497,12 +31522,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_chase.webp</t>
+          <t>resources/si/renna_newhair/renna_si_front.webp</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_chase.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_front.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31519,12 +31544,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_chase2.webp</t>
+          <t>resources/si/renna_newhair/renna_si_intense.webp</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_chase2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_intense.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31541,12 +31566,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_command.webp</t>
+          <t>resources/si/renna_newhair/renna_si_intense2.webp</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_command.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_intense2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31563,12 +31588,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_covermouth.webp</t>
+          <t>resources/si/renna_newhair/renna_si_invite.webp</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_covermouth.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_invite.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31585,12 +31610,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_cringe.webp</t>
+          <t>resources/si/renna_newhair/renna_si_lookaway.webp</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_cringe.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_lookaway.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31607,12 +31632,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_curious.webp</t>
+          <t>resources/si/renna_newhair/renna_si_lookawaytalk.webp</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_curious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_lookawaytalk.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31629,12 +31654,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_die.webp</t>
+          <t>resources/si/renna_newhair/renna_si_lookdown.webp</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_die.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_lookdown.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31651,12 +31676,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_evaluate.webp</t>
+          <t>resources/si/renna_newhair/renna_si_lookup.webp</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_evaluate.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_lookup.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31673,12 +31698,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_front.webp</t>
+          <t>resources/si/renna_newhair/renna_si_pause.webp</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_front.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_pause.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31695,12 +31720,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_intense.webp</t>
+          <t>resources/si/renna_newhair/renna_si_relief.webp</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_intense.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_relief.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31717,12 +31742,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_intense2.webp</t>
+          <t>resources/si/renna_newhair/renna_si_sad.webp</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_intense2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_sad.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31739,12 +31764,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_invite.webp</t>
+          <t>resources/si/renna_newhair/renna_si_shout.webp</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_invite.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_shout.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31761,12 +31786,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_lookaway.webp</t>
+          <t>resources/si/renna_newhair/renna_si_smile.webp</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_lookaway.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_smile.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31783,12 +31808,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_lookawaytalk.webp</t>
+          <t>resources/si/renna_newhair/renna_si_stare.webp</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_lookawaytalk.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_stare.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31805,12 +31830,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_lookdown.webp</t>
+          <t>resources/si/renna_newhair/renna_si_surprise.webp</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_lookdown.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_surprise.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31827,12 +31852,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_lookup.webp</t>
+          <t>resources/si/renna_newhair/renna_si_talkserious.webp</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_lookup.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_talkserious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31849,12 +31874,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_pause.webp</t>
+          <t>resources/si/renna_newhair/renna_si_talkwork.webp</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_pause.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_talkwork.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31871,12 +31896,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_relief.webp</t>
+          <t>resources/si/renna_newhair/renna_si_think.webp</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_relief.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_think.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31893,12 +31918,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_sad.webp</t>
+          <t>resources/si/renna_newhair/renna_si_tire.webp</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_sad.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_tire.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31915,12 +31940,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_shout.webp</t>
+          <t>resources/si/renna_newhair/renna_si_upset.webp</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_shout.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_upset.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31937,12 +31962,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_smile.webp</t>
+          <t>resources/si/renna_newhair/renna_si_upsetstare.webp</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_smile.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_upsetstare.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31959,12 +31984,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_stare.webp</t>
+          <t>resources/si/renna_newhair/renna_si_wake.webp</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_stare.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_wake.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -31981,12 +32006,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_surprise.webp</t>
+          <t>resources/si/renna_newhair/renna_si_watch.webp</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_surprise.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_watch.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -32003,12 +32028,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_talkserious.webp</t>
+          <t>resources/si/renna_newhair/renna_si_worry.webp</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_talkserious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_worry.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -32025,12 +32050,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_talkwork.webp</t>
+          <t>resources/si/renna_newhair/renna_si_write.webp</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_talkwork.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_write.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -32047,12 +32072,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_think.webp</t>
+          <t>resources/si/renna_si_hug.png</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_think.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_hug.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -32069,12 +32094,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_tire.webp</t>
+          <t>resources/si/renna_si_hugangry2.png</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_tire.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_hugangry2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -32091,12 +32116,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_upset.webp</t>
+          <t>resources/si/renna_si_hugclose.png</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_upset.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_hugclose.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -32113,12 +32138,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_upsetstare.webp</t>
+          <t>resources/si/renna_si_huglookaway.png</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_upsetstare.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_huglookaway.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -32130,191 +32155,15 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Renna</t>
+          <t>Torsten</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_wake.webp</t>
+          <t>resources/si/torsten_si_back.png</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_wake.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Renna</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>resources/si/renna_newhair/renna_si_watch.webp</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_watch.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Renna</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>resources/si/renna_newhair/renna_si_worry.webp</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_worry.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Renna</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>resources/si/renna_newhair/renna_si_write.webp</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_write.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Renna</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>resources/si/renna_si_hug.png</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_hug.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Renna</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>resources/si/renna_si_hugangry2.png</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_hugangry2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Renna</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>resources/si/renna_si_hugclose.png</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_hugclose.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Renna</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>resources/si/renna_si_huglookaway.png</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_huglookaway.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Torsten</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>resources/si/torsten_si_back.png</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
         <is>
           <t>線上跑的是 torsten_si_back.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
@@ -37557,42 +37406,47 @@
       </c>
     </row>
     <row r="34" ht="111" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>安雅</t>
         </is>
       </c>
-      <c r="B34" s="5" t="n"/>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>anya_si_sad.webp</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="n"/>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="n"/>
-      <c r="I34" s="4" t="n"/>
-      <c r="J34" s="4" t="n"/>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L34" s="6" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>sad</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="n"/>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>1523</v>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
         <is>
           <t>resources/si/anya_si_sad.webp</t>
         </is>
@@ -37693,42 +37547,47 @@
       </c>
     </row>
     <row r="37" ht="111" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>安雅</t>
         </is>
       </c>
-      <c r="B37" s="5" t="n"/>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>anya_si_shakehead.webp</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F37" s="6" t="n"/>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="n"/>
-      <c r="I37" s="4" t="n"/>
-      <c r="J37" s="4" t="n"/>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L37" s="6" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>shakehead</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="n"/>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>1521</v>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
         <is>
           <t>resources/si/anya_si_shakehead.webp</t>
         </is>
@@ -40807,42 +40666,47 @@
       </c>
     </row>
     <row r="14" ht="111" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>賽西莉</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>cecilie_si_teary.webp</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n"/>
-      <c r="J14" s="4" t="n"/>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L14" s="6" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>teary</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>1531</v>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>resources/si/cecilie_si_teary.webp</t>
         </is>

--- a/resources/si/_SI_差分總表.xlsx
+++ b/resources/si/_SI_差分總表.xlsx
@@ -14,14 +14,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="米夏" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="賽西莉" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="茉莉" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="索菈娜2" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="蕾娜2" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="亞隆" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="科爾文" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="科爾文" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="索菈娜2" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="蕾娜2" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="亞隆" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="璐娜莉亞" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阿瑞尼斯" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="羅伯特" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教廷衛士" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="衛士" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="羅伯特" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="尼莫" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="蘿芮" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="馬努" sheetId="18" state="visible" r:id="rId18"/>
@@ -2916,6 +2916,31 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1333500" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -3891,6 +3916,31 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1333500" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -10021,6 +10071,56 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>78</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1333500" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="78" name="Image 78" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId78"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>79</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1333500" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="79" name="Image 79" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId79"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -13296,6 +13396,31 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1333500" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -13541,6 +13666,56 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1333500" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1333500" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -18812,7 +18987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -18892,380 +19067,472 @@
       </c>
     </row>
     <row r="2" ht="111" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Aaron</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n"/>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>aaron_si_angry.webp</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="n"/>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="n"/>
-      <c r="I2" s="4" t="n"/>
-      <c r="J2" s="4" t="n"/>
-      <c r="K2" s="4" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L2" s="6" t="inlineStr">
-        <is>
-          <t>resources/si/npc/aaron_si_angry.webp</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>蕾娜</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>renna_ad_si_bow.webp</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>ad_bow</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>1510</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/renna_ad_si_bow.webp</t>
         </is>
       </c>
     </row>
     <row r="3" ht="111" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Aaron</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>aaron_si_armscross.webp</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="n"/>
-      <c r="I3" s="4" t="n"/>
-      <c r="J3" s="4" t="n"/>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L3" s="6" t="inlineStr">
-        <is>
-          <t>resources/si/npc/aaron_si_armscross.webp</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>蕾娜</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>renna_ad_si_command.webp</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>ad_command</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>1516</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/renna_ad_si_command.webp</t>
         </is>
       </c>
     </row>
     <row r="4" ht="111" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Aaron</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>aaron_si_attention.webp</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="n"/>
-      <c r="J4" s="4" t="n"/>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>resources/si/npc/aaron_si_attention.webp</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>蕾娜</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>renna_ad_si_commandsoft.webp</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>ad_commandsoft</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>1515</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/renna_ad_si_commandsoft.webp</t>
         </is>
       </c>
     </row>
     <row r="5" ht="111" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Aaron</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>aaron_si_blindeye.webp</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>resources/si/npc/aaron_si_blindeye.webp</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>蕾娜</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>renna_ad_si_front.webp</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>ad_front</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>1524</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/renna_ad_si_front.webp</t>
         </is>
       </c>
     </row>
     <row r="6" ht="111" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Aaron</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>aaron_si_closedsmile.webp</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="4" t="n"/>
-      <c r="J6" s="4" t="n"/>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr">
-        <is>
-          <t>resources/si/npc/aaron_si_closedsmile.webp</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>蕾娜</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>renna_ad_si_lookaway.webp</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>ad_lookaway</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>1519</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/renna_ad_si_lookaway.webp</t>
         </is>
       </c>
     </row>
     <row r="7" ht="111" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Aaron</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>aaron_si_confused.webp</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L7" s="6" t="inlineStr">
-        <is>
-          <t>resources/si/npc/aaron_si_confused.webp</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>蕾娜</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>renna_ad_si_remind.webp</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>ad_remind</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>1521</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/renna_ad_si_remind.webp</t>
         </is>
       </c>
     </row>
     <row r="8" ht="111" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Aaron</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>aaron_si_draw.webp</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="n"/>
-      <c r="I8" s="4" t="n"/>
-      <c r="J8" s="4" t="n"/>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L8" s="6" t="inlineStr">
-        <is>
-          <t>resources/si/npc/aaron_si_draw.webp</t>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>蕾娜</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>renna_ad_si_smile.webp</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>ad_smile</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>1508</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/renna_ad_si_smile.webp</t>
         </is>
       </c>
     </row>
     <row r="9" ht="111" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Aaron</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>aaron_si_front.webp</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="inlineStr">
-        <is>
-          <t>resources/si/npc/aaron_si_front.webp</t>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>蕾娜</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>renna_ad_si_think.webp</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>ad_think</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>1510</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/renna_ad_si_think.webp</t>
         </is>
       </c>
     </row>
     <row r="10" ht="111" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Aaron</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>aaron_si_signal.webp</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="n"/>
-      <c r="I10" s="4" t="n"/>
-      <c r="J10" s="4" t="n"/>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L10" s="6" t="inlineStr">
-        <is>
-          <t>resources/si/npc/aaron_si_signal.webp</t>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>蕾娜</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>renna_ad_si_watch.webp</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>ad_watch</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>1515</v>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/renna_ad_si_watch.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="111" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>蕾娜</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>renna_ad_si_write.webp</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>ad_write</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>1521</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/renna_ad_si_write.webp</t>
         </is>
       </c>
     </row>
@@ -19361,425 +19628,380 @@
       </c>
     </row>
     <row r="2" ht="111" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>科爾文</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>corvin_si_ecstasy.webp</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>ecstasy</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>量</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>0.443</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>1525</v>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>resources/si/npc/corvin_si_ecstasy.webp</t>
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Aaron</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>aaron_si_angry.webp</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>✘ 未接線</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="n"/>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>估</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="4" t="n"/>
+      <c r="J2" s="4" t="n"/>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L2" s="6" t="inlineStr">
+        <is>
+          <t>resources/si/npc/aaron_si_angry.webp</t>
         </is>
       </c>
     </row>
     <row r="3" ht="111" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>科爾文</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>corvin_si_front.webp</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>(base)</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>量</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>0.459</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>1528</v>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>resources/si/npc/corvin_si_front.webp</t>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Aaron</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>aaron_si_armscross.webp</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>✘ 未接線</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>估</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>resources/si/npc/aaron_si_armscross.webp</t>
         </is>
       </c>
     </row>
     <row r="4" ht="111" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>科爾文</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>corvin_si_lookaside.webp</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>lookaside</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>量</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>0.501</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>1533</v>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>resources/si/npc/corvin_si_lookaside.webp</t>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Aaron</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>aaron_si_attention.webp</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>✘ 未接線</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>估</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>resources/si/npc/aaron_si_attention.webp</t>
         </is>
       </c>
     </row>
     <row r="5" ht="111" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>科爾文</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>corvin_si_read.webp</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>量</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>0.459</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>1532</v>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>resources/si/npc/corvin_si_read.webp</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Aaron</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>aaron_si_blindeye.webp</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>✘ 未接線</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>估</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>resources/si/npc/aaron_si_blindeye.webp</t>
         </is>
       </c>
     </row>
     <row r="6" ht="111" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>科爾文</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>corvin_si_shock.webp</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>shock</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>量</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>1533</v>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>resources/si/npc/corvin_si_shock.webp</t>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Aaron</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>aaron_si_closedsmile.webp</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>✘ 未接線</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>估</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>resources/si/npc/aaron_si_closedsmile.webp</t>
         </is>
       </c>
     </row>
     <row r="7" ht="111" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>科爾文</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>corvin_si_smile.webp</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>smile</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>量</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>0.451</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>1529</v>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>resources/si/npc/corvin_si_smile.webp</t>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Aaron</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>aaron_si_confused.webp</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>✘ 未接線</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>估</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="n"/>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="4" t="n"/>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>resources/si/npc/aaron_si_confused.webp</t>
         </is>
       </c>
     </row>
     <row r="8" ht="111" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>科爾文</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>corvin_si_stare.webp</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>stare</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>量</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>1531</v>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>resources/si/npc/corvin_si_stare.webp</t>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Aaron</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>aaron_si_draw.webp</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>✘ 未接線</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>估</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="n"/>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="4" t="n"/>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>resources/si/npc/aaron_si_draw.webp</t>
         </is>
       </c>
     </row>
     <row r="9" ht="111" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>科爾文</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>corvin_si_talk.webp</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>talk</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>量</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0.459</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>1531</v>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>resources/si/npc/corvin_si_talk.webp</t>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Aaron</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>aaron_si_front.webp</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>✘ 未接線</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>估</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="n"/>
+      <c r="I9" s="4" t="n"/>
+      <c r="J9" s="4" t="n"/>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>resources/si/npc/aaron_si_front.webp</t>
         </is>
       </c>
     </row>
     <row r="10" ht="111" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>科爾文</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>corvin_si_think.webp</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>think</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>量</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>1530</v>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>resources/si/npc/corvin_si_think.webp</t>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Aaron</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>aaron_si_signal.webp</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>✘ 未接線</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>估</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="n"/>
+      <c r="I10" s="4" t="n"/>
+      <c r="J10" s="4" t="n"/>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>resources/si/npc/aaron_si_signal.webp</t>
         </is>
       </c>
     </row>
@@ -20801,13 +21023,13 @@
     <row r="2" ht="111" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Church_guard</t>
         </is>
       </c>
       <c r="B2" s="5" t="n"/>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>robert_si_blindeye.webp</t>
+          <t>church_guard_si_a.webp</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -20836,20 +21058,20 @@
       </c>
       <c r="L2" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/robert_si_blindeye.webp</t>
+          <t>resources/si/npc/church_guard_si_a.webp</t>
         </is>
       </c>
     </row>
     <row r="3" ht="111" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Church_guard</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>robert_si_bow.webp</t>
+          <t>church_guard_si_b.webp</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -20878,20 +21100,20 @@
       </c>
       <c r="L3" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/robert_si_bow.webp</t>
+          <t>resources/si/npc/church_guard_si_b.webp</t>
         </is>
       </c>
     </row>
     <row r="4" ht="111" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Church_guard</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>robert_si_closedtalk.webp</t>
+          <t>church_guard_si_c.webp</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -20920,20 +21142,20 @@
       </c>
       <c r="L4" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/robert_si_closedtalk.webp</t>
+          <t>resources/si/npc/church_guard_si_c.webp</t>
         </is>
       </c>
     </row>
     <row r="5" ht="111" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Church_guard</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>robert_si_front.webp</t>
+          <t>church_guard_si_d.webp</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -20962,20 +21184,20 @@
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/robert_si_front.webp</t>
+          <t>resources/si/npc/church_guard_si_d.webp</t>
         </is>
       </c>
     </row>
     <row r="6" ht="111" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Church_guard</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>robert_si_sideeye.webp</t>
+          <t>church_guard_si_e.webp</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -21004,20 +21226,20 @@
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/robert_si_sideeye.webp</t>
+          <t>resources/si/npc/church_guard_si_e.webp</t>
         </is>
       </c>
     </row>
     <row r="7" ht="111" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Church_guard</t>
         </is>
       </c>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>robert_si_surprise.webp</t>
+          <t>church_guard_si_f.webp</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -21046,49 +21268,54 @@
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/robert_si_surprise.webp</t>
+          <t>resources/si/npc/church_guard_si_f.webp</t>
         </is>
       </c>
     </row>
     <row r="8" ht="111" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Robert</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>robert_si_talk.webp</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="n"/>
-      <c r="I8" s="4" t="n"/>
-      <c r="J8" s="4" t="n"/>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L8" s="6" t="inlineStr">
-        <is>
-          <t>resources/si/npc/robert_si_talk.webp</t>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>衛士</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>church_guard_si_draw.webp</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>(base)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>758</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>512×768</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/npc/church_guard_si_draw.webp</t>
         </is>
       </c>
     </row>
@@ -21104,7 +21331,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -21186,13 +21413,13 @@
     <row r="2" ht="111" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Church_guard</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="B2" s="5" t="n"/>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>church_guard_si_a.webp</t>
+          <t>robert_si_blindeye.webp</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -21221,20 +21448,20 @@
       </c>
       <c r="L2" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/church_guard_si_a.webp</t>
+          <t>resources/si/npc/robert_si_blindeye.webp</t>
         </is>
       </c>
     </row>
     <row r="3" ht="111" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Church_guard</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>church_guard_si_b.webp</t>
+          <t>robert_si_bow.webp</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -21263,20 +21490,20 @@
       </c>
       <c r="L3" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/church_guard_si_b.webp</t>
+          <t>resources/si/npc/robert_si_bow.webp</t>
         </is>
       </c>
     </row>
     <row r="4" ht="111" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Church_guard</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>church_guard_si_c.webp</t>
+          <t>robert_si_closedtalk.webp</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -21305,20 +21532,20 @@
       </c>
       <c r="L4" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/church_guard_si_c.webp</t>
+          <t>resources/si/npc/robert_si_closedtalk.webp</t>
         </is>
       </c>
     </row>
     <row r="5" ht="111" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Church_guard</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>church_guard_si_d.webp</t>
+          <t>robert_si_front.webp</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -21347,20 +21574,20 @@
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/church_guard_si_d.webp</t>
+          <t>resources/si/npc/robert_si_front.webp</t>
         </is>
       </c>
     </row>
     <row r="6" ht="111" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Church_guard</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>church_guard_si_e.webp</t>
+          <t>robert_si_sideeye.webp</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -21389,20 +21616,20 @@
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/church_guard_si_e.webp</t>
+          <t>resources/si/npc/robert_si_sideeye.webp</t>
         </is>
       </c>
     </row>
     <row r="7" ht="111" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Church_guard</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>church_guard_si_f.webp</t>
+          <t>robert_si_surprise.webp</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -21431,7 +21658,49 @@
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>resources/si/npc/church_guard_si_f.webp</t>
+          <t>resources/si/npc/robert_si_surprise.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="111" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Robert</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>robert_si_talk.webp</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>✘ 未接線</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>估</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="n"/>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="4" t="n"/>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>resources/si/npc/robert_si_talk.webp</t>
         </is>
       </c>
     </row>
@@ -30490,7 +30759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L78"/>
+  <dimension ref="A1:L80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -32027,42 +32296,47 @@
       </c>
     </row>
     <row r="33" ht="111" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>索菈娜</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>sorana_si_guardgrimace.webp</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="n"/>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="n"/>
-      <c r="I33" s="4" t="n"/>
-      <c r="J33" s="4" t="n"/>
-      <c r="K33" s="4" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L33" s="6" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>guardgrimace</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="n"/>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>1527</v>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
         <is>
           <t>resources/si/sorana_si_guardgrimace.webp</t>
         </is>
@@ -33105,12 +33379,12 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>sorana_si_sad.webp</t>
+          <t>sorana_si_runserious.webp</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>sad</t>
+          <t>runserious</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -33125,22 +33399,22 @@
         </is>
       </c>
       <c r="H56" s="2" t="n">
-        <v>0.515</v>
+        <v>0.509</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1527</v>
+        <v>1515</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>1024×1535</t>
+          <t>1024×1536</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_sad.webp</t>
+          <t>resources/si/sorana_si_runserious.webp</t>
         </is>
       </c>
     </row>
@@ -33152,12 +33426,12 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>sorana_si_salute.webp</t>
+          <t>sorana_si_runserious_side.webp</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>salute</t>
+          <t>runserious_side</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -33172,13 +33446,13 @@
         </is>
       </c>
       <c r="H57" s="2" t="n">
-        <v>0.58</v>
+        <v>0.774</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1525</v>
+        <v>1507</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
@@ -33187,7 +33461,7 @@
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_salute.webp</t>
+          <t>resources/si/sorana_si_runserious_side.webp</t>
         </is>
       </c>
     </row>
@@ -33199,12 +33473,12 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>sorana_si_scare.webp</t>
+          <t>sorana_si_sad.webp</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>scare</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -33219,22 +33493,22 @@
         </is>
       </c>
       <c r="H58" s="2" t="n">
-        <v>0.54</v>
+        <v>0.515</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1518</v>
+        <v>1527</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>1024×1536</t>
+          <t>1024×1535</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_scare.webp</t>
+          <t>resources/si/sorana_si_sad.webp</t>
         </is>
       </c>
     </row>
@@ -33246,12 +33520,12 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>sorana_si_serious.webp</t>
+          <t>sorana_si_salute.webp</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>serious</t>
+          <t>salute</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -33266,13 +33540,13 @@
         </is>
       </c>
       <c r="H59" s="2" t="n">
-        <v>0.576</v>
+        <v>0.58</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
@@ -33281,7 +33555,7 @@
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_serious.webp</t>
+          <t>resources/si/sorana_si_salute.webp</t>
         </is>
       </c>
     </row>
@@ -33293,12 +33567,12 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>sorana_si_shy.webp</t>
+          <t>sorana_si_scare.webp</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>shy</t>
+          <t>scare</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -33313,13 +33587,13 @@
         </is>
       </c>
       <c r="H60" s="2" t="n">
-        <v>0.586</v>
+        <v>0.54</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1531</v>
+        <v>1518</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
@@ -33328,7 +33602,7 @@
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_shy.webp</t>
+          <t>resources/si/sorana_si_scare.webp</t>
         </is>
       </c>
     </row>
@@ -33340,12 +33614,12 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>sorana_si_side.webp</t>
+          <t>sorana_si_serious.webp</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>(base)</t>
+          <t>serious</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -33360,13 +33634,13 @@
         </is>
       </c>
       <c r="H61" s="2" t="n">
-        <v>0.498</v>
+        <v>0.576</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
@@ -33375,7 +33649,7 @@
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_side.webp</t>
+          <t>resources/si/sorana_si_serious.webp</t>
         </is>
       </c>
     </row>
@@ -33387,12 +33661,12 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>sorana_si_sleep.webp</t>
+          <t>sorana_si_shy.webp</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>sleep</t>
+          <t>shy</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -33407,22 +33681,22 @@
         </is>
       </c>
       <c r="H62" s="2" t="n">
-        <v>0.461</v>
+        <v>0.586</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>230</v>
+        <v>7</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1424</v>
+        <v>1531</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>1024×1535</t>
+          <t>1024×1536</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_sleep.webp</t>
+          <t>resources/si/sorana_si_shy.webp</t>
         </is>
       </c>
     </row>
@@ -33434,12 +33708,12 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>sorana_si_smile.webp</t>
+          <t>sorana_si_side.webp</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>smile</t>
+          <t>(base)</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -33454,13 +33728,13 @@
         </is>
       </c>
       <c r="H63" s="2" t="n">
-        <v>0.528</v>
+        <v>0.498</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1530</v>
+        <v>1526</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
@@ -33469,7 +33743,7 @@
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_smile.webp</t>
+          <t>resources/si/sorana_si_side.webp</t>
         </is>
       </c>
     </row>
@@ -33481,12 +33755,12 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>sorana_si_smirk.webp</t>
+          <t>sorana_si_sleep.webp</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>smirk</t>
+          <t>sleep</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -33501,22 +33775,22 @@
         </is>
       </c>
       <c r="H64" s="2" t="n">
-        <v>0.582</v>
+        <v>0.461</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>8</v>
+        <v>230</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1528</v>
+        <v>1424</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>1024×1536</t>
+          <t>1024×1535</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_smirk.webp</t>
+          <t>resources/si/sorana_si_sleep.webp</t>
         </is>
       </c>
     </row>
@@ -33528,12 +33802,12 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>sorana_si_sorry.webp</t>
+          <t>sorana_si_smile.webp</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>sorry</t>
+          <t>smile</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -33548,13 +33822,13 @@
         </is>
       </c>
       <c r="H65" s="2" t="n">
-        <v>0.511</v>
+        <v>0.528</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
@@ -33563,7 +33837,7 @@
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_sorry.webp</t>
+          <t>resources/si/sorana_si_smile.webp</t>
         </is>
       </c>
     </row>
@@ -33575,12 +33849,12 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>sorana_si_stare.webp</t>
+          <t>sorana_si_smirk.webp</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>stare</t>
+          <t>smirk</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -33595,13 +33869,13 @@
         </is>
       </c>
       <c r="H66" s="2" t="n">
-        <v>0.576</v>
+        <v>0.582</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1524</v>
+        <v>1528</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
@@ -33610,7 +33884,7 @@
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_stare.webp</t>
+          <t>resources/si/sorana_si_smirk.webp</t>
         </is>
       </c>
     </row>
@@ -33622,12 +33896,12 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>sorana_si_surprise.webp</t>
+          <t>sorana_si_sorry.webp</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>surprise</t>
+          <t>sorry</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -33642,13 +33916,13 @@
         </is>
       </c>
       <c r="H67" s="2" t="n">
-        <v>0.537</v>
+        <v>0.511</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1522</v>
+        <v>1528</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
@@ -33657,7 +33931,7 @@
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_surprise.webp</t>
+          <t>resources/si/sorana_si_sorry.webp</t>
         </is>
       </c>
     </row>
@@ -33669,12 +33943,12 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>sorana_si_talk.webp</t>
+          <t>sorana_si_stare.webp</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>talk</t>
+          <t>stare</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -33689,13 +33963,13 @@
         </is>
       </c>
       <c r="H68" s="2" t="n">
-        <v>0.508</v>
+        <v>0.576</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
@@ -33704,7 +33978,7 @@
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_talk.webp</t>
+          <t>resources/si/sorana_si_stare.webp</t>
         </is>
       </c>
     </row>
@@ -33716,12 +33990,12 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>sorana_si_talksmile.webp</t>
+          <t>sorana_si_surprise.webp</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>talksmile</t>
+          <t>surprise</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -33736,10 +34010,10 @@
         </is>
       </c>
       <c r="H69" s="2" t="n">
-        <v>0.512</v>
+        <v>0.537</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J69" s="2" t="n">
         <v>1522</v>
@@ -33751,7 +34025,7 @@
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_talksmile.webp</t>
+          <t>resources/si/sorana_si_surprise.webp</t>
         </is>
       </c>
     </row>
@@ -33763,12 +34037,12 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>sorana_si_taunt.webp</t>
+          <t>sorana_si_talk.webp</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>taunt</t>
+          <t>talk</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -33783,13 +34057,13 @@
         </is>
       </c>
       <c r="H70" s="2" t="n">
-        <v>0.514</v>
+        <v>0.508</v>
       </c>
       <c r="I70" s="2" t="n">
         <v>7</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1528</v>
+        <v>1525</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
@@ -33798,7 +34072,7 @@
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_taunt.webp</t>
+          <t>resources/si/sorana_si_talk.webp</t>
         </is>
       </c>
     </row>
@@ -33810,12 +34084,12 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>sorana_si_tease.webp</t>
+          <t>sorana_si_talksmile.webp</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>tease</t>
+          <t>talksmile</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -33830,13 +34104,13 @@
         </is>
       </c>
       <c r="H71" s="2" t="n">
-        <v>0.583</v>
+        <v>0.512</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1528</v>
+        <v>1522</v>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
@@ -33845,7 +34119,7 @@
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_tease.webp</t>
+          <t>resources/si/sorana_si_talksmile.webp</t>
         </is>
       </c>
     </row>
@@ -33857,12 +34131,12 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>sorana_si_think.webp</t>
+          <t>sorana_si_taunt.webp</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>think</t>
+          <t>taunt</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -33877,13 +34151,13 @@
         </is>
       </c>
       <c r="H72" s="2" t="n">
-        <v>0.529</v>
+        <v>0.514</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
@@ -33892,7 +34166,7 @@
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_think.webp</t>
+          <t>resources/si/sorana_si_taunt.webp</t>
         </is>
       </c>
     </row>
@@ -33904,12 +34178,12 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>sorana_si_tire.webp</t>
+          <t>sorana_si_tease.webp</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>tire</t>
+          <t>tease</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -33924,13 +34198,13 @@
         </is>
       </c>
       <c r="H73" s="2" t="n">
-        <v>0.511</v>
+        <v>0.583</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1522</v>
+        <v>1528</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
@@ -33939,7 +34213,7 @@
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_tire.webp</t>
+          <t>resources/si/sorana_si_tease.webp</t>
         </is>
       </c>
     </row>
@@ -33951,12 +34225,12 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>sorana_si_upset.webp</t>
+          <t>sorana_si_think.webp</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>upset</t>
+          <t>think</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -33971,13 +34245,13 @@
         </is>
       </c>
       <c r="H74" s="2" t="n">
-        <v>0.514</v>
+        <v>0.529</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
@@ -33986,7 +34260,7 @@
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_upset.webp</t>
+          <t>resources/si/sorana_si_think.webp</t>
         </is>
       </c>
     </row>
@@ -33998,12 +34272,12 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>sorana_si_watch.webp</t>
+          <t>sorana_si_tire.webp</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>watch</t>
+          <t>tire</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -34018,13 +34292,13 @@
         </is>
       </c>
       <c r="H75" s="2" t="n">
-        <v>0.68</v>
+        <v>0.511</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
@@ -34033,7 +34307,7 @@
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_watch.webp</t>
+          <t>resources/si/sorana_si_tire.webp</t>
         </is>
       </c>
     </row>
@@ -34045,12 +34319,12 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>sorana_si_wave.webp</t>
+          <t>sorana_si_upset.webp</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>wave</t>
+          <t>upset</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -34065,13 +34339,13 @@
         </is>
       </c>
       <c r="H76" s="2" t="n">
-        <v>0.53</v>
+        <v>0.514</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
@@ -34080,7 +34354,7 @@
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_wave.webp</t>
+          <t>resources/si/sorana_si_upset.webp</t>
         </is>
       </c>
     </row>
@@ -34092,12 +34366,12 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>sorana_si_whisper.webp</t>
+          <t>sorana_si_watch.webp</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>whisper</t>
+          <t>watch</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -34112,22 +34386,22 @@
         </is>
       </c>
       <c r="H77" s="2" t="n">
-        <v>0.524</v>
+        <v>0.68</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1524</v>
+        <v>1521</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>1024×1535</t>
+          <t>1024×1536</t>
         </is>
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>resources/si/sorana_si_whisper.webp</t>
+          <t>resources/si/sorana_si_watch.webp</t>
         </is>
       </c>
     </row>
@@ -34139,12 +34413,12 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>sorana_si_worry.webp</t>
+          <t>sorana_si_wave.webp</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>worry</t>
+          <t>wave</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -34159,20 +34433,114 @@
         </is>
       </c>
       <c r="H78" s="2" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>1527</v>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/sorana_si_wave.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="111" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>索菈娜</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>sorana_si_whisper.webp</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>whisper</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="n"/>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>1524</v>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>1024×1535</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/sorana_si_whisper.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="111" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>索菈娜</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>sorana_si_worry.webp</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>worry</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="n"/>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="n">
         <v>0.543</v>
       </c>
-      <c r="I78" s="2" t="n">
+      <c r="I80" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J78" s="2" t="n">
+      <c r="J80" s="2" t="n">
         <v>1519</v>
       </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L78" s="3" t="inlineStr">
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
         <is>
           <t>resources/si/sorana_si_worry.webp</t>
         </is>
@@ -34190,7 +34558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D140"/>
+  <dimension ref="A1:D139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -35554,7 +35922,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>sorana_si_guardgrimace.webp</t>
+          <t>sorana_si_q.webp</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -35571,12 +35939,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Sorana</t>
+          <t>image - 2026-09-20T150615.066</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>sorana_si_q.webp</t>
+          <t>image - 2026-09-20T150615.066.png</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -35593,12 +35961,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T150615.066</t>
+          <t>image - 2026-09-20T150842.343</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T150615.066.png</t>
+          <t>image - 2026-09-20T150842.343.png</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -35615,12 +35983,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T150842.343</t>
+          <t>image - 2026-09-20T151013.881</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T150842.343.png</t>
+          <t>image - 2026-09-20T151013.881.png</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -35637,12 +36005,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T151013.881</t>
+          <t>image - 2026-09-20T151141.942</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T151013.881.png</t>
+          <t>image - 2026-09-20T151141.942.png</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -35659,12 +36027,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T151141.942</t>
+          <t>Torsten</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T151141.942.png</t>
+          <t>torsten_si_front.webp</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -35686,7 +36054,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>torsten_si_front.webp</t>
+          <t>torsten_si_q.webp</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -35703,12 +36071,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Torsten</t>
+          <t>Xanya</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>torsten_si_q.webp</t>
+          <t>xanya_si_front.webp</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -35720,22 +36088,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>美術交了沒接線</t>
+          <t>同差分的另一個版本</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Xanya</t>
+          <t>Anya</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>xanya_si_front.webp</t>
+          <t>resources/si/anya_si_nod.png</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>在 script/speakers.js 的 ART 補一筆 expr，並量 fx／top／bot（§6.5）</t>
+          <t>線上跑的是 anya_si_nod.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -35747,17 +36115,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Anya</t>
+          <t>Cecilie</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>resources/si/anya_si_nod.png</t>
+          <t>resources/si/cecilie_si_saintinstall.png</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>線上跑的是 anya_si_nod.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_saintinstall.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -35769,17 +36137,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Misha</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>resources/si/cecilie_si_saintinstall.png</t>
+          <t>resources/si/misha_si_fight.png</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_saintinstall.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 misha_si_fight.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -35796,12 +36164,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>resources/si/misha_si_fight.png</t>
+          <t>resources/si/misha_si_ni.png</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>線上跑的是 misha_si_fight.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 misha_si_ni.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -35813,17 +36181,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Misha</t>
+          <t>Nouvelle</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>resources/si/misha_si_ni.png</t>
+          <t>resources/si/nouvelle_si_gossip1.png</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>線上跑的是 misha_si_ni.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 nouvelle_si_gossip1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -35840,12 +36208,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>resources/si/nouvelle_si_gossip1.png</t>
+          <t>resources/si/nouvelle_si_salute.png</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>線上跑的是 nouvelle_si_gossip1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 nouvelle_si_salute.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -35862,12 +36230,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>resources/si/nouvelle_si_salute.png</t>
+          <t>resources/si/nouvelle_si_sigh.png</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>線上跑的是 nouvelle_si_salute.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 nouvelle_si_sigh.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -35879,17 +36247,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Nouvelle</t>
+          <t>Npc_grocer</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>resources/si/nouvelle_si_sigh.png</t>
+          <t>resources/si/npc/npc_grocer_si_v2.webp</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>線上跑的是 nouvelle_si_sigh.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -35906,7 +36274,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_grocer_si_v2.webp</t>
+          <t>resources/si/npc/npc_grocer_si_v3.webp</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -35928,7 +36296,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_grocer_si_v3.webp</t>
+          <t>resources/si/npc/npc_grocer_si_v4.webp</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -35950,7 +36318,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_grocer_si_v4.webp</t>
+          <t>resources/si/npc/npc_grocer_si_v5.webp</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -35967,17 +36335,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Npc_grocer</t>
+          <t>Npc_guildcounter</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_grocer_si_v5.webp</t>
+          <t>resources/si/npc/npc_guildcounter_si_v1.webp</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_guildcounter_si_v5.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -35994,7 +36362,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_guildcounter_si_v1.webp</t>
+          <t>resources/si/npc/npc_guildcounter_si_v3.webp</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -36016,7 +36384,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_guildcounter_si_v3.webp</t>
+          <t>resources/si/npc/npc_guildcounter_si_v4.webp</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -36033,17 +36401,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Npc_guildcounter</t>
+          <t>Npc_gunsmith</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_guildcounter_si_v4.webp</t>
+          <t>resources/si/npc/npc_gunsmith_si_v2.webp</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_guildcounter_si_v5.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36060,7 +36428,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_gunsmith_si_v2.webp</t>
+          <t>resources/si/npc/npc_gunsmith_si_v3.webp</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -36082,7 +36450,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_gunsmith_si_v3.webp</t>
+          <t>resources/si/npc/npc_gunsmith_si_v4.webp</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -36104,7 +36472,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_gunsmith_si_v4.webp</t>
+          <t>resources/si/npc/npc_gunsmith_si_v5.webp</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -36121,17 +36489,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Npc_gunsmith</t>
+          <t>Cecilie</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_gunsmith_si_v5.webp</t>
+          <t>resources/si/old/cecilie_si_front.png</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_front.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36148,12 +36516,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_front.png</t>
+          <t>resources/si/old/cecilie_si_lookaside.png</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_front.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_lookaside.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36170,12 +36538,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_lookaside.png</t>
+          <t>resources/si/old/cecilie_si_sadback.png</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_lookaside.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_sadback.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36192,12 +36560,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_sadback.png</t>
+          <t>resources/si/old/cecilie_si_smile.png</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_sadback.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_smile.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36214,12 +36582,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_smile.png</t>
+          <t>resources/si/old/cecilie_si_tease.png</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_smile.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_tease.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36236,12 +36604,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_tease.png</t>
+          <t>resources/si/old/cecilie_si_upset.png</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_tease.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_upset.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36253,17 +36621,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_upset.png</t>
+          <t>resources/si/renna_newhair/renna_si_argue.webp</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_upset.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_argue.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36280,12 +36648,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_argue.webp</t>
+          <t>resources/si/renna_newhair/renna_si_arguecute.webp</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_argue.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_arguecute.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36302,12 +36670,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_arguecute.webp</t>
+          <t>resources/si/renna_newhair/renna_si_ask.webp</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_arguecute.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_ask.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36324,12 +36692,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_ask.webp</t>
+          <t>resources/si/renna_newhair/renna_si_askserious.webp</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_ask.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_askserious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36346,12 +36714,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_askserious.webp</t>
+          <t>resources/si/renna_newhair/renna_si_awkwerd.webp</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_askserious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_awkwerd.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36368,12 +36736,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_awkwerd.webp</t>
+          <t>resources/si/renna_newhair/renna_si_blush.webp</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_awkwerd.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_blush.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36390,12 +36758,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_blush.webp</t>
+          <t>resources/si/renna_newhair/renna_si_bow.webp</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_blush.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_bow.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36412,12 +36780,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_bow.webp</t>
+          <t>resources/si/renna_newhair/renna_si_callangry.webp</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_bow.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_callangry.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36434,12 +36802,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_callangry.webp</t>
+          <t>resources/si/renna_newhair/renna_si_chase.webp</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_callangry.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_chase.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36456,12 +36824,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_chase.webp</t>
+          <t>resources/si/renna_newhair/renna_si_chase2.webp</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_chase.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_chase2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36478,12 +36846,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_chase2.webp</t>
+          <t>resources/si/renna_newhair/renna_si_command.webp</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_chase2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_command.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36500,12 +36868,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_command.webp</t>
+          <t>resources/si/renna_newhair/renna_si_covermouth.webp</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_command.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_covermouth.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36522,12 +36890,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_covermouth.webp</t>
+          <t>resources/si/renna_newhair/renna_si_cringe.webp</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_covermouth.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_cringe.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36544,12 +36912,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_cringe.webp</t>
+          <t>resources/si/renna_newhair/renna_si_curious.webp</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_cringe.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_curious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36566,12 +36934,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_curious.webp</t>
+          <t>resources/si/renna_newhair/renna_si_die.webp</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_curious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_die.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36588,12 +36956,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_die.webp</t>
+          <t>resources/si/renna_newhair/renna_si_evaluate.webp</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_die.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_evaluate.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36610,12 +36978,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_evaluate.webp</t>
+          <t>resources/si/renna_newhair/renna_si_front.webp</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_evaluate.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_front.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36632,12 +37000,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_front.webp</t>
+          <t>resources/si/renna_newhair/renna_si_intense.webp</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_front.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_intense.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36654,12 +37022,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_intense.webp</t>
+          <t>resources/si/renna_newhair/renna_si_intense2.webp</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_intense.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_intense2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36676,12 +37044,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_intense2.webp</t>
+          <t>resources/si/renna_newhair/renna_si_invite.webp</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_intense2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_invite.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36698,12 +37066,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_invite.webp</t>
+          <t>resources/si/renna_newhair/renna_si_lookaway.webp</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_invite.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_lookaway.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36720,12 +37088,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_lookaway.webp</t>
+          <t>resources/si/renna_newhair/renna_si_lookawaytalk.webp</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_lookaway.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_lookawaytalk.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36742,12 +37110,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_lookawaytalk.webp</t>
+          <t>resources/si/renna_newhair/renna_si_lookdown.webp</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_lookawaytalk.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_lookdown.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36764,12 +37132,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_lookdown.webp</t>
+          <t>resources/si/renna_newhair/renna_si_lookup.webp</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_lookdown.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_lookup.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36786,12 +37154,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_lookup.webp</t>
+          <t>resources/si/renna_newhair/renna_si_pause.webp</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_lookup.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_pause.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36808,12 +37176,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_pause.webp</t>
+          <t>resources/si/renna_newhair/renna_si_relief.webp</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_pause.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_relief.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36830,12 +37198,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_relief.webp</t>
+          <t>resources/si/renna_newhair/renna_si_sad.webp</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_relief.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_sad.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36852,12 +37220,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_sad.webp</t>
+          <t>resources/si/renna_newhair/renna_si_shout.webp</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_sad.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_shout.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36874,12 +37242,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_shout.webp</t>
+          <t>resources/si/renna_newhair/renna_si_smile.webp</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_shout.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_smile.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36896,12 +37264,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_smile.webp</t>
+          <t>resources/si/renna_newhair/renna_si_stare.webp</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_smile.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_stare.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36918,12 +37286,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_stare.webp</t>
+          <t>resources/si/renna_newhair/renna_si_surprise.webp</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_stare.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_surprise.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36940,12 +37308,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_surprise.webp</t>
+          <t>resources/si/renna_newhair/renna_si_talkserious.webp</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_surprise.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_talkserious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36962,12 +37330,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_talkserious.webp</t>
+          <t>resources/si/renna_newhair/renna_si_talkwork.webp</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_talkserious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_talkwork.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -36984,12 +37352,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_talkwork.webp</t>
+          <t>resources/si/renna_newhair/renna_si_think.webp</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_talkwork.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_think.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -37006,12 +37374,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_think.webp</t>
+          <t>resources/si/renna_newhair/renna_si_tire.webp</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_think.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_tire.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -37028,12 +37396,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_tire.webp</t>
+          <t>resources/si/renna_newhair/renna_si_upset.webp</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_tire.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_upset.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -37050,12 +37418,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_upset.webp</t>
+          <t>resources/si/renna_newhair/renna_si_upsetstare.webp</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_upset.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_upsetstare.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -37072,12 +37440,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_upsetstare.webp</t>
+          <t>resources/si/renna_newhair/renna_si_wake.webp</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_upsetstare.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_wake.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -37094,12 +37462,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_wake.webp</t>
+          <t>resources/si/renna_newhair/renna_si_watch.webp</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_wake.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_watch.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -37116,12 +37484,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_watch.webp</t>
+          <t>resources/si/renna_newhair/renna_si_worry.webp</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_watch.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_worry.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -37138,12 +37506,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_worry.webp</t>
+          <t>resources/si/renna_newhair/renna_si_write.webp</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_worry.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_write.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -37160,12 +37528,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_write.webp</t>
+          <t>resources/si/renna_si_hug.png</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_write.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_hug.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -37182,12 +37550,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_hug.png</t>
+          <t>resources/si/renna_si_hugangry2.png</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_hug.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_hugangry2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -37204,12 +37572,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_hugangry2.png</t>
+          <t>resources/si/renna_si_hugclose.png</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_hugangry2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_hugclose.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -37226,12 +37594,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_hugclose.png</t>
+          <t>resources/si/renna_si_huglookaway.png</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_hugclose.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_huglookaway.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -37243,37 +37611,15 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Renna</t>
+          <t>Torsten</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_huglookaway.png</t>
+          <t>resources/si/torsten_si_back.png</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_huglookaway.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Torsten</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>resources/si/torsten_si_back.png</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
         <is>
           <t>線上跑的是 torsten_si_back.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
@@ -43140,6 +43486,708 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="42" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>角色</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>縮圖（抓臉）</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>檔名</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>差分鍵</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>已接線</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>另有版本</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>取景</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>fx</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>top</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>bot</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>尺寸</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>路徑</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="111" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>科爾文</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>corvin_si_bow.webp</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>bow</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>1522</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/npc/corvin_si_bow.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="111" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>科爾文</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>corvin_si_ecstasy.webp</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>ecstasy</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>1525</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/npc/corvin_si_ecstasy.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="111" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>科爾文</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>corvin_si_front.webp</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>(base)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>1528</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/npc/corvin_si_front.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="111" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>科爾文</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>corvin_si_hurtcommand.webp</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>hurtcommand</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>1522</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/npc/corvin_si_hurtcommand.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="111" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>科爾文</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>corvin_si_hurthold.webp</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>hurthold</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>1523</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/npc/corvin_si_hurthold.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="111" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>科爾文</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>corvin_si_hurttalk.webp</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>hurttalk</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>1504</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/npc/corvin_si_hurttalk.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="111" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>科爾文</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>corvin_si_lookaside.webp</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>lookaside</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>1533</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/npc/corvin_si_lookaside.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="111" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>科爾文</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>corvin_si_read.webp</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>1532</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/npc/corvin_si_read.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="111" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>科爾文</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>corvin_si_shock.webp</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>shock</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>1533</v>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/npc/corvin_si_shock.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="111" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>科爾文</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>corvin_si_smile.webp</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>smile</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>1529</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/npc/corvin_si_smile.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="111" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>科爾文</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>corvin_si_stare.webp</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>stare</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>1531</v>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/npc/corvin_si_stare.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="111" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>科爾文</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>corvin_si_talk.webp</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>talk</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>1531</v>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/npc/corvin_si_talk.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="111" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>科爾文</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>corvin_si_think.webp</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>think</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>1530</v>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/npc/corvin_si_think.webp</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -43787,565 +44835,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="7" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="42" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>角色</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>縮圖（抓臉）</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>檔名</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>差分鍵</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>已接線</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>另有版本</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>取景</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>fx</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>top</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>bot</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>尺寸</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>路徑</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="111" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>蕾娜</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>renna_ad_si_bow.webp</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>ad_bow</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>量</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>0.492</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>1510</v>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>resources/si/renna_ad_si_bow.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="111" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>蕾娜</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>renna_ad_si_command.webp</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>ad_command</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>量</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>0.512</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>1516</v>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>resources/si/renna_ad_si_command.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="111" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>蕾娜</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>renna_ad_si_commandsoft.webp</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>ad_commandsoft</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>量</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>0.531</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>1515</v>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>resources/si/renna_ad_si_commandsoft.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="111" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>蕾娜</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>renna_ad_si_front.webp</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>ad_front</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>量</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>0.479</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>1524</v>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>resources/si/renna_ad_si_front.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="111" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>蕾娜</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>renna_ad_si_lookaway.webp</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>ad_lookaway</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>量</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>0.517</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>1519</v>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>resources/si/renna_ad_si_lookaway.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="111" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>蕾娜</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>renna_ad_si_remind.webp</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>ad_remind</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>量</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>1521</v>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>resources/si/renna_ad_si_remind.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="111" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>蕾娜</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>renna_ad_si_smile.webp</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>ad_smile</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>量</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>1508</v>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>resources/si/renna_ad_si_smile.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="111" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>蕾娜</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>renna_ad_si_think.webp</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>ad_think</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>量</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0.508</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>1510</v>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>resources/si/renna_ad_si_think.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="111" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>蕾娜</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>renna_ad_si_watch.webp</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>ad_watch</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>量</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>0.522</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>1515</v>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>resources/si/renna_ad_si_watch.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="111" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>蕾娜</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>renna_ad_si_write.webp</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>ad_write</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>量</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>0.504</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" s="2" t="n">
-        <v>1521</v>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>resources/si/renna_ad_si_write.webp</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
 </file>
--- a/resources/si/_SI_差分總表.xlsx
+++ b/resources/si/_SI_差分總表.xlsx
@@ -19676,42 +19676,47 @@
       </c>
     </row>
     <row r="6" ht="111" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>謎之術師</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>mage_si_hurtsmile.webp</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="4" t="n"/>
-      <c r="J6" s="4" t="n"/>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>hurtsmile</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>1529</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>resources/si/npc/mage_si_hurtsmile.webp</t>
         </is>
@@ -31145,7 +31150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D151"/>
+  <dimension ref="A1:D139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -31272,12 +31277,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>image - 2026-09-26T205756.614</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cecilie_si_battlecry.webp</t>
+          <t>image - 2026-09-26T205756.614.png</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -31294,12 +31299,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Luna</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cecilie_si_call.webp</t>
+          <t>luna_si_front.webp</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -31316,12 +31321,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Luna</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cecilie_si_command.webp</t>
+          <t>luna_si_seat_lookdown.webp</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -31338,12 +31343,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Nouvelle_nun</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cecilie_si_nosebleed.webp</t>
+          <t>nouvelle_nun_si_front.webp</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -31360,12 +31365,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Nouvelle</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cecilie_si_pant.webp</t>
+          <t>nouvelle_si_back.webp</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -31382,12 +31387,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Nouvelle</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>cecilie_si_proud.webp</t>
+          <t>nouvelle_si_bye.webp</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -31404,12 +31409,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Nouvelle</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>cecilie_si_ready.webp</t>
+          <t>nouvelle_si_expainsweat.webp</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -31426,12 +31431,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Nouvelle</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>cecilie_si_shocknose.webp</t>
+          <t>nouvelle_si_meetagain.webp</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -31448,12 +31453,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Nouvelle</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>cecilie_si_shyhand.webp</t>
+          <t>nouvelle_si_reliefbreath.webp</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -31470,12 +31475,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Nouvelle</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>cecilie_si_shynose.webp</t>
+          <t>nouvelle_si_scare.webp</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -31492,12 +31497,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Nouvelle</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>cecilie_si_smirk.webp</t>
+          <t>nouvelle_si_side.webp</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -31514,12 +31519,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>image - 2026-09-26T205756.614</t>
+          <t>Npc_aaron</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>image - 2026-09-26T205756.614.png</t>
+          <t>npc_aaron_si_trial.png</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -31536,12 +31541,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Luna</t>
+          <t>Npc_molly</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>luna_si_front.webp</t>
+          <t>npc_molly_si_trial.png</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -31558,12 +31563,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Luna</t>
+          <t>Npc_robert</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>luna_si_seat_lookdown.webp</t>
+          <t>npc_robert_si_trial.png</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -31580,12 +31585,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nouvelle_nun</t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>nouvelle_nun_si_front.webp</t>
+          <t>aaron_si_angry.webp</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -31602,12 +31607,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nouvelle</t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>nouvelle_si_back.webp</t>
+          <t>aaron_si_armscross.webp</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -31624,12 +31629,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nouvelle</t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>nouvelle_si_bye.webp</t>
+          <t>aaron_si_attention.webp</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -31646,12 +31651,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nouvelle</t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>nouvelle_si_expainsweat.webp</t>
+          <t>aaron_si_blindeye.webp</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -31668,12 +31673,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nouvelle</t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>nouvelle_si_meetagain.webp</t>
+          <t>aaron_si_closedsmile.webp</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -31690,12 +31695,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Nouvelle</t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>nouvelle_si_reliefbreath.webp</t>
+          <t>aaron_si_confused.webp</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -31712,12 +31717,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nouvelle</t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>nouvelle_si_scare.webp</t>
+          <t>aaron_si_draw.webp</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -31734,12 +31739,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nouvelle</t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>nouvelle_si_side.webp</t>
+          <t>aaron_si_front.webp</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -31756,12 +31761,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Npc_aaron</t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>npc_aaron_si_trial.png</t>
+          <t>aaron_si_signal.webp</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -31778,12 +31783,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Npc_molly</t>
+          <t>Church_guard</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>npc_molly_si_trial.png</t>
+          <t>church_guard_si_a.webp</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -31800,12 +31805,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Npc_robert</t>
+          <t>Church_guard</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>npc_robert_si_trial.png</t>
+          <t>church_guard_si_b.webp</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -31822,12 +31827,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Church_guard</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>aaron_si_angry.webp</t>
+          <t>church_guard_si_c.webp</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -31844,12 +31849,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Church_guard</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>aaron_si_armscross.webp</t>
+          <t>church_guard_si_d.webp</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -31866,12 +31871,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Church_guard</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>aaron_si_attention.webp</t>
+          <t>church_guard_si_e.webp</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -31888,12 +31893,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Church_guard</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>aaron_si_blindeye.webp</t>
+          <t>church_guard_si_f.webp</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -31910,12 +31915,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>f734e7ba-e7bb-457b-8cf7-66e13324c45d</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>aaron_si_closedsmile.webp</t>
+          <t>f734e7ba-e7bb-457b-8cf7-66e13324c45d.png</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -31932,12 +31937,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Mage</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>aaron_si_confused.webp</t>
+          <t>mage_si_cast.webp</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -31954,12 +31959,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Molly</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>aaron_si_draw.webp</t>
+          <t>molly_si_ask.webp</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -31976,12 +31981,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Molly</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>aaron_si_front.webp</t>
+          <t>molly_si_closedtalk.webp</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -31998,12 +32003,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Molly</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>aaron_si_signal.webp</t>
+          <t>molly_si_eyesmile.webp</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -32020,12 +32025,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Church_guard</t>
+          <t>Molly</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>church_guard_si_a.webp</t>
+          <t>molly_si_front.webp</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -32042,12 +32047,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Church_guard</t>
+          <t>Molly</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>church_guard_si_b.webp</t>
+          <t>molly_si_gossip.webp</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -32064,12 +32069,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Church_guard</t>
+          <t>Molly</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>church_guard_si_c.webp</t>
+          <t>molly_si_lookdown.webp</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -32086,12 +32091,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Church_guard</t>
+          <t>Molly</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>church_guard_si_d.webp</t>
+          <t>molly_si_order.webp</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -32108,12 +32113,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Church_guard</t>
+          <t>Molly</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>church_guard_si_e.webp</t>
+          <t>molly_si_serious.webp</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -32130,12 +32135,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Church_guard</t>
+          <t>Molly</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>church_guard_si_f.webp</t>
+          <t>molly_si_softsmile.webp</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -32152,12 +32157,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>f734e7ba-e7bb-457b-8cf7-66e13324c45d</t>
+          <t>Molly</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>f734e7ba-e7bb-457b-8cf7-66e13324c45d.png</t>
+          <t>molly_si_stern.webp</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -32174,12 +32179,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mage</t>
+          <t>Molly</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>mage_si_cast.webp</t>
+          <t>molly_si_superior.webp</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -32196,12 +32201,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Mage</t>
+          <t>Molly</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>mage_si_hurtsmile.webp</t>
+          <t>molly_si_surprise.webp</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -32223,7 +32228,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>molly_si_ask.webp</t>
+          <t>molly_si_talk.webp</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -32245,7 +32250,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>molly_si_closedtalk.webp</t>
+          <t>molly_si_think.webp</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -32267,7 +32272,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>molly_si_eyesmile.webp</t>
+          <t>molly_si_whisper.webp</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -32284,12 +32289,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Molly</t>
+          <t>npc_ss_lofa_shoot</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>molly_si_front.webp</t>
+          <t>npc_ss_lofa_shoot.png</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -32306,12 +32311,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Molly</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>molly_si_gossip.webp</t>
+          <t>robert_si_blindeye.webp</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -32328,12 +32333,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Molly</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>molly_si_lookdown.webp</t>
+          <t>robert_si_bow.webp</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -32350,12 +32355,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Molly</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>molly_si_order.webp</t>
+          <t>robert_si_closedtalk.webp</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -32372,12 +32377,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Molly</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>molly_si_serious.webp</t>
+          <t>robert_si_front.webp</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -32394,12 +32399,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Molly</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>molly_si_softsmile.webp</t>
+          <t>robert_si_sideeye.webp</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -32416,12 +32421,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Molly</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>molly_si_stern.webp</t>
+          <t>robert_si_surprise.webp</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -32438,12 +32443,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Molly</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>molly_si_superior.webp</t>
+          <t>robert_si_talk.webp</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -32460,12 +32465,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Molly</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>molly_si_surprise.webp</t>
+          <t>renna_si_evalutatingclosemouth.webp</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -32482,12 +32487,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Molly</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>molly_si_talk.webp</t>
+          <t>renna_si_annoy.webp</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -32504,12 +32509,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Molly</t>
+          <t>Sorana</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>molly_si_think.webp</t>
+          <t>sorana_si_q.webp</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -32526,12 +32531,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Molly</t>
+          <t>image - 2026-09-20T150615.066</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>molly_si_whisper.webp</t>
+          <t>image - 2026-09-20T150615.066.png</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -32548,12 +32553,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>npc_ss_lofa_shoot</t>
+          <t>image - 2026-09-20T150842.343</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>npc_ss_lofa_shoot.png</t>
+          <t>image - 2026-09-20T150842.343.png</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -32570,12 +32575,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>image - 2026-09-20T151013.881</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>robert_si_blindeye.webp</t>
+          <t>image - 2026-09-20T151013.881.png</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -32592,12 +32597,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>image - 2026-09-20T151141.942</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>robert_si_bow.webp</t>
+          <t>image - 2026-09-20T151141.942.png</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -32614,12 +32619,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Torsten</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>robert_si_closedtalk.webp</t>
+          <t>torsten_si_front.webp</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -32636,12 +32641,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Torsten</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>robert_si_front.webp</t>
+          <t>torsten_si_q.webp</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -32658,12 +32663,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Xanya</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>robert_si_sideeye.webp</t>
+          <t>xanya_si_front.webp</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -32675,264 +32680,264 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>美術交了沒接線</t>
+          <t>同差分的另一個版本</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Anya</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>robert_si_surprise.webp</t>
+          <t>resources/si/anya_si_nod.png</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>在 script/speakers.js 的 ART 補一筆 expr，並量 fx／top／bot（§6.5）</t>
+          <t>線上跑的是 anya_si_nod.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>美術交了沒接線</t>
+          <t>同差分的另一個版本</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Cecilie</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>robert_si_talk.webp</t>
+          <t>resources/si/cecilie_si_saintinstall.png</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>在 script/speakers.js 的 ART 補一筆 expr，並量 fx／top／bot（§6.5）</t>
+          <t>線上跑的是 cecilie_si_saintinstall.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>美術交了沒接線</t>
+          <t>同差分的另一個版本</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Renna</t>
+          <t>Misha</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>renna_si_evalutatingclosemouth.webp</t>
+          <t>resources/si/misha_si_fight.png</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>在 script/speakers.js 的 ART 補一筆 expr，並量 fx／top／bot（§6.5）</t>
+          <t>線上跑的是 misha_si_fight.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>美術交了沒接線</t>
+          <t>同差分的另一個版本</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Renna</t>
+          <t>Misha</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>renna_si_annoy.webp</t>
+          <t>resources/si/misha_si_ni.png</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>在 script/speakers.js 的 ART 補一筆 expr，並量 fx／top／bot（§6.5）</t>
+          <t>線上跑的是 misha_si_ni.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>美術交了沒接線</t>
+          <t>同差分的另一個版本</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Sorana</t>
+          <t>Nouvelle</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>sorana_si_q.webp</t>
+          <t>resources/si/nouvelle_si_gossip1.png</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>在 script/speakers.js 的 ART 補一筆 expr，並量 fx／top／bot（§6.5）</t>
+          <t>線上跑的是 nouvelle_si_gossip1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>美術交了沒接線</t>
+          <t>同差分的另一個版本</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T150615.066</t>
+          <t>Nouvelle</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T150615.066.png</t>
+          <t>resources/si/nouvelle_si_salute.png</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>在 script/speakers.js 的 ART 補一筆 expr，並量 fx／top／bot（§6.5）</t>
+          <t>線上跑的是 nouvelle_si_salute.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>美術交了沒接線</t>
+          <t>同差分的另一個版本</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T150842.343</t>
+          <t>Nouvelle</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T150842.343.png</t>
+          <t>resources/si/nouvelle_si_sigh.png</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>在 script/speakers.js 的 ART 補一筆 expr，並量 fx／top／bot（§6.5）</t>
+          <t>線上跑的是 nouvelle_si_sigh.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>美術交了沒接線</t>
+          <t>同差分的另一個版本</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T151013.881</t>
+          <t>Npc_grocer</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T151013.881.png</t>
+          <t>resources/si/npc/npc_grocer_si_v2.webp</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>在 script/speakers.js 的 ART 補一筆 expr，並量 fx／top／bot（§6.5）</t>
+          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>美術交了沒接線</t>
+          <t>同差分的另一個版本</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T151141.942</t>
+          <t>Npc_grocer</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T151141.942.png</t>
+          <t>resources/si/npc/npc_grocer_si_v3.webp</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>在 script/speakers.js 的 ART 補一筆 expr，並量 fx／top／bot（§6.5）</t>
+          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>美術交了沒接線</t>
+          <t>同差分的另一個版本</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Torsten</t>
+          <t>Npc_grocer</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>torsten_si_front.webp</t>
+          <t>resources/si/npc/npc_grocer_si_v4.webp</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>在 script/speakers.js 的 ART 補一筆 expr，並量 fx／top／bot（§6.5）</t>
+          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>美術交了沒接線</t>
+          <t>同差分的另一個版本</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Torsten</t>
+          <t>Npc_grocer</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>torsten_si_q.webp</t>
+          <t>resources/si/npc/npc_grocer_si_v5.webp</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>在 script/speakers.js 的 ART 補一筆 expr，並量 fx／top／bot（§6.5）</t>
+          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>美術交了沒接線</t>
+          <t>同差分的另一個版本</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Xanya</t>
+          <t>Npc_guildcounter</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>xanya_si_front.webp</t>
+          <t>resources/si/npc/npc_guildcounter_si_v1.webp</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>在 script/speakers.js 的 ART 補一筆 expr，並量 fx／top／bot（§6.5）</t>
+          <t>線上跑的是 npc_guildcounter_si_v5.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -32944,17 +32949,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Anya</t>
+          <t>Npc_guildcounter</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>resources/si/anya_si_nod.png</t>
+          <t>resources/si/npc/npc_guildcounter_si_v3.webp</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>線上跑的是 anya_si_nod.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_guildcounter_si_v5.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -32966,17 +32971,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Npc_guildcounter</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>resources/si/cecilie_si_saintinstall.png</t>
+          <t>resources/si/npc/npc_guildcounter_si_v4.webp</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_saintinstall.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_guildcounter_si_v5.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -32988,17 +32993,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Misha</t>
+          <t>Npc_gunsmith</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>resources/si/misha_si_fight.png</t>
+          <t>resources/si/npc/npc_gunsmith_si_v2.webp</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>線上跑的是 misha_si_fight.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33010,17 +33015,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Misha</t>
+          <t>Npc_gunsmith</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>resources/si/misha_si_ni.png</t>
+          <t>resources/si/npc/npc_gunsmith_si_v3.webp</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>線上跑的是 misha_si_ni.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33032,17 +33037,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Nouvelle</t>
+          <t>Npc_gunsmith</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>resources/si/nouvelle_si_gossip1.png</t>
+          <t>resources/si/npc/npc_gunsmith_si_v4.webp</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>線上跑的是 nouvelle_si_gossip1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33054,17 +33059,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Nouvelle</t>
+          <t>Npc_gunsmith</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>resources/si/nouvelle_si_salute.png</t>
+          <t>resources/si/npc/npc_gunsmith_si_v5.webp</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>線上跑的是 nouvelle_si_salute.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33076,17 +33081,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Nouvelle</t>
+          <t>Cecilie</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>resources/si/nouvelle_si_sigh.png</t>
+          <t>resources/si/old/cecilie_si_front.png</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>線上跑的是 nouvelle_si_sigh.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_front.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33098,17 +33103,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Npc_grocer</t>
+          <t>Cecilie</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_grocer_si_v2.webp</t>
+          <t>resources/si/old/cecilie_si_lookaside.png</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_lookaside.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33120,17 +33125,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Npc_grocer</t>
+          <t>Cecilie</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_grocer_si_v3.webp</t>
+          <t>resources/si/old/cecilie_si_sadback.png</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_sadback.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33142,17 +33147,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Npc_grocer</t>
+          <t>Cecilie</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_grocer_si_v4.webp</t>
+          <t>resources/si/old/cecilie_si_smile.png</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_smile.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33164,17 +33169,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Npc_grocer</t>
+          <t>Cecilie</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_grocer_si_v5.webp</t>
+          <t>resources/si/old/cecilie_si_tease.png</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_tease.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33186,17 +33191,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Npc_guildcounter</t>
+          <t>Cecilie</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_guildcounter_si_v1.webp</t>
+          <t>resources/si/old/cecilie_si_upset.png</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_guildcounter_si_v5.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_upset.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33208,17 +33213,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Npc_guildcounter</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_guildcounter_si_v3.webp</t>
+          <t>resources/si/renna_newhair/renna_si_argue.webp</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_guildcounter_si_v5.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_argue.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33230,17 +33235,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Npc_guildcounter</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_guildcounter_si_v4.webp</t>
+          <t>resources/si/renna_newhair/renna_si_arguecute.webp</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_guildcounter_si_v5.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_arguecute.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33252,17 +33257,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Npc_gunsmith</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_gunsmith_si_v2.webp</t>
+          <t>resources/si/renna_newhair/renna_si_ask.webp</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_ask.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33274,17 +33279,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Npc_gunsmith</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_gunsmith_si_v3.webp</t>
+          <t>resources/si/renna_newhair/renna_si_askserious.webp</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_askserious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33296,17 +33301,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Npc_gunsmith</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_gunsmith_si_v4.webp</t>
+          <t>resources/si/renna_newhair/renna_si_awkwerd.webp</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_awkwerd.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33318,17 +33323,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Npc_gunsmith</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_gunsmith_si_v5.webp</t>
+          <t>resources/si/renna_newhair/renna_si_blush.webp</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_blush.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33340,17 +33345,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_front.png</t>
+          <t>resources/si/renna_newhair/renna_si_bow.webp</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_front.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_bow.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33362,17 +33367,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_lookaside.png</t>
+          <t>resources/si/renna_newhair/renna_si_callangry.webp</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_lookaside.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_callangry.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33384,17 +33389,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_sadback.png</t>
+          <t>resources/si/renna_newhair/renna_si_chase.webp</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_sadback.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_chase.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33406,17 +33411,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_smile.png</t>
+          <t>resources/si/renna_newhair/renna_si_chase2.webp</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_smile.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_chase2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33428,17 +33433,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_tease.png</t>
+          <t>resources/si/renna_newhair/renna_si_command.webp</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_tease.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_command.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33450,17 +33455,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_upset.png</t>
+          <t>resources/si/renna_newhair/renna_si_covermouth.webp</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_upset.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_covermouth.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33477,12 +33482,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_argue.webp</t>
+          <t>resources/si/renna_newhair/renna_si_cringe.webp</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_argue.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_cringe.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33499,12 +33504,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_arguecute.webp</t>
+          <t>resources/si/renna_newhair/renna_si_curious.webp</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_arguecute.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_curious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33521,12 +33526,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_ask.webp</t>
+          <t>resources/si/renna_newhair/renna_si_die.webp</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_ask.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_die.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33543,12 +33548,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_askserious.webp</t>
+          <t>resources/si/renna_newhair/renna_si_evaluate.webp</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_askserious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_evaluate.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33565,12 +33570,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_awkwerd.webp</t>
+          <t>resources/si/renna_newhair/renna_si_front.webp</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_awkwerd.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_front.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33587,12 +33592,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_blush.webp</t>
+          <t>resources/si/renna_newhair/renna_si_intense.webp</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_blush.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_intense.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33609,12 +33614,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_bow.webp</t>
+          <t>resources/si/renna_newhair/renna_si_intense2.webp</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_bow.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_intense2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33631,12 +33636,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_callangry.webp</t>
+          <t>resources/si/renna_newhair/renna_si_invite.webp</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_callangry.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_invite.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33653,12 +33658,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_chase.webp</t>
+          <t>resources/si/renna_newhair/renna_si_lookaway.webp</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_chase.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_lookaway.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33675,12 +33680,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_chase2.webp</t>
+          <t>resources/si/renna_newhair/renna_si_lookawaytalk.webp</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_chase2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_lookawaytalk.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33697,12 +33702,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_command.webp</t>
+          <t>resources/si/renna_newhair/renna_si_lookdown.webp</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_command.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_lookdown.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33719,12 +33724,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_covermouth.webp</t>
+          <t>resources/si/renna_newhair/renna_si_lookup.webp</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_covermouth.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_lookup.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33741,12 +33746,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_cringe.webp</t>
+          <t>resources/si/renna_newhair/renna_si_pause.webp</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_cringe.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_pause.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33763,12 +33768,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_curious.webp</t>
+          <t>resources/si/renna_newhair/renna_si_relief.webp</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_curious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_relief.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33785,12 +33790,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_die.webp</t>
+          <t>resources/si/renna_newhair/renna_si_sad.webp</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_die.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_sad.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33807,12 +33812,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_evaluate.webp</t>
+          <t>resources/si/renna_newhair/renna_si_shout.webp</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_evaluate.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_shout.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33829,12 +33834,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_front.webp</t>
+          <t>resources/si/renna_newhair/renna_si_smile.webp</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_front.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_smile.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33851,12 +33856,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_intense.webp</t>
+          <t>resources/si/renna_newhair/renna_si_stare.webp</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_intense.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_stare.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33873,12 +33878,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_intense2.webp</t>
+          <t>resources/si/renna_newhair/renna_si_surprise.webp</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_intense2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_surprise.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33895,12 +33900,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_invite.webp</t>
+          <t>resources/si/renna_newhair/renna_si_talkserious.webp</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_invite.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_talkserious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33917,12 +33922,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_lookaway.webp</t>
+          <t>resources/si/renna_newhair/renna_si_talkwork.webp</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_lookaway.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_talkwork.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33939,12 +33944,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_lookawaytalk.webp</t>
+          <t>resources/si/renna_newhair/renna_si_think.webp</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_lookawaytalk.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_think.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33961,12 +33966,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_lookdown.webp</t>
+          <t>resources/si/renna_newhair/renna_si_tire.webp</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_lookdown.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_tire.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33983,12 +33988,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_lookup.webp</t>
+          <t>resources/si/renna_newhair/renna_si_upset.webp</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_lookup.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_upset.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -34005,12 +34010,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_pause.webp</t>
+          <t>resources/si/renna_newhair/renna_si_upsetstare.webp</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_pause.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_upsetstare.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -34027,12 +34032,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_relief.webp</t>
+          <t>resources/si/renna_newhair/renna_si_wake.webp</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_relief.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_wake.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -34049,12 +34054,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_sad.webp</t>
+          <t>resources/si/renna_newhair/renna_si_watch.webp</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_sad.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_watch.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -34071,12 +34076,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_shout.webp</t>
+          <t>resources/si/renna_newhair/renna_si_worry.webp</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_shout.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_worry.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -34093,12 +34098,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_smile.webp</t>
+          <t>resources/si/renna_newhair/renna_si_write.webp</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_smile.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_write.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -34115,12 +34120,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_stare.webp</t>
+          <t>resources/si/renna_si_hug.png</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_stare.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_hug.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -34137,12 +34142,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_surprise.webp</t>
+          <t>resources/si/renna_si_hugangry2.png</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_surprise.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_hugangry2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -34159,12 +34164,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_talkserious.webp</t>
+          <t>resources/si/renna_si_hugclose.png</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_talkserious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_hugclose.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -34181,12 +34186,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_talkwork.webp</t>
+          <t>resources/si/renna_si_huglookaway.png</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_talkwork.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_huglookaway.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -34198,279 +34203,15 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Renna</t>
+          <t>Torsten</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_think.webp</t>
+          <t>resources/si/torsten_si_back.png</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_think.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Renna</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>resources/si/renna_newhair/renna_si_tire.webp</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_tire.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Renna</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>resources/si/renna_newhair/renna_si_upset.webp</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_upset.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Renna</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>resources/si/renna_newhair/renna_si_upsetstare.webp</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_upsetstare.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Renna</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>resources/si/renna_newhair/renna_si_wake.webp</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_wake.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Renna</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>resources/si/renna_newhair/renna_si_watch.webp</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_watch.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Renna</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>resources/si/renna_newhair/renna_si_worry.webp</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_worry.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Renna</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>resources/si/renna_newhair/renna_si_write.webp</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_write.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Renna</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>resources/si/renna_si_hug.png</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_hug.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Renna</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>resources/si/renna_si_hugangry2.png</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_hugangry2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Renna</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>resources/si/renna_si_hugclose.png</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_hugclose.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Renna</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>resources/si/renna_si_huglookaway.png</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_huglookaway.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Torsten</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>resources/si/torsten_si_back.png</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
         <is>
           <t>線上跑的是 torsten_si_back.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
@@ -41444,42 +41185,47 @@
       </c>
     </row>
     <row r="3" ht="111" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>賽西莉</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>cecilie_si_battlecry.webp</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="n"/>
-      <c r="I3" s="4" t="n"/>
-      <c r="J3" s="4" t="n"/>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L3" s="6" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>battlecry</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>1528</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>resources/si/cecilie_si_battlecry.webp</t>
         </is>
@@ -41533,84 +41279,94 @@
       </c>
     </row>
     <row r="5" ht="111" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>賽西莉</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>cecilie_si_call.webp</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>1526</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>resources/si/cecilie_si_call.webp</t>
         </is>
       </c>
     </row>
     <row r="6" ht="111" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>賽西莉</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>cecilie_si_command.webp</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="4" t="n"/>
-      <c r="J6" s="4" t="n"/>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>command</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>1526</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>resources/si/cecilie_si_command.webp</t>
         </is>
@@ -41860,168 +41616,188 @@
       </c>
     </row>
     <row r="12" ht="111" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>賽西莉</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>cecilie_si_nosebleed.webp</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="n"/>
-      <c r="I12" s="4" t="n"/>
-      <c r="J12" s="4" t="n"/>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L12" s="6" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>nosebleed</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>1511</v>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>resources/si/cecilie_si_nosebleed.webp</t>
         </is>
       </c>
     </row>
     <row r="13" ht="111" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>賽西莉</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>cecilie_si_pant.webp</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="n"/>
-      <c r="I13" s="4" t="n"/>
-      <c r="J13" s="4" t="n"/>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L13" s="6" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>pant</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>1443</v>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>resources/si/cecilie_si_pant.webp</t>
         </is>
       </c>
     </row>
     <row r="14" ht="111" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>賽西莉</t>
         </is>
       </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>cecilie_si_proud.webp</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n"/>
-      <c r="J14" s="4" t="n"/>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L14" s="6" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>proud</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>1526</v>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>resources/si/cecilie_si_proud.webp</t>
         </is>
       </c>
     </row>
     <row r="15" ht="111" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>賽西莉</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>cecilie_si_ready.webp</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="n"/>
-      <c r="J15" s="4" t="n"/>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L15" s="6" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>0.701</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>1509</v>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>resources/si/cecilie_si_ready.webp</t>
         </is>
@@ -42130,126 +41906,141 @@
       </c>
     </row>
     <row r="18" ht="111" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>賽西莉</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>cecilie_si_shocknose.webp</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="n"/>
-      <c r="I18" s="4" t="n"/>
-      <c r="J18" s="4" t="n"/>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L18" s="6" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>shocknose</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>1497</v>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
         <is>
           <t>resources/si/cecilie_si_shocknose.webp</t>
         </is>
       </c>
     </row>
     <row r="19" ht="111" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>賽西莉</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>cecilie_si_shyhand.webp</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="n"/>
-      <c r="I19" s="4" t="n"/>
-      <c r="J19" s="4" t="n"/>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L19" s="6" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>shyhand</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>0.5590000000000001</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>1498</v>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t>resources/si/cecilie_si_shyhand.webp</t>
         </is>
       </c>
     </row>
     <row r="20" ht="111" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>賽西莉</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>cecilie_si_shynose.webp</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="n"/>
-      <c r="I20" s="4" t="n"/>
-      <c r="J20" s="4" t="n"/>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L20" s="6" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>shynose</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>1496</v>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>resources/si/cecilie_si_shynose.webp</t>
         </is>
@@ -42307,42 +42098,47 @@
       </c>
     </row>
     <row r="22" ht="111" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>賽西莉</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>cecilie_si_smirk.webp</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="n"/>
-      <c r="I22" s="4" t="n"/>
-      <c r="J22" s="4" t="n"/>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L22" s="6" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>smirk</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="n"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>1529</v>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>resources/si/cecilie_si_smirk.webp</t>
         </is>

--- a/resources/si/_SI_差分總表.xlsx
+++ b/resources/si/_SI_差分總表.xlsx
@@ -16,7 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="茉莉" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="科爾文" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="索菈娜2" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="謎之術師" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="愛里歐" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="蕾娜2" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="亞隆" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="璐娜莉亞" sheetId="13" state="visible" r:id="rId13"/>
@@ -19495,7 +19495,7 @@
     <row r="2" ht="111" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>謎之術師</t>
+          <t>愛里歐</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -19542,7 +19542,7 @@
     <row r="3" ht="111" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>謎之術師</t>
+          <t>愛里歐</t>
         </is>
       </c>
       <c r="B3" s="5" t="n"/>
@@ -19584,7 +19584,7 @@
     <row r="4" ht="111" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>謎之術師</t>
+          <t>愛里歐</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -19631,7 +19631,7 @@
     <row r="5" ht="111" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>謎之術師</t>
+          <t>愛里歐</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -19676,56 +19676,51 @@
       </c>
     </row>
     <row r="6" ht="111" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>謎之術師</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>mage_si_hurtsmile.webp</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>hurtsmile</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>量</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>1529</v>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>resources/si/npc/mage_si_hurtsmile.webp</t>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>愛里歐</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>mage_si_hurtdown.webp</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>✘ 未接線</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>估</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>resources/si/npc/mage_si_hurtdown.webp</t>
         </is>
       </c>
     </row>
     <row r="7" ht="111" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>謎之術師</t>
+          <t>愛里歐</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -19772,7 +19767,7 @@
     <row r="8" ht="111" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>謎之術師</t>
+          <t>愛里歐</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -19819,7 +19814,7 @@
     <row r="9" ht="111" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>謎之術師</t>
+          <t>愛里歐</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -19866,7 +19861,7 @@
     <row r="10" ht="111" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>謎之術師</t>
+          <t>愛里歐</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -19913,7 +19908,7 @@
     <row r="11" ht="111" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>謎之術師</t>
+          <t>愛里歐</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -19960,7 +19955,7 @@
     <row r="12" ht="111" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>謎之術師</t>
+          <t>愛里歐</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -31150,7 +31145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D139"/>
+  <dimension ref="A1:D141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -31959,12 +31954,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Molly</t>
+          <t>Mage</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>molly_si_ask.webp</t>
+          <t>mage_si_hurtdown.webp</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -31986,7 +31981,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>molly_si_closedtalk.webp</t>
+          <t>molly_si_ask.webp</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -32008,7 +32003,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>molly_si_eyesmile.webp</t>
+          <t>molly_si_closedtalk.webp</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -32030,7 +32025,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>molly_si_front.webp</t>
+          <t>molly_si_eyesmile.webp</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -32052,7 +32047,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>molly_si_gossip.webp</t>
+          <t>molly_si_front.webp</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -32074,7 +32069,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>molly_si_lookdown.webp</t>
+          <t>molly_si_gossip.webp</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -32096,7 +32091,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>molly_si_order.webp</t>
+          <t>molly_si_lookdown.webp</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -32118,7 +32113,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>molly_si_serious.webp</t>
+          <t>molly_si_order.webp</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -32140,7 +32135,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>molly_si_softsmile.webp</t>
+          <t>molly_si_serious.webp</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -32162,7 +32157,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>molly_si_stern.webp</t>
+          <t>molly_si_softsmile.webp</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -32184,7 +32179,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>molly_si_superior.webp</t>
+          <t>molly_si_stern.webp</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -32206,7 +32201,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>molly_si_surprise.webp</t>
+          <t>molly_si_superior.webp</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -32228,7 +32223,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>molly_si_talk.webp</t>
+          <t>molly_si_surprise.webp</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -32250,7 +32245,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>molly_si_think.webp</t>
+          <t>molly_si_talk.webp</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -32272,7 +32267,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>molly_si_whisper.webp</t>
+          <t>molly_si_think.webp</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -32289,12 +32284,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>npc_ss_lofa_shoot</t>
+          <t>Molly</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>npc_ss_lofa_shoot.png</t>
+          <t>molly_si_whisper.webp</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -32311,12 +32306,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>npc_ss_lofa_shoot</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>robert_si_blindeye.webp</t>
+          <t>npc_ss_lofa_shoot.png</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -32338,7 +32333,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>robert_si_bow.webp</t>
+          <t>robert_si_blindeye.webp</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -32360,7 +32355,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>robert_si_closedtalk.webp</t>
+          <t>robert_si_bow.webp</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -32382,7 +32377,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>robert_si_front.webp</t>
+          <t>robert_si_closedtalk.webp</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -32404,7 +32399,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>robert_si_sideeye.webp</t>
+          <t>robert_si_front.webp</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -32426,7 +32421,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>robert_si_surprise.webp</t>
+          <t>robert_si_sideeye.webp</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -32448,7 +32443,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>robert_si_talk.webp</t>
+          <t>robert_si_surprise.webp</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -32465,12 +32460,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Renna</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>renna_si_evalutatingclosemouth.webp</t>
+          <t>robert_si_talk.webp</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -32492,7 +32487,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>renna_si_annoy.webp</t>
+          <t>renna_si_evalutatingclosemouth.webp</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -32509,12 +32504,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Sorana</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>sorana_si_q.webp</t>
+          <t>renna_si_annoy.webp</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -32531,12 +32526,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T150615.066</t>
+          <t>Sorana</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T150615.066.png</t>
+          <t>sorana_si_q.webp</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -32553,12 +32548,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T150842.343</t>
+          <t>image - 2026-09-20T150615.066</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T150842.343.png</t>
+          <t>image - 2026-09-20T150615.066.png</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -32575,12 +32570,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T151013.881</t>
+          <t>image - 2026-09-20T150842.343</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T151013.881.png</t>
+          <t>image - 2026-09-20T150842.343.png</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -32597,12 +32592,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T151141.942</t>
+          <t>image - 2026-09-20T151013.881</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>image - 2026-09-20T151141.942.png</t>
+          <t>image - 2026-09-20T151013.881.png</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -32619,12 +32614,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Torsten</t>
+          <t>image - 2026-09-20T151141.942</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>torsten_si_front.webp</t>
+          <t>image - 2026-09-20T151141.942.png</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -32646,7 +32641,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>torsten_si_q.webp</t>
+          <t>torsten_si_front.webp</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -32663,12 +32658,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Xanya</t>
+          <t>Torsten</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>xanya_si_front.webp</t>
+          <t>torsten_si_q.webp</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -32680,44 +32675,44 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>同差分的另一個版本</t>
+          <t>美術交了沒接線</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Anya</t>
+          <t>Xanya</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>resources/si/anya_si_nod.png</t>
+          <t>xanya_si_front.webp</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>線上跑的是 anya_si_nod.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>在 script/speakers.js 的 ART 補一筆 expr，並量 fx／top／bot（§6.5）</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>同差分的另一個版本</t>
+          <t>指到但檔案不在</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>mage / hurtsmile</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>resources/si/cecilie_si_saintinstall.png</t>
+          <t>resources/si/npc/mage_si_hurtsmile.webp</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_saintinstall.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>路徑打錯，或美術還沒交 —— 演到那一句會回退基本立繪</t>
         </is>
       </c>
     </row>
@@ -32729,17 +32724,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Misha</t>
+          <t>Anya</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>resources/si/misha_si_fight.png</t>
+          <t>resources/si/anya_si_nod.png</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>線上跑的是 misha_si_fight.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 anya_si_nod.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -32751,17 +32746,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Misha</t>
+          <t>Cecilie</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>resources/si/misha_si_ni.png</t>
+          <t>resources/si/cecilie_si_saintinstall.png</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>線上跑的是 misha_si_ni.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_saintinstall.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -32773,17 +32768,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Nouvelle</t>
+          <t>Misha</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>resources/si/nouvelle_si_gossip1.png</t>
+          <t>resources/si/misha_si_fight.png</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>線上跑的是 nouvelle_si_gossip1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 misha_si_fight.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -32795,17 +32790,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Nouvelle</t>
+          <t>Misha</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>resources/si/nouvelle_si_salute.png</t>
+          <t>resources/si/misha_si_ni.png</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>線上跑的是 nouvelle_si_salute.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 misha_si_ni.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -32822,12 +32817,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>resources/si/nouvelle_si_sigh.png</t>
+          <t>resources/si/nouvelle_si_gossip1.png</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>線上跑的是 nouvelle_si_sigh.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 nouvelle_si_gossip1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -32839,17 +32834,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Npc_grocer</t>
+          <t>Nouvelle</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_grocer_si_v2.webp</t>
+          <t>resources/si/nouvelle_si_salute.png</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 nouvelle_si_salute.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -32861,17 +32856,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Npc_grocer</t>
+          <t>Nouvelle</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_grocer_si_v3.webp</t>
+          <t>resources/si/nouvelle_si_sigh.png</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 nouvelle_si_sigh.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -32888,7 +32883,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_grocer_si_v4.webp</t>
+          <t>resources/si/npc/npc_grocer_si_v2.webp</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -32910,7 +32905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_grocer_si_v5.webp</t>
+          <t>resources/si/npc/npc_grocer_si_v3.webp</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -32927,17 +32922,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Npc_guildcounter</t>
+          <t>Npc_grocer</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_guildcounter_si_v1.webp</t>
+          <t>resources/si/npc/npc_grocer_si_v4.webp</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_guildcounter_si_v5.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -32949,17 +32944,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Npc_guildcounter</t>
+          <t>Npc_grocer</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_guildcounter_si_v3.webp</t>
+          <t>resources/si/npc/npc_grocer_si_v5.webp</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_guildcounter_si_v5.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -32976,7 +32971,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_guildcounter_si_v4.webp</t>
+          <t>resources/si/npc/npc_guildcounter_si_v1.webp</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -32993,17 +32988,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Npc_gunsmith</t>
+          <t>Npc_guildcounter</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_gunsmith_si_v2.webp</t>
+          <t>resources/si/npc/npc_guildcounter_si_v3.webp</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_guildcounter_si_v5.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33015,17 +33010,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Npc_gunsmith</t>
+          <t>Npc_guildcounter</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_gunsmith_si_v3.webp</t>
+          <t>resources/si/npc/npc_guildcounter_si_v4.webp</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_guildcounter_si_v5.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33042,7 +33037,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_gunsmith_si_v4.webp</t>
+          <t>resources/si/npc/npc_gunsmith_si_v2.webp</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -33064,7 +33059,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_gunsmith_si_v5.webp</t>
+          <t>resources/si/npc/npc_gunsmith_si_v3.webp</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -33081,17 +33076,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Npc_gunsmith</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_front.png</t>
+          <t>resources/si/npc/npc_gunsmith_si_v4.webp</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_front.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33103,17 +33098,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Npc_gunsmith</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_lookaside.png</t>
+          <t>resources/si/npc/npc_gunsmith_si_v5.webp</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_lookaside.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33130,12 +33125,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_sadback.png</t>
+          <t>resources/si/old/cecilie_si_front.png</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_sadback.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_front.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33152,12 +33147,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_smile.png</t>
+          <t>resources/si/old/cecilie_si_lookaside.png</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_smile.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_lookaside.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33174,12 +33169,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_tease.png</t>
+          <t>resources/si/old/cecilie_si_sadback.png</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_tease.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_sadback.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33196,12 +33191,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_upset.png</t>
+          <t>resources/si/old/cecilie_si_smile.png</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_upset.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_smile.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33213,17 +33208,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Renna</t>
+          <t>Cecilie</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_argue.webp</t>
+          <t>resources/si/old/cecilie_si_tease.png</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_argue.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_tease.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33235,17 +33230,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Renna</t>
+          <t>Cecilie</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_arguecute.webp</t>
+          <t>resources/si/old/cecilie_si_upset.png</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_arguecute.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_upset.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33262,12 +33257,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_ask.webp</t>
+          <t>resources/si/renna_newhair/renna_si_argue.webp</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_ask.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_argue.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33284,12 +33279,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_askserious.webp</t>
+          <t>resources/si/renna_newhair/renna_si_arguecute.webp</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_askserious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_arguecute.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33306,12 +33301,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_awkwerd.webp</t>
+          <t>resources/si/renna_newhair/renna_si_ask.webp</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_awkwerd.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_ask.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33328,12 +33323,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_blush.webp</t>
+          <t>resources/si/renna_newhair/renna_si_askserious.webp</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_blush.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_askserious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33350,12 +33345,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_bow.webp</t>
+          <t>resources/si/renna_newhair/renna_si_awkwerd.webp</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_bow.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_awkwerd.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33372,12 +33367,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_callangry.webp</t>
+          <t>resources/si/renna_newhair/renna_si_blush.webp</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_callangry.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_blush.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33394,12 +33389,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_chase.webp</t>
+          <t>resources/si/renna_newhair/renna_si_bow.webp</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_chase.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_bow.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33416,12 +33411,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_chase2.webp</t>
+          <t>resources/si/renna_newhair/renna_si_callangry.webp</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_chase2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_callangry.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33438,12 +33433,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_command.webp</t>
+          <t>resources/si/renna_newhair/renna_si_chase.webp</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_command.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_chase.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33460,12 +33455,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_covermouth.webp</t>
+          <t>resources/si/renna_newhair/renna_si_chase2.webp</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_covermouth.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_chase2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33482,12 +33477,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_cringe.webp</t>
+          <t>resources/si/renna_newhair/renna_si_command.webp</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_cringe.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_command.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33504,12 +33499,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_curious.webp</t>
+          <t>resources/si/renna_newhair/renna_si_covermouth.webp</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_curious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_covermouth.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33526,12 +33521,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_die.webp</t>
+          <t>resources/si/renna_newhair/renna_si_cringe.webp</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_die.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_cringe.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33548,12 +33543,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_evaluate.webp</t>
+          <t>resources/si/renna_newhair/renna_si_curious.webp</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_evaluate.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_curious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33570,12 +33565,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_front.webp</t>
+          <t>resources/si/renna_newhair/renna_si_die.webp</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_front.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_die.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33592,12 +33587,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_intense.webp</t>
+          <t>resources/si/renna_newhair/renna_si_evaluate.webp</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_intense.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_evaluate.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33614,12 +33609,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_intense2.webp</t>
+          <t>resources/si/renna_newhair/renna_si_front.webp</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_intense2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_front.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33636,12 +33631,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_invite.webp</t>
+          <t>resources/si/renna_newhair/renna_si_intense.webp</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_invite.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_intense.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33658,12 +33653,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_lookaway.webp</t>
+          <t>resources/si/renna_newhair/renna_si_intense2.webp</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_lookaway.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_intense2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33680,12 +33675,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_lookawaytalk.webp</t>
+          <t>resources/si/renna_newhair/renna_si_invite.webp</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_lookawaytalk.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_invite.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33702,12 +33697,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_lookdown.webp</t>
+          <t>resources/si/renna_newhair/renna_si_lookaway.webp</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_lookdown.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_lookaway.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33724,12 +33719,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_lookup.webp</t>
+          <t>resources/si/renna_newhair/renna_si_lookawaytalk.webp</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_lookup.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_lookawaytalk.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33746,12 +33741,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_pause.webp</t>
+          <t>resources/si/renna_newhair/renna_si_lookdown.webp</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_pause.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_lookdown.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33768,12 +33763,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_relief.webp</t>
+          <t>resources/si/renna_newhair/renna_si_lookup.webp</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_relief.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_lookup.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33790,12 +33785,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_sad.webp</t>
+          <t>resources/si/renna_newhair/renna_si_pause.webp</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_sad.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_pause.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33812,12 +33807,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_shout.webp</t>
+          <t>resources/si/renna_newhair/renna_si_relief.webp</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_shout.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_relief.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33834,12 +33829,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_smile.webp</t>
+          <t>resources/si/renna_newhair/renna_si_sad.webp</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_smile.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_sad.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33856,12 +33851,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_stare.webp</t>
+          <t>resources/si/renna_newhair/renna_si_shout.webp</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_stare.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_shout.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33878,12 +33873,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_surprise.webp</t>
+          <t>resources/si/renna_newhair/renna_si_smile.webp</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_surprise.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_smile.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33900,12 +33895,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_talkserious.webp</t>
+          <t>resources/si/renna_newhair/renna_si_stare.webp</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_talkserious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_stare.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33922,12 +33917,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_talkwork.webp</t>
+          <t>resources/si/renna_newhair/renna_si_surprise.webp</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_talkwork.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_surprise.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33944,12 +33939,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_think.webp</t>
+          <t>resources/si/renna_newhair/renna_si_talkserious.webp</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_think.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_talkserious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33966,12 +33961,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_tire.webp</t>
+          <t>resources/si/renna_newhair/renna_si_talkwork.webp</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_tire.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_talkwork.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33988,12 +33983,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_upset.webp</t>
+          <t>resources/si/renna_newhair/renna_si_think.webp</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_upset.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_think.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -34010,12 +34005,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_upsetstare.webp</t>
+          <t>resources/si/renna_newhair/renna_si_tire.webp</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_upsetstare.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_tire.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -34032,12 +34027,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_wake.webp</t>
+          <t>resources/si/renna_newhair/renna_si_upset.webp</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_wake.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_upset.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -34054,12 +34049,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_watch.webp</t>
+          <t>resources/si/renna_newhair/renna_si_upsetstare.webp</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_watch.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_upsetstare.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -34076,12 +34071,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_worry.webp</t>
+          <t>resources/si/renna_newhair/renna_si_wake.webp</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_worry.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_wake.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -34098,12 +34093,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_write.webp</t>
+          <t>resources/si/renna_newhair/renna_si_watch.webp</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_write.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_watch.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -34120,12 +34115,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_hug.png</t>
+          <t>resources/si/renna_newhair/renna_si_worry.webp</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_hug.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_worry.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -34142,12 +34137,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_hugangry2.png</t>
+          <t>resources/si/renna_newhair/renna_si_write.webp</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_hugangry2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_write.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -34164,12 +34159,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_hugclose.png</t>
+          <t>resources/si/renna_si_hug.png</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_hugclose.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_hug.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -34186,12 +34181,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_huglookaway.png</t>
+          <t>resources/si/renna_si_hugangry2.png</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_huglookaway.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_hugangry2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -34203,15 +34198,59 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
+          <t>Renna</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>resources/si/renna_si_hugclose.png</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>線上跑的是 renna_si_hugclose.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>同差分的另一個版本</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Renna</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>resources/si/renna_si_huglookaway.png</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>線上跑的是 renna_si_huglookaway.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>同差分的另一個版本</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
           <t>Torsten</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
+      <c r="C141" t="inlineStr">
         <is>
           <t>resources/si/torsten_si_back.png</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="D141" t="inlineStr">
         <is>
           <t>線上跑的是 torsten_si_back.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>

--- a/resources/si/_SI_差分總表.xlsx
+++ b/resources/si/_SI_差分總表.xlsx
@@ -8152,6 +8152,356 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId56"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>57</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1333500" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="57" name="Image 57" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId57"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>58</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1333500" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="58" name="Image 58" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId58"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>59</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1333500" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="59" name="Image 59" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId59"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>60</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1333500" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="60" name="Image 60" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId60"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>61</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1333500" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="61" name="Image 61" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId61"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>62</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1333500" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="62" name="Image 62" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId62"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>63</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1333500" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="63" name="Image 63" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId63"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>64</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1333500" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="64" name="Image 64" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId64"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>65</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1333500" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="65" name="Image 65" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId65"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>66</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1333500" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="66" name="Image 66" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId66"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1333500" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="67" name="Image 67" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId67"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>68</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1333500" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="68" name="Image 68" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId68"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>69</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1333500" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="69" name="Image 69" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId69"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>70</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1333500" cy="1333500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="70" name="Image 70" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId70"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -19676,42 +20026,47 @@
       </c>
     </row>
     <row r="6" ht="111" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>愛里歐</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>mage_si_hurtdown.webp</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>✘ 未接線</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>估</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="4" t="n"/>
-      <c r="J6" s="4" t="n"/>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>hurtdown</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>1517</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>resources/si/npc/mage_si_hurtdown.webp</t>
         </is>
@@ -28134,7 +28489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:L71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -28342,13 +28697,13 @@
     <row r="5" ht="111" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>f734e7ba-e7bb-457b-8cf7-66e13324c45d</t>
+          <t>a69b6fbd-57a2-4ca2-852c-2a6ac63f8a25</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>f734e7ba-e7bb-457b-8cf7-66e13324c45d.png</t>
+          <t>a69b6fbd-57a2-4ca2-852c-2a6ac63f8a25.png</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -28377,160 +28732,155 @@
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
+          <t>resources/si/npc/a69b6fbd-57a2-4ca2-852c-2a6ac63f8a25.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="111" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>commander</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>npc_commander_si_front.webp</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>(base)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>1525</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/npc/npc_commander_si_front.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="111" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>f734e7ba-e7bb-457b-8cf7-66e13324c45d</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>f734e7ba-e7bb-457b-8cf7-66e13324c45d.png</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>✘ 未接線</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>估</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="n"/>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="4" t="n"/>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
           <t>resources/si/npc/f734e7ba-e7bb-457b-8cf7-66e13324c45d.png</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="111" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="8" ht="111" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>npc_ss_lofa_shoot</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>npc_ss_lofa_shoot.png</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>✘ 未接線</t>
         </is>
       </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>估</t>
         </is>
       </c>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="4" t="n"/>
-      <c r="J6" s="4" t="n"/>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="inlineStr">
+      <c r="H8" s="4" t="n"/>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="4" t="n"/>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
         <is>
           <t>resources/si/npc/npc_ss_lofa_shoot.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="111" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>前台</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>npc_hotel_capital.webp</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>(base)</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>量</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>0.494</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>1535</v>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>resources/si/npc/npc_hotel_capital.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="111" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>司祭</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>npc_np_priest.webp</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>(base)</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>✔</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>量</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>1527</v>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>resources/si/npc/npc_np_priest.webp</t>
         </is>
       </c>
     </row>
     <row r="9" ht="111" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>娜塔莉</t>
+          <t>前台</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>npc_natalia_si_dead.webp</t>
+          <t>npc_hotel_capital.webp</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>dead</t>
+          <t>(base)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -28545,10 +28895,10 @@
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.363</v>
+        <v>0.494</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>1535</v>
@@ -28560,19 +28910,19 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_natalia_si_dead.webp</t>
+          <t>resources/si/npc/npc_hotel_capital.webp</t>
         </is>
       </c>
     </row>
     <row r="10" ht="111" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>娜塔莉</t>
+          <t>司祭</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>npc_natalia_si_die.webp</t>
+          <t>npc_np_priest.webp</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -28592,13 +28942,13 @@
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.363</v>
+        <v>0.46</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>103</v>
+        <v>5</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1535</v>
+        <v>1527</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -28607,24 +28957,24 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_natalia_si_die.webp</t>
+          <t>resources/si/npc/npc_np_priest.webp</t>
         </is>
       </c>
     </row>
     <row r="11" ht="111" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>小女孩</t>
+          <t>士兵</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_loti_ask.webp</t>
+          <t>npc_imsoldier_si_alarm.webp</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>(base)</t>
+          <t>alarm</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -28639,13 +28989,13 @@
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.477</v>
+        <v>0.351</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1527</v>
+        <v>1507</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
@@ -28654,24 +29004,24 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_loti_ask.webp</t>
+          <t>resources/si/npc/npc_imsoldier_si_alarm.webp</t>
         </is>
       </c>
     </row>
     <row r="12" ht="111" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>小女孩</t>
+          <t>士兵</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_loti_cry.webp</t>
+          <t>npc_imsoldier_si_awe.webp</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>cry</t>
+          <t>awe</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -28686,13 +29036,13 @@
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0.46</v>
+        <v>0.406</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1520</v>
+        <v>1514</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -28701,24 +29051,24 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_loti_cry.webp</t>
+          <t>resources/si/npc/npc_imsoldier_si_awe.webp</t>
         </is>
       </c>
     </row>
     <row r="13" ht="111" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>小女孩</t>
+          <t>士兵</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_loti_give.webp</t>
+          <t>npc_imsoldier_si_doubt.webp</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>give</t>
+          <t>doubt</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -28733,13 +29083,13 @@
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.463</v>
+        <v>0.647</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1529</v>
+        <v>1521</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
@@ -28748,24 +29098,24 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_loti_give.webp</t>
+          <t>resources/si/npc/npc_imsoldier_si_doubt.webp</t>
         </is>
       </c>
     </row>
     <row r="14" ht="111" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>小女孩</t>
+          <t>士兵</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_loti_guard.webp</t>
+          <t>npc_imsoldier_si_front.webp</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>guard</t>
+          <t>(base)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -28780,13 +29130,13 @@
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.51</v>
+        <v>0.493</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1529</v>
+        <v>1516</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
@@ -28795,24 +29145,24 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_loti_guard.webp</t>
+          <t>resources/si/npc/npc_imsoldier_si_front.webp</t>
         </is>
       </c>
     </row>
     <row r="15" ht="111" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>小女孩</t>
+          <t>士兵</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_loti_happy.webp</t>
+          <t>npc_imsoldier_si_panic.webp</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>panic</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -28827,13 +29177,13 @@
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.441</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1523</v>
+        <v>1517</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
@@ -28842,24 +29192,24 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_loti_happy.webp</t>
+          <t>resources/si/npc/npc_imsoldier_si_panic.webp</t>
         </is>
       </c>
     </row>
     <row r="16" ht="111" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>小女孩</t>
+          <t>士兵</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_loti_sad.webp</t>
+          <t>npc_imsoldier_si_rally.webp</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>sad</t>
+          <t>rally</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -28874,13 +29224,13 @@
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0.475</v>
+        <v>0.365</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1523</v>
+        <v>1512</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -28889,24 +29239,24 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_loti_sad.webp</t>
+          <t>resources/si/npc/npc_imsoldier_si_rally.webp</t>
         </is>
       </c>
     </row>
     <row r="17" ht="111" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>小女孩</t>
+          <t>士兵</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_loti_shock.webp</t>
+          <t>npc_imsoldier_si_worried.webp</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>shock</t>
+          <t>worry</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -28921,13 +29271,13 @@
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>0.461</v>
+        <v>0.592</v>
       </c>
       <c r="I17" s="2" t="n">
         <v>11</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1530</v>
+        <v>1519</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
@@ -28936,24 +29286,24 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_loti_shock.webp</t>
+          <t>resources/si/npc/npc_imsoldier_si_worried.webp</t>
         </is>
       </c>
     </row>
     <row r="18" ht="111" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>小男孩</t>
+          <t>娜塔莉</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>capi_boy.webp</t>
+          <t>npc_natalia_si_dead.webp</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>(base)</t>
+          <t>dead</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -28968,13 +29318,13 @@
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0.352</v>
+        <v>0.363</v>
       </c>
       <c r="I18" s="2" t="n">
         <v>47</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1501</v>
+        <v>1535</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
@@ -28983,24 +29333,24 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/capi_boy.webp</t>
+          <t>resources/si/npc/npc_natalia_si_dead.webp</t>
         </is>
       </c>
     </row>
     <row r="19" ht="111" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>少女</t>
+          <t>娜塔莉</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_lofa_ask.webp</t>
+          <t>npc_natalia_si_die.webp</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>(base)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -29015,13 +29365,13 @@
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>0.497</v>
+        <v>0.363</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1522</v>
+        <v>1535</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
@@ -29030,24 +29380,24 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_lofa_ask.webp</t>
+          <t>resources/si/npc/npc_natalia_si_die.webp</t>
         </is>
       </c>
     </row>
     <row r="20" ht="111" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>少女</t>
+          <t>小女孩</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_lofa_complain.webp</t>
+          <t>npc_ss_loti_ask.webp</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>complain</t>
+          <t>(base)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -29062,13 +29412,13 @@
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>0.488</v>
+        <v>0.477</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
@@ -29077,19 +29427,19 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_lofa_complain.webp</t>
+          <t>resources/si/npc/npc_ss_loti_ask.webp</t>
         </is>
       </c>
     </row>
     <row r="21" ht="111" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>少女</t>
+          <t>小女孩</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_lofa_cry.webp</t>
+          <t>npc_ss_loti_cry.webp</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -29109,39 +29459,39 @@
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>0.464</v>
+        <v>0.46</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1525</v>
+        <v>1520</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1024×1535</t>
+          <t>1024×1536</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_lofa_cry.webp</t>
+          <t>resources/si/npc/npc_ss_loti_cry.webp</t>
         </is>
       </c>
     </row>
     <row r="22" ht="111" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>少女</t>
+          <t>小女孩</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_lofa_cryhug.webp</t>
+          <t>npc_ss_loti_give.webp</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>cryhug</t>
+          <t>give</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -29156,13 +29506,13 @@
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>0.594</v>
+        <v>0.463</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
@@ -29171,24 +29521,24 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_lofa_cryhug.webp</t>
+          <t>resources/si/npc/npc_ss_loti_give.webp</t>
         </is>
       </c>
     </row>
     <row r="23" ht="111" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>少女</t>
+          <t>小女孩</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_lofa_front.webp</t>
+          <t>npc_ss_loti_guard.webp</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>(base)</t>
+          <t>guard</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -29203,10 +29553,10 @@
         </is>
       </c>
       <c r="H23" s="2" t="n">
-        <v>0.431</v>
+        <v>0.51</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>1529</v>
@@ -29218,24 +29568,24 @@
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_lofa_front.webp</t>
+          <t>resources/si/npc/npc_ss_loti_guard.webp</t>
         </is>
       </c>
     </row>
     <row r="24" ht="111" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>少女</t>
+          <t>小女孩</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_lofa_lookaway.webp</t>
+          <t>npc_ss_loti_happy.webp</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>lookaway</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -29250,10 +29600,10 @@
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>0.454</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>1523</v>
@@ -29265,24 +29615,24 @@
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_lofa_lookaway.webp</t>
+          <t>resources/si/npc/npc_ss_loti_happy.webp</t>
         </is>
       </c>
     </row>
     <row r="25" ht="111" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>少女</t>
+          <t>小女孩</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_lofa_lookdown.webp</t>
+          <t>npc_ss_loti_sad.webp</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>lookdown</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -29297,13 +29647,13 @@
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>0.512</v>
+        <v>0.475</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
@@ -29312,24 +29662,24 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_lofa_lookdown.webp</t>
+          <t>resources/si/npc/npc_ss_loti_sad.webp</t>
         </is>
       </c>
     </row>
     <row r="26" ht="111" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>少女</t>
+          <t>小女孩</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_lofa_shy.webp</t>
+          <t>npc_ss_loti_shock.webp</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>shy</t>
+          <t>shock</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -29344,13 +29694,13 @@
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>0.48</v>
+        <v>0.461</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1521</v>
+        <v>1530</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
@@ -29359,24 +29709,24 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_lofa_shy.webp</t>
+          <t>resources/si/npc/npc_ss_loti_shock.webp</t>
         </is>
       </c>
     </row>
     <row r="27" ht="111" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>少女</t>
+          <t>小男孩</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_lofa_talk.webp</t>
+          <t>capi_boy.webp</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>talk</t>
+          <t>(base)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -29391,13 +29741,13 @@
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>0.464</v>
+        <v>0.352</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1530</v>
+        <v>1501</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
@@ -29406,24 +29756,24 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_lofa_talk.webp</t>
+          <t>resources/si/npc/capi_boy.webp</t>
         </is>
       </c>
     </row>
     <row r="28" ht="111" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>店主</t>
+          <t>少女</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>npc_capital_gunstore_si.webp</t>
+          <t>npc_ss_lofa_ask.webp</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>(base)</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -29438,13 +29788,13 @@
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>0.476</v>
+        <v>0.497</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1531</v>
+        <v>1522</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
@@ -29453,24 +29803,24 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_capital_gunstore_si.webp</t>
+          <t>resources/si/npc/npc_ss_lofa_ask.webp</t>
         </is>
       </c>
     </row>
     <row r="29" ht="111" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>店主</t>
+          <t>少女</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>npc_grocer_si_v1.webp</t>
+          <t>npc_ss_lofa_complain.webp</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>(base)</t>
+          <t>complain</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -29478,24 +29828,20 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>4 張：npc_grocer_si_v2.webp、npc_grocer_si_v3.webp、npc_grocer_si_v4.webp…</t>
-        </is>
-      </c>
+      <c r="F29" s="3" t="n"/>
       <c r="G29" s="2" t="inlineStr">
         <is>
           <t>量</t>
         </is>
       </c>
       <c r="H29" s="2" t="n">
-        <v>0.442</v>
+        <v>0.488</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
@@ -29504,24 +29850,24 @@
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_grocer_si_v1.webp</t>
+          <t>resources/si/npc/npc_ss_lofa_complain.webp</t>
         </is>
       </c>
     </row>
     <row r="30" ht="111" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>店主</t>
+          <t>少女</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>npc_grocerie_si.webp</t>
+          <t>npc_ss_lofa_cry.webp</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>(base)</t>
+          <t>cry</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -29536,39 +29882,39 @@
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>0.434</v>
+        <v>0.464</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1533</v>
+        <v>1525</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1024×1536</t>
+          <t>1024×1535</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_grocerie_si.webp</t>
+          <t>resources/si/npc/npc_ss_lofa_cry.webp</t>
         </is>
       </c>
     </row>
     <row r="31" ht="111" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>店主</t>
+          <t>少女</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>npc_grocery_si_northport.webp</t>
+          <t>npc_ss_lofa_cryhug.webp</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>(base)</t>
+          <t>cryhug</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -29583,13 +29929,13 @@
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>0.515</v>
+        <v>0.594</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
@@ -29598,19 +29944,19 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_grocery_si_northport.webp</t>
+          <t>resources/si/npc/npc_ss_lofa_cryhug.webp</t>
         </is>
       </c>
     </row>
     <row r="32" ht="111" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>店主</t>
+          <t>少女</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>npc_gunsmith_si_northport.webp</t>
+          <t>npc_ss_lofa_front.webp</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -29630,13 +29976,13 @@
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>0.547</v>
+        <v>0.431</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1524</v>
+        <v>1529</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
@@ -29645,24 +29991,24 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_gunsmith_si_northport.webp</t>
+          <t>resources/si/npc/npc_ss_lofa_front.webp</t>
         </is>
       </c>
     </row>
     <row r="33" ht="111" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>店主</t>
+          <t>少女</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>npc_gunsmith_si_v1.webp</t>
+          <t>npc_ss_lofa_lookaway.webp</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>(base)</t>
+          <t>lookaway</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -29670,24 +30016,20 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>4 張：npc_gunsmith_si_v2.webp、npc_gunsmith_si_v3.webp、npc_gunsmith_si_v4.webp…</t>
-        </is>
-      </c>
+      <c r="F33" s="3" t="n"/>
       <c r="G33" s="2" t="inlineStr">
         <is>
           <t>量</t>
         </is>
       </c>
       <c r="H33" s="2" t="n">
-        <v>0.546</v>
+        <v>0.454</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1506</v>
+        <v>1523</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
@@ -29696,24 +30038,24 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_gunsmith_si_v1.webp</t>
+          <t>resources/si/npc/npc_ss_lofa_lookaway.webp</t>
         </is>
       </c>
     </row>
     <row r="34" ht="111" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>指揮官</t>
+          <t>少女</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>npc_commander_si_front.webp</t>
+          <t>npc_ss_lofa_lookdown.webp</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>(base)</t>
+          <t>lookdown</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -29728,13 +30070,13 @@
         </is>
       </c>
       <c r="H34" s="2" t="n">
-        <v>0.53</v>
+        <v>0.512</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1525</v>
+        <v>1522</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
@@ -29743,24 +30085,24 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_commander_si_front.webp</t>
+          <t>resources/si/npc/npc_ss_lofa_lookdown.webp</t>
         </is>
       </c>
     </row>
     <row r="35" ht="111" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>村民</t>
+          <t>少女</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>npc_shinier_grocery_si.webp</t>
+          <t>npc_ss_lofa_shy.webp</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>(base)</t>
+          <t>shy</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -29775,13 +30117,13 @@
         </is>
       </c>
       <c r="H35" s="2" t="n">
-        <v>0.542</v>
+        <v>0.48</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1530</v>
+        <v>1521</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
@@ -29790,24 +30132,24 @@
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_shinier_grocery_si.webp</t>
+          <t>resources/si/npc/npc_ss_lofa_shy.webp</t>
         </is>
       </c>
     </row>
     <row r="36" ht="111" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>村民</t>
+          <t>少女</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>npc_shinier_gunsmith_si.webp</t>
+          <t>npc_ss_lofa_talk.webp</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>(base)</t>
+          <t>talk</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -29822,13 +30164,13 @@
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>0.603</v>
+        <v>0.464</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
@@ -29837,19 +30179,19 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_shinier_gunsmith_si.webp</t>
+          <t>resources/si/npc/npc_ss_lofa_talk.webp</t>
         </is>
       </c>
     </row>
     <row r="37" ht="111" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>村民</t>
+          <t>店主</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>npc_shinier_hunter_si.webp</t>
+          <t>npc_capital_gunstore_si.webp</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -29869,13 +30211,13 @@
         </is>
       </c>
       <c r="H37" s="2" t="n">
-        <v>0.421</v>
+        <v>0.476</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1524</v>
+        <v>1531</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
@@ -29884,19 +30226,19 @@
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_shinier_hunter_si.webp</t>
+          <t>resources/si/npc/npc_capital_gunstore_si.webp</t>
         </is>
       </c>
     </row>
     <row r="38" ht="111" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>村長</t>
+          <t>店主</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>npc_shinier_chief_si.webp</t>
+          <t>npc_grocer_si_v1.webp</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -29909,20 +30251,24 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F38" s="3" t="n"/>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>4 張：npc_grocer_si_v2.webp、npc_grocer_si_v3.webp、npc_grocer_si_v4.webp…</t>
+        </is>
+      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
           <t>量</t>
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>0.537</v>
+        <v>0.442</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1520</v>
+        <v>1527</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
@@ -29931,19 +30277,19 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_shinier_chief_si.webp</t>
+          <t>resources/si/npc/npc_grocer_si_v1.webp</t>
         </is>
       </c>
     </row>
     <row r="39" ht="111" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>櫃台</t>
+          <t>店主</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>guildcounterca_si.webp</t>
+          <t>npc_grocerie_si.webp</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -29963,13 +30309,13 @@
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>0.511</v>
+        <v>0.434</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1526</v>
+        <v>1533</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
@@ -29978,19 +30324,19 @@
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>resources/si/guildcounterca_si.webp</t>
+          <t>resources/si/npc/npc_grocerie_si.webp</t>
         </is>
       </c>
     </row>
     <row r="40" ht="111" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>櫃台</t>
+          <t>店主</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>npc_guildcounter_si_northport.webp</t>
+          <t>npc_grocery_si_northport.webp</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -30010,13 +30356,13 @@
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>0.49</v>
+        <v>0.515</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1522</v>
+        <v>1531</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
@@ -30025,19 +30371,19 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_guildcounter_si_northport.webp</t>
+          <t>resources/si/npc/npc_grocery_si_northport.webp</t>
         </is>
       </c>
     </row>
     <row r="41" ht="111" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>櫃台</t>
+          <t>店主</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>npc_guildcounter_si_v5.webp</t>
+          <t>npc_gunsmith_si_northport.webp</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -30050,24 +30396,20 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>3 張：npc_guildcounter_si_v1.webp、npc_guildcounter_si_v3.webp、npc_guildcounter_si_v4.webp</t>
-        </is>
-      </c>
+      <c r="F41" s="3" t="n"/>
       <c r="G41" s="2" t="inlineStr">
         <is>
           <t>量</t>
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>0.492</v>
+        <v>0.547</v>
       </c>
       <c r="I41" s="2" t="n">
         <v>11</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1531</v>
+        <v>1524</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
@@ -30076,24 +30418,24 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_guildcounter_si_v5.webp</t>
+          <t>resources/si/npc/npc_gunsmith_si_northport.webp</t>
         </is>
       </c>
     </row>
     <row r="42" ht="111" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>櫃台</t>
+          <t>店主</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_cityhall_cringe.webp</t>
+          <t>npc_gunsmith_si_v1.webp</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>cringe</t>
+          <t>(base)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -30101,20 +30443,24 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F42" s="3" t="n"/>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>4 張：npc_gunsmith_si_v2.webp、npc_gunsmith_si_v3.webp、npc_gunsmith_si_v4.webp…</t>
+        </is>
+      </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
           <t>量</t>
         </is>
       </c>
       <c r="H42" s="2" t="n">
-        <v>0.494</v>
+        <v>0.546</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1520</v>
+        <v>1506</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
@@ -30123,19 +30469,19 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_cityhall_cringe.webp</t>
+          <t>resources/si/npc/npc_gunsmith_si_v1.webp</t>
         </is>
       </c>
     </row>
     <row r="43" ht="111" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>櫃台</t>
+          <t>指揮官</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_cityhall_front.webp</t>
+          <t>npc_imcommander_si_front.webp</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -30155,13 +30501,13 @@
         </is>
       </c>
       <c r="H43" s="2" t="n">
-        <v>0.582</v>
+        <v>0.46</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1511</v>
+        <v>1523</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
@@ -30170,24 +30516,24 @@
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_cityhall_front.webp</t>
+          <t>resources/si/npc/npc_imcommander_si_front.webp</t>
         </is>
       </c>
     </row>
     <row r="44" ht="111" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>母親</t>
+          <t>指揮官</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>capi_mom.webp</t>
+          <t>npc_imcommander_si_plead.webp</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>(base)</t>
+          <t>plead</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -30202,13 +30548,13 @@
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>0.413</v>
+        <v>0.481</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1535</v>
+        <v>1515</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
@@ -30217,24 +30563,24 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/capi_mom.webp</t>
+          <t>resources/si/npc/npc_imcommander_si_plead.webp</t>
         </is>
       </c>
     </row>
     <row r="45" ht="111" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>獵人</t>
+          <t>指揮官</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>npc_ep_si_bounty.webp</t>
+          <t>npc_imcommander_si_salute.webp</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>(base)</t>
+          <t>salute</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -30249,13 +30595,13 @@
         </is>
       </c>
       <c r="H45" s="2" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.452</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1535</v>
+        <v>1521</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
@@ -30264,24 +30610,24 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ep_si_bounty.webp</t>
+          <t>resources/si/npc/npc_imcommander_si_salute.webp</t>
         </is>
       </c>
     </row>
     <row r="46" ht="111" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>獵人</t>
+          <t>指揮官</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>npc_guildhunter_si.webp</t>
+          <t>npc_imcommander_si_shock.webp</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>(base)</t>
+          <t>shock</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -30296,13 +30642,13 @@
         </is>
       </c>
       <c r="H46" s="2" t="n">
-        <v>0.485</v>
+        <v>0.699</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1529</v>
+        <v>1518</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
@@ -30311,24 +30657,24 @@
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_guildhunter_si.webp</t>
+          <t>resources/si/npc/npc_imcommander_si_shock.webp</t>
         </is>
       </c>
     </row>
     <row r="47" ht="111" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>獵人</t>
+          <t>指揮官</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>npc_guildhunter_si_attack.webp</t>
+          <t>npc_imcommander_si_surprise.webp</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>attack</t>
+          <t>surprise</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -30343,13 +30689,13 @@
         </is>
       </c>
       <c r="H47" s="2" t="n">
-        <v>0.546</v>
+        <v>0.444</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1535</v>
+        <v>1521</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
@@ -30358,24 +30704,24 @@
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_guildhunter_si_attack.webp</t>
+          <t>resources/si/npc/npc_imcommander_si_surprise.webp</t>
         </is>
       </c>
     </row>
     <row r="48" ht="111" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>獵人</t>
+          <t>指揮官</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>npc_guildhunter_si_lost.webp</t>
+          <t>npc_imcommander_si_urgent.webp</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>lost</t>
+          <t>urgent</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -30390,13 +30736,13 @@
         </is>
       </c>
       <c r="H48" s="2" t="n">
-        <v>0.487</v>
+        <v>0.669</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1529</v>
+        <v>1518</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
@@ -30405,24 +30751,24 @@
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_guildhunter_si_lost.webp</t>
+          <t>resources/si/npc/npc_imcommander_si_urgent.webp</t>
         </is>
       </c>
     </row>
     <row r="49" ht="111" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>獵人</t>
+          <t>村民</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>npc_guildhunter_si_shock.webp</t>
+          <t>npc_shinier_grocery_si.webp</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>shock</t>
+          <t>(base)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -30437,13 +30783,13 @@
         </is>
       </c>
       <c r="H49" s="2" t="n">
-        <v>0.453</v>
+        <v>0.542</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1535</v>
+        <v>1530</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
@@ -30452,19 +30798,19 @@
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_guildhunter_si_shock.webp</t>
+          <t>resources/si/npc/npc_shinier_grocery_si.webp</t>
         </is>
       </c>
     </row>
     <row r="50" ht="111" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>瑪麗亞</t>
+          <t>村民</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>npc_shinier_cook_si.webp</t>
+          <t>npc_shinier_gunsmith_si.webp</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -30484,13 +30830,13 @@
         </is>
       </c>
       <c r="H50" s="2" t="n">
-        <v>0.463</v>
+        <v>0.603</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1522</v>
+        <v>1531</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
@@ -30499,19 +30845,19 @@
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_shinier_cook_si.webp</t>
+          <t>resources/si/npc/npc_shinier_gunsmith_si.webp</t>
         </is>
       </c>
     </row>
     <row r="51" ht="111" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>群眾</t>
+          <t>村民</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>npc_northport_crowd.webp</t>
+          <t>npc_shinier_hunter_si.webp</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -30531,13 +30877,13 @@
         </is>
       </c>
       <c r="H51" s="2" t="n">
-        <v>0.37</v>
+        <v>0.421</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1527</v>
+        <v>1524</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
@@ -30546,19 +30892,19 @@
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_northport_crowd.webp</t>
+          <t>resources/si/npc/npc_shinier_hunter_si.webp</t>
         </is>
       </c>
     </row>
     <row r="52" ht="111" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>路人</t>
+          <t>村長</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_worker_talk.webp</t>
+          <t>npc_shinier_chief_si.webp</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -30578,13 +30924,13 @@
         </is>
       </c>
       <c r="H52" s="2" t="n">
-        <v>0.43</v>
+        <v>0.537</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1532</v>
+        <v>1520</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
@@ -30593,19 +30939,19 @@
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_worker_talk.webp</t>
+          <t>resources/si/npc/npc_shinier_chief_si.webp</t>
         </is>
       </c>
     </row>
     <row r="53" ht="111" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>里朋</t>
+          <t>櫃台</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_boss_clap.webp</t>
+          <t>guildcounterca_si.webp</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -30625,13 +30971,13 @@
         </is>
       </c>
       <c r="H53" s="2" t="n">
-        <v>0.409</v>
+        <v>0.511</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1518</v>
+        <v>1526</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
@@ -30640,24 +30986,24 @@
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_boss_clap.webp</t>
+          <t>resources/si/guildcounterca_si.webp</t>
         </is>
       </c>
     </row>
     <row r="54" ht="111" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>里朋</t>
+          <t>櫃台</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_boss_hurt.webp</t>
+          <t>npc_guildcounter_si_northport.webp</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>hurt</t>
+          <t>(base)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -30672,13 +31018,13 @@
         </is>
       </c>
       <c r="H54" s="2" t="n">
-        <v>0.261</v>
+        <v>0.49</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1529</v>
+        <v>1522</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
@@ -30687,19 +31033,19 @@
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_boss_hurt.webp</t>
+          <t>resources/si/npc/npc_guildcounter_si_northport.webp</t>
         </is>
       </c>
     </row>
     <row r="55" ht="111" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>隨從</t>
+          <t>櫃台</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>sodier_.webp</t>
+          <t>npc_guildcounter_si_v5.webp</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -30712,20 +31058,24 @@
           <t>✔</t>
         </is>
       </c>
-      <c r="F55" s="3" t="n"/>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>3 張：npc_guildcounter_si_v1.webp、npc_guildcounter_si_v3.webp、npc_guildcounter_si_v4.webp</t>
+        </is>
+      </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
           <t>量</t>
         </is>
       </c>
       <c r="H55" s="2" t="n">
-        <v>0.451</v>
+        <v>0.492</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1534</v>
+        <v>1531</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
@@ -30734,24 +31084,24 @@
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/sodier_.webp</t>
+          <t>resources/si/npc/npc_guildcounter_si_v5.webp</t>
         </is>
       </c>
     </row>
     <row r="56" ht="111" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>馬努</t>
+          <t>櫃台</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_lofa_capture.webp</t>
+          <t>npc_ss_cityhall_cringe.webp</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>capture</t>
+          <t>cringe</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -30766,13 +31116,13 @@
         </is>
       </c>
       <c r="H56" s="2" t="n">
-        <v>0.46</v>
+        <v>0.494</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1501</v>
+        <v>1520</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
@@ -30781,24 +31131,24 @@
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_ss_lofa_capture.webp</t>
+          <t>resources/si/npc/npc_ss_cityhall_cringe.webp</t>
         </is>
       </c>
     </row>
     <row r="57" ht="111" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>馬努</t>
+          <t>櫃台</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>npc_ss_lofa_cryshoot.webp</t>
+          <t>npc_ss_cityhall_front.webp</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>shot</t>
+          <t>(base)</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -30813,20 +31163,678 @@
         </is>
       </c>
       <c r="H57" s="2" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>1511</v>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/npc/npc_ss_cityhall_front.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="111" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>母親</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>capi_mom.webp</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>(base)</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="n"/>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>1535</v>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/npc/capi_mom.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="111" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>獵人</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>npc_ep_si_bounty.webp</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>(base)</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="n"/>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>1535</v>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/npc/npc_ep_si_bounty.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="111" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>獵人</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>npc_guildhunter_si.webp</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>(base)</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="n"/>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>1529</v>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/npc/npc_guildhunter_si.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="111" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>獵人</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>npc_guildhunter_si_attack.webp</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="n"/>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>1535</v>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/npc/npc_guildhunter_si_attack.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="111" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>獵人</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>npc_guildhunter_si_lost.webp</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>lost</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="n"/>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>1529</v>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/npc/npc_guildhunter_si_lost.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="111" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>獵人</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>npc_guildhunter_si_shock.webp</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>shock</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="n"/>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>0.453</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>1535</v>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/npc/npc_guildhunter_si_shock.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="111" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>瑪麗亞</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>npc_shinier_cook_si.webp</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>(base)</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="n"/>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>1522</v>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/npc/npc_shinier_cook_si.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="111" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>群眾</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>npc_northport_crowd.webp</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>(base)</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="n"/>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>1527</v>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/npc/npc_northport_crowd.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="111" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>路人</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>npc_ss_worker_talk.webp</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>(base)</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="n"/>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>1532</v>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/npc/npc_ss_worker_talk.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="111" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>里朋</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>npc_ss_boss_clap.webp</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>(base)</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="n"/>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>1518</v>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/npc/npc_ss_boss_clap.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="111" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>里朋</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>npc_ss_boss_hurt.webp</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>hurt</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="n"/>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>1529</v>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/npc/npc_ss_boss_hurt.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="111" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>隨從</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>sodier_.webp</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>(base)</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="n"/>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>1534</v>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/npc/sodier_.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="111" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>馬努</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>npc_ss_lofa_capture.webp</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>capture</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="n"/>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>1501</v>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>resources/si/npc/npc_ss_lofa_capture.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="111" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>馬努</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>npc_ss_lofa_cryshoot.webp</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>shot</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="n"/>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>量</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="n">
         <v>0.42</v>
       </c>
-      <c r="I57" s="2" t="n">
+      <c r="I71" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J57" s="2" t="n">
+      <c r="J71" s="2" t="n">
         <v>1514</v>
       </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>1024×1536</t>
-        </is>
-      </c>
-      <c r="L57" s="3" t="inlineStr">
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>1024×1536</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
         <is>
           <t>resources/si/npc/npc_ss_lofa_cryshoot.webp</t>
         </is>
@@ -31145,7 +32153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D141"/>
+  <dimension ref="A1:D140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -31580,12 +32588,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>a69b6fbd-57a2-4ca2-852c-2a6ac63f8a25</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>aaron_si_angry.webp</t>
+          <t>a69b6fbd-57a2-4ca2-852c-2a6ac63f8a25.png</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -31607,7 +32615,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>aaron_si_armscross.webp</t>
+          <t>aaron_si_angry.webp</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -31629,7 +32637,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>aaron_si_attention.webp</t>
+          <t>aaron_si_armscross.webp</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -31651,7 +32659,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>aaron_si_blindeye.webp</t>
+          <t>aaron_si_attention.webp</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -31673,7 +32681,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>aaron_si_closedsmile.webp</t>
+          <t>aaron_si_blindeye.webp</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -31695,7 +32703,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>aaron_si_confused.webp</t>
+          <t>aaron_si_closedsmile.webp</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -31717,7 +32725,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>aaron_si_draw.webp</t>
+          <t>aaron_si_confused.webp</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -31739,7 +32747,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>aaron_si_front.webp</t>
+          <t>aaron_si_draw.webp</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -31761,7 +32769,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>aaron_si_signal.webp</t>
+          <t>aaron_si_front.webp</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -31778,12 +32786,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Church_guard</t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>church_guard_si_a.webp</t>
+          <t>aaron_si_signal.webp</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -31805,7 +32813,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>church_guard_si_b.webp</t>
+          <t>church_guard_si_a.webp</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -31827,7 +32835,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>church_guard_si_c.webp</t>
+          <t>church_guard_si_b.webp</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -31849,7 +32857,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>church_guard_si_d.webp</t>
+          <t>church_guard_si_c.webp</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -31871,7 +32879,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>church_guard_si_e.webp</t>
+          <t>church_guard_si_d.webp</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -31893,7 +32901,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>church_guard_si_f.webp</t>
+          <t>church_guard_si_e.webp</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -31910,12 +32918,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>f734e7ba-e7bb-457b-8cf7-66e13324c45d</t>
+          <t>Church_guard</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>f734e7ba-e7bb-457b-8cf7-66e13324c45d.png</t>
+          <t>church_guard_si_f.webp</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -31932,12 +32940,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mage</t>
+          <t>f734e7ba-e7bb-457b-8cf7-66e13324c45d</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>mage_si_cast.webp</t>
+          <t>f734e7ba-e7bb-457b-8cf7-66e13324c45d.png</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -31959,7 +32967,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>mage_si_hurtdown.webp</t>
+          <t>mage_si_cast.webp</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -32697,22 +33705,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>指到但檔案不在</t>
+          <t>同差分的另一個版本</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>mage / hurtsmile</t>
+          <t>Anya</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>resources/si/npc/mage_si_hurtsmile.webp</t>
+          <t>resources/si/anya_si_nod.png</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>路徑打錯，或美術還沒交 —— 演到那一句會回退基本立繪</t>
+          <t>線上跑的是 anya_si_nod.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -32724,17 +33732,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Anya</t>
+          <t>Cecilie</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>resources/si/anya_si_nod.png</t>
+          <t>resources/si/cecilie_si_saintinstall.png</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>線上跑的是 anya_si_nod.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_saintinstall.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -32746,17 +33754,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Misha</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>resources/si/cecilie_si_saintinstall.png</t>
+          <t>resources/si/misha_si_fight.png</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_saintinstall.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 misha_si_fight.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -32773,12 +33781,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>resources/si/misha_si_fight.png</t>
+          <t>resources/si/misha_si_ni.png</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>線上跑的是 misha_si_fight.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 misha_si_ni.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -32790,17 +33798,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Misha</t>
+          <t>Nouvelle</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>resources/si/misha_si_ni.png</t>
+          <t>resources/si/nouvelle_si_gossip1.png</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>線上跑的是 misha_si_ni.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 nouvelle_si_gossip1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -32817,12 +33825,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>resources/si/nouvelle_si_gossip1.png</t>
+          <t>resources/si/nouvelle_si_salute.png</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>線上跑的是 nouvelle_si_gossip1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 nouvelle_si_salute.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -32839,12 +33847,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>resources/si/nouvelle_si_salute.png</t>
+          <t>resources/si/nouvelle_si_sigh.png</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>線上跑的是 nouvelle_si_salute.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 nouvelle_si_sigh.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -32856,17 +33864,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Nouvelle</t>
+          <t>Npc_grocer</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>resources/si/nouvelle_si_sigh.png</t>
+          <t>resources/si/npc/npc_grocer_si_v2.webp</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>線上跑的是 nouvelle_si_sigh.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -32883,7 +33891,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_grocer_si_v2.webp</t>
+          <t>resources/si/npc/npc_grocer_si_v3.webp</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -32905,7 +33913,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_grocer_si_v3.webp</t>
+          <t>resources/si/npc/npc_grocer_si_v4.webp</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -32927,7 +33935,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_grocer_si_v4.webp</t>
+          <t>resources/si/npc/npc_grocer_si_v5.webp</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -32944,17 +33952,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Npc_grocer</t>
+          <t>Npc_guildcounter</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_grocer_si_v5.webp</t>
+          <t>resources/si/npc/npc_guildcounter_si_v1.webp</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_grocer_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_guildcounter_si_v5.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -32971,7 +33979,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_guildcounter_si_v1.webp</t>
+          <t>resources/si/npc/npc_guildcounter_si_v3.webp</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -32993,7 +34001,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_guildcounter_si_v3.webp</t>
+          <t>resources/si/npc/npc_guildcounter_si_v4.webp</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -33010,17 +34018,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Npc_guildcounter</t>
+          <t>Npc_gunsmith</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_guildcounter_si_v4.webp</t>
+          <t>resources/si/npc/npc_gunsmith_si_v2.webp</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_guildcounter_si_v5.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33037,7 +34045,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_gunsmith_si_v2.webp</t>
+          <t>resources/si/npc/npc_gunsmith_si_v3.webp</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -33059,7 +34067,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_gunsmith_si_v3.webp</t>
+          <t>resources/si/npc/npc_gunsmith_si_v4.webp</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -33081,7 +34089,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_gunsmith_si_v4.webp</t>
+          <t>resources/si/npc/npc_gunsmith_si_v5.webp</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -33098,17 +34106,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Npc_gunsmith</t>
+          <t>Cecilie</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>resources/si/npc/npc_gunsmith_si_v5.webp</t>
+          <t>resources/si/old/cecilie_si_front.png</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>線上跑的是 npc_gunsmith_si_v1.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_front.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33125,12 +34133,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_front.png</t>
+          <t>resources/si/old/cecilie_si_lookaside.png</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_front.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_lookaside.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33147,12 +34155,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_lookaside.png</t>
+          <t>resources/si/old/cecilie_si_sadback.png</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_lookaside.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_sadback.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33169,12 +34177,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_sadback.png</t>
+          <t>resources/si/old/cecilie_si_smile.png</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_sadback.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_smile.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33191,12 +34199,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_smile.png</t>
+          <t>resources/si/old/cecilie_si_tease.png</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_smile.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_tease.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33213,12 +34221,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_tease.png</t>
+          <t>resources/si/old/cecilie_si_upset.png</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_tease.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 cecilie_si_upset.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33230,17 +34238,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Cecilie</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>resources/si/old/cecilie_si_upset.png</t>
+          <t>resources/si/renna_newhair/renna_si_argue.webp</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>線上跑的是 cecilie_si_upset.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_argue.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33257,12 +34265,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_argue.webp</t>
+          <t>resources/si/renna_newhair/renna_si_arguecute.webp</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_argue.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_arguecute.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33279,12 +34287,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_arguecute.webp</t>
+          <t>resources/si/renna_newhair/renna_si_ask.webp</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_arguecute.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_ask.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33301,12 +34309,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_ask.webp</t>
+          <t>resources/si/renna_newhair/renna_si_askserious.webp</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_ask.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_askserious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33323,12 +34331,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_askserious.webp</t>
+          <t>resources/si/renna_newhair/renna_si_awkwerd.webp</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_askserious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_awkwerd.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33345,12 +34353,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_awkwerd.webp</t>
+          <t>resources/si/renna_newhair/renna_si_blush.webp</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_awkwerd.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_blush.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33367,12 +34375,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_blush.webp</t>
+          <t>resources/si/renna_newhair/renna_si_bow.webp</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_blush.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_bow.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33389,12 +34397,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_bow.webp</t>
+          <t>resources/si/renna_newhair/renna_si_callangry.webp</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_bow.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_callangry.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33411,12 +34419,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_callangry.webp</t>
+          <t>resources/si/renna_newhair/renna_si_chase.webp</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_callangry.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_chase.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33433,12 +34441,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_chase.webp</t>
+          <t>resources/si/renna_newhair/renna_si_chase2.webp</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_chase.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_chase2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33455,12 +34463,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_chase2.webp</t>
+          <t>resources/si/renna_newhair/renna_si_command.webp</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_chase2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_command.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33477,12 +34485,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_command.webp</t>
+          <t>resources/si/renna_newhair/renna_si_covermouth.webp</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_command.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_covermouth.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33499,12 +34507,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_covermouth.webp</t>
+          <t>resources/si/renna_newhair/renna_si_cringe.webp</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_covermouth.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_cringe.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33521,12 +34529,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_cringe.webp</t>
+          <t>resources/si/renna_newhair/renna_si_curious.webp</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_cringe.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_curious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33543,12 +34551,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_curious.webp</t>
+          <t>resources/si/renna_newhair/renna_si_die.webp</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_curious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_die.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33565,12 +34573,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_die.webp</t>
+          <t>resources/si/renna_newhair/renna_si_evaluate.webp</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_die.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_evaluate.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33587,12 +34595,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_evaluate.webp</t>
+          <t>resources/si/renna_newhair/renna_si_front.webp</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_evaluate.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_front.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33609,12 +34617,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_front.webp</t>
+          <t>resources/si/renna_newhair/renna_si_intense.webp</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_front.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_intense.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33631,12 +34639,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_intense.webp</t>
+          <t>resources/si/renna_newhair/renna_si_intense2.webp</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_intense.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_intense2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33653,12 +34661,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_intense2.webp</t>
+          <t>resources/si/renna_newhair/renna_si_invite.webp</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_intense2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_invite.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33675,12 +34683,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_invite.webp</t>
+          <t>resources/si/renna_newhair/renna_si_lookaway.webp</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_invite.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_lookaway.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33697,12 +34705,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_lookaway.webp</t>
+          <t>resources/si/renna_newhair/renna_si_lookawaytalk.webp</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_lookaway.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_lookawaytalk.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33719,12 +34727,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_lookawaytalk.webp</t>
+          <t>resources/si/renna_newhair/renna_si_lookdown.webp</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_lookawaytalk.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_lookdown.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33741,12 +34749,12 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_lookdown.webp</t>
+          <t>resources/si/renna_newhair/renna_si_lookup.webp</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_lookdown.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_lookup.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33763,12 +34771,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_lookup.webp</t>
+          <t>resources/si/renna_newhair/renna_si_pause.webp</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_lookup.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_pause.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33785,12 +34793,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_pause.webp</t>
+          <t>resources/si/renna_newhair/renna_si_relief.webp</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_pause.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_relief.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33807,12 +34815,12 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_relief.webp</t>
+          <t>resources/si/renna_newhair/renna_si_sad.webp</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_relief.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_sad.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33829,12 +34837,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_sad.webp</t>
+          <t>resources/si/renna_newhair/renna_si_shout.webp</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_sad.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_shout.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33851,12 +34859,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_shout.webp</t>
+          <t>resources/si/renna_newhair/renna_si_smile.webp</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_shout.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_smile.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33873,12 +34881,12 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_smile.webp</t>
+          <t>resources/si/renna_newhair/renna_si_stare.webp</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_smile.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_stare.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33895,12 +34903,12 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_stare.webp</t>
+          <t>resources/si/renna_newhair/renna_si_surprise.webp</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_stare.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_surprise.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33917,12 +34925,12 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_surprise.webp</t>
+          <t>resources/si/renna_newhair/renna_si_talkserious.webp</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_surprise.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_talkserious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33939,12 +34947,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_talkserious.webp</t>
+          <t>resources/si/renna_newhair/renna_si_talkwork.webp</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_talkserious.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_talkwork.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33961,12 +34969,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_talkwork.webp</t>
+          <t>resources/si/renna_newhair/renna_si_think.webp</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_talkwork.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_think.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -33983,12 +34991,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_think.webp</t>
+          <t>resources/si/renna_newhair/renna_si_tire.webp</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_think.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_tire.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -34005,12 +35013,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_tire.webp</t>
+          <t>resources/si/renna_newhair/renna_si_upset.webp</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_tire.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_upset.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -34027,12 +35035,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_upset.webp</t>
+          <t>resources/si/renna_newhair/renna_si_upsetstare.webp</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_upset.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_upsetstare.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -34049,12 +35057,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_upsetstare.webp</t>
+          <t>resources/si/renna_newhair/renna_si_wake.webp</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_upsetstare.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_wake.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -34071,12 +35079,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_wake.webp</t>
+          <t>resources/si/renna_newhair/renna_si_watch.webp</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_wake.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_watch.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -34093,12 +35101,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_watch.webp</t>
+          <t>resources/si/renna_newhair/renna_si_worry.webp</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_watch.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_worry.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -34115,12 +35123,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_worry.webp</t>
+          <t>resources/si/renna_newhair/renna_si_write.webp</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_worry.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_write.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -34137,12 +35145,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>resources/si/renna_newhair/renna_si_write.webp</t>
+          <t>resources/si/renna_si_hug.png</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_write.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_hug.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -34159,12 +35167,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_hug.png</t>
+          <t>resources/si/renna_si_hugangry2.png</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_hug.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_hugangry2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -34181,12 +35189,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_hugangry2.png</t>
+          <t>resources/si/renna_si_hugclose.png</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_hugangry2.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_hugclose.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -34203,12 +35211,12 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_hugclose.png</t>
+          <t>resources/si/renna_si_huglookaway.png</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>線上跑的是 renna_si_hugclose.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
+          <t>線上跑的是 renna_si_huglookaway.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
       </c>
     </row>
@@ -34220,37 +35228,15 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Renna</t>
+          <t>Torsten</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>resources/si/renna_si_huglookaway.png</t>
+          <t>resources/si/torsten_si_back.png</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
-        <is>
-          <t>線上跑的是 renna_si_huglookaway.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>同差分的另一個版本</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Torsten</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>resources/si/torsten_si_back.png</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
         <is>
           <t>線上跑的是 torsten_si_back.webp —— 要換上去就改 speakers.js 的 src，並**重量** fx／top／bot（§5：換圖一定要重量取景）</t>
         </is>
